--- a/public/scripts.xlsx
+++ b/public/scripts.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1527" uniqueCount="1200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1602" uniqueCount="1278">
   <si>
     <t>CF</t>
   </si>
@@ -944,9 +944,6 @@
     <t>상담 운영시간 챗봇</t>
   </si>
   <si>
-    <t>⏳ 상담운영시간: 월~금 10:00 ~ 18:00</t>
-  </si>
-  <si>
     <t>MD 3 상담 신뢰 형성</t>
   </si>
   <si>
@@ -954,9 +951,6 @@
   </si>
   <si>
     <t>신원증빙</t>
-  </si>
-  <si>
-    <t>[banksalad/CNR 명함 이미지 - 센트럴미디어본부 / 본부장]</t>
   </si>
   <si>
     <t>OOO님, 안녕하세요! 오늘 보험 상담을 꼼꼼하게 도와드릴 전담 전문가 정복선 본부장이에요😊 궁금하신 점들 제가 하나씩 쉽게 풀어서 안내해 드릴게요:)</t>
@@ -4502,44 +4496,410 @@
     <t>내용</t>
   </si>
   <si>
-    <t>오프닝 인사</t>
-  </si>
-  <si>
-    <t>안녕하세요, 오늘 시간 내주셔서 감사합니다. 뱅크샐러드 보험 서비스를 이용해주셔서 감사드려요. 고객님께 꼭 맞는 보험을 찾아드릴게요.</t>
-  </si>
-  <si>
-    <t>앞서 상담 받은 분들은 평균 30% 이상 보험료를 줄이고, 보장받을 확률은 높이셨어요. 고객님도 한번 확인해보시겠어요?</t>
-  </si>
-  <si>
-    <t>거절 대응</t>
-  </si>
-  <si>
-    <t>지금 당장 결정 안 하셔도 됩니다. 부담 없이 한번만 확인해보시고 결정하셔도 충분해요.</t>
-  </si>
-  <si>
-    <t>주계약 외 대부분이 갱신형으로 되어 있어서 보험료가 100세까지 계속 오르는 구조입니다. 비갱신형으로 바꾸시면 보험료를 고정할 수 있어요.</t>
-  </si>
-  <si>
-    <t>보장기간 부족</t>
-  </si>
-  <si>
-    <t>현재 만기가 짧게 설정되어 있어 가장 병원비가 많이 드는 노후에 보장이 끊길 수 있습니다. 100세 만기로 조정하시는 걸 추천드려요.</t>
-  </si>
-  <si>
-    <t>여러 보험사를 비교해서 고객님께 가장 유리한 보장과 보험료를 찾아드릴 수 있습니다. 비교 진행해드릴까요?</t>
-  </si>
-  <si>
-    <t>가입 완료 인사</t>
-  </si>
-  <si>
-    <t>보험이 진짜 힘이 되는 날은 보험금을 받는 날이에요. 고객님 전담 매니저로서 그날까지 함께하겠습니다.</t>
+    <t>첫 인사</t>
+  </si>
+  <si>
+    <t>00님, 안녕하세요! 오늘 보험 상담을 꼼꼼하게 도와드릴 전담 전문가 김나경이에요😊 궁금하신 점들 제가 하나씩 쉽게 풀어서 안내해 드릴게요:)</t>
+  </si>
+  <si>
+    <t>상담 니즈 파악</t>
+  </si>
+  <si>
+    <t>네, 00님의 소중한 상담 요청 감사합니다. 이번 상담을 통해 얻고 싶은 가치나 해결하고 싶으신 게 있으실까요?</t>
+  </si>
+  <si>
+    <t>점검 시작 안내</t>
+  </si>
+  <si>
+    <t>보험 점검 받고 싶어서 상담 신청해 주신 걸로 확인되는데요! 제가 전체적으로 점검 후 하나씩 설명드릴게요! 혹시 상담에서 원하시는 것이 있나용?</t>
+  </si>
+  <si>
+    <t>분석 시작 안내 (긴 상담량 대비)</t>
+  </si>
+  <si>
+    <t>네 확인 감사합니다 :)
+우선순위가 높은 건강보험에 대해 [🟦 유지/🟩 조정 후 유지/🟥 해지]로 분석해드릴 예정이며, 휴일이라 상담량이 많은 편으로 다소 시간이 소요될 수 있는 점 양해 부탁드립니다!
+(+) 또한 보험상담을 요청주신 고민이나, 계기가 따로 있으시다면 편히 말씀해 주세요 😊</t>
+  </si>
+  <si>
+    <t>여러 보험사 비교를 위한 고객 등록</t>
+  </si>
+  <si>
+    <t>비교 견적 보내드리기 앞서, 간단 설계를 위한 고객님의 최소한의 정보가 필요합니다.
+아래의 링크를 눌러 고객님의 【직업, 병력사항, 예산】정보를 입력해주세요!
+ 작성 후에는 꼭 『입력완료!』를 말씀해 주셔야 누락되지 않아요!</t>
+  </si>
+  <si>
+    <t>기존 보장 / 조정 후 보장 설명</t>
+  </si>
+  <si>
+    <t>☑️[기존 보장]
+현재 가입 중인 보험의 주요 보장을 정리한 항목입니다!
+※ 보장기간이 80세 이하로 장기적인 보장 역할이 불가한 만기가 짧은 보장은 제외했습니다‼️
+☑️[조정 후 보장]
+기존 보험 중 보장을 조정하거나 향후 정리가 필요한 특약들을 제외하고, 남은 주요 보장 내용만을 정리한 항목입니다</t>
+  </si>
+  <si>
+    <t>보험료 절감 안내</t>
+  </si>
+  <si>
+    <t>제가 위에 안내드리는 보험들을 정리하시면 총 362,440원을 아끼실 수 있습니다.
+부족한 보장범위를 채워드려서 새로 넣는다면
+&lt;1안&gt; 97,190원 → 기존 월 보험료보다 265,250원 절감!
+&lt;2안&gt; 109,754원 → 기존 월 보험료보다 252,686원 절감!</t>
+  </si>
+  <si>
+    <t>CI보험 설명 (짧음)</t>
+  </si>
+  <si>
+    <t>CI보험은 암 진단을 받아도 보험사가 정한 기준에 맞는 심각한 수준의 암이어야만 돈이 나오는 구조이고, 사망보험금을 선지급하는 구조이기에 19년을 유지하셔도 실제로 보장받을 수 있는 경우가 생각보다 많지 않습니다. 오래 가지고 계신 것과 보장이 잘 된다는 건 별개의 얘기입니다.</t>
+  </si>
+  <si>
+    <t>CI보험 설명 (상세)</t>
+  </si>
+  <si>
+    <t>CI보험은 일반 암 보험과 다릅니다. CI보험은 원래 사망보험금을 미리 받는 구조라서, 암 진단을 받아도 약관에서 정한 '중대한 암'이어야만 보험금의 50~80%를 받을 수 있어요. 초기 암이나 애매한 단계의 종양은 보장이 안 될 수도 있거든요.
+반면 일반 암보험은 암으로 진단받으면 초기든 중증이든 약속한 금액을 전액 드리는 구조라, 실제 치료비 대비 목적으로는 일반 암보험이 훨씬 넓게 보장돼요!</t>
+  </si>
+  <si>
+    <t>실손보험 갱신형, 유지 이유</t>
+  </si>
+  <si>
+    <t>실손보험은 갱신형이지만 예외입니다.
+실손보험은 비갱신형 상품 자체가 존재하지 않아요. 모든 실손보험이 갱신형 구조로만 출시되기 때문에, 갱신형이라는 이유로 정리하면 실손 자체를 포기하는 게 됩니다.
+실손은 병원 치료비를 직접 보전해주는 보험이라 없으면 안 되는 기본 중의 기본이라, 갱신형이어도 유지하시는 게 맞습니다.
+정리 대상인 갱신형은 진단비·수술비처럼 비갱신형으로 대체 가능한 보장들이고, 실손은 대체 수단이 없어서 구분해서 보셔야 해요.</t>
+  </si>
+  <si>
+    <t>갱신형 위험성 (상세)</t>
+  </si>
+  <si>
+    <t>보험료가 앞으로 계속 오르고 끝까지 납입하셔야 하는 점에서 가성비가 매우 떨어집니다. 일반 20년납 보험이면 20년 후 납입이 완전히 끝납니다. 이후에는 보험료를 한 푼도 내지 않아도 보장이 계속됩니다.
+하지만 갱신형은 납입 기간이라는 개념 자체가 없습니다. 5년 또는 10년마다 계약을 '갱신'하는 방식이기 때문에, 갱신할 때마다 그 시점의 나이와 위험률을 반영해서 보험료가 새로 책정됩니다. 그리고 그 보험료를 만기까지 계속 내셔야 합니다.</t>
+  </si>
+  <si>
+    <t>갱신형 정리 후 부족 보장 채우기</t>
+  </si>
+  <si>
+    <t>갱신형 보험들을 정리하시면, 현재 있는 보장에서 부족한 보장이 생기기 때문에 정리하시고 아낀 금액으로 보장을 채우시는 걸 추천드립니다. 
+= 갱신형 보험들을 정리하고, 아낀 보험료로 지금 부족한 보장을 채우는 방향을 추천드려요.</t>
+  </si>
+  <si>
+    <t>갱신형 위험성 (노후 강조)</t>
+  </si>
+  <si>
+    <t>지금은 소득이 있으셔서 납부하실 수 있지만 나중에 노동능력을 상실하게 될 노후에는 그 보험료를 납입할 수 없어서 결국 해지하게 되고, 그때에는 병에 걸려도 보장받을 수 없습니다. 그래서 미리미리 준비하셔서 20년 납입하시고 평생 보장받으실 수 있는 기초를 미리 쌓아두는 게 좋습니다!</t>
+  </si>
+  <si>
+    <t>갱신형 개념 정의</t>
+  </si>
+  <si>
+    <t>✅ 갱신형 보험이란?
+약속한 기간이 지나면 '보험료가 변동'되며 '보장받는 기간 동안 계속하여 보험료를 납입'하는 구조의 보험을 말합니다. 반대로 가입 당시 '약속한 보험료가 동일하게 유지'되는 구조의 보험은 비갱신형이라고 합니다.
+갱신형 구조의 상품은 장기적으로 보험을 유지하는 데 큰 부담을 줍니다. 나이가 젊을 땐 질병의 발병 가능성이 낮아 보험료가 저렴하지만, 나이가 들어갈수록 높아지는 발병률만큼 보험료는 상승하게 되는 구조입니다.</t>
+  </si>
+  <si>
+    <t>나중에 생각하면 안 되나요?' 반론 대응</t>
+  </si>
+  <si>
+    <t>중요한 것은 '얼마나 오를지 정확히 맞히는 것'보다 '오를 수 있는 구조이고, 그때도 유지 가능한지'를 보는 것인데요!
+갱신형은 보험료가 오를 때 나이도 같이 올라가 있어요. 그 시점에 비갱신형으로 새로 가입하려 하면 지금보다 보험료가 훨씬 비싸진 건 기본이고, 그 사이에 건강 이상이 하나라도 생기면 가입 자체가 거절되거나 해당 보장이 빠질 수 있어요.
+지금 이 순간이 사실상 가장 저렴하고, 가장 조건 좋게 들 수 있는 타이밍이에요.</t>
+  </si>
+  <si>
+    <t>위험률이란</t>
+  </si>
+  <si>
+    <t>위험율이란?
+특정 보험 기간 내 가입자가 사고를 당하거나 사망할 확률.</t>
+  </si>
+  <si>
+    <t>청년 고객에게 비갱신형 우선 추천</t>
+  </si>
+  <si>
+    <t>갱신형 보험은 선제적으론 추천드리지 않습니다!
+비갱신형으로 뼈대를 든든히 준비하신 분들에게는 보완 목적의 서브 개념으로 갱신형 상품을 추천드리긴 하나, 현재 고객님은 전체적으로 보장이 부족하신 상황 + 나이대가 너무 젊으시기에 비갱신형으로 뼈대를 우선적으로 준비하시는 것을 권장드려요!</t>
+  </si>
+  <si>
+    <t>80/90세 만기 문제점</t>
+  </si>
+  <si>
+    <t>80세 만기 보험은 80세 이후에는 보장이 없다는 뜻입니다. 암·뇌·심장처럼 고령기에 위험이 커지는 보장이 80세에 끝난다면 공백이 생길 수 있습니다. 보험료는 저렴했지만, 정작 아플 가능성이 커지는 나이에 보장이 사라질 수 있습니다.</t>
+  </si>
+  <si>
+    <t>90세 만기 보장 소멸 흐름 시각화 (암/뇌/심장)</t>
+  </si>
+  <si>
+    <t>국가암통계 기준으로 여성은 60대에 암 발병이 가장 많고, 기대수명까지 생존하면 3명 중 1명이 암에 걸려요.
+지금 당장 → 암 5,000만 / 뇌 2,000만 / 심장 2,000만
+80세 이후 → 만기 도래 보험들 소멸 시작
+90세 이후 → 흥국화재·DB 90세 만기 소멸 → 전부 0원
+암이 가장 많이 오는 시기에 보장이 오히려 줄어들고, 결국 90세엔 실질적으로 0원이 되는 구조예요.</t>
+  </si>
+  <si>
+    <t>청년보험 설명</t>
+  </si>
+  <si>
+    <t>✅ 현재 고객님께서는 보험나이 40세 이하이기에 청년보험으로 준비가 가능합니다!👦🏻
+청년보험(기존 어린이보험)은 성인보험과 비교했을 때 다음과 같은 장점이 있습니다:
+· '가입 후 1년 이내 50% 감액기간'이 없습니다.
+· 납입면제 조건이 뇌혈관, 허혈성심장질환까지 포함됩니다.
+· 동일한 보장으로 성인보험보다 보험료가 저렴합니다.
+청년보험은 보험나이 40세까지만 보장되는 것이 아닙니다. 가입 가능 시기가 40세 이하이며, 보장은 일반 보험과 동일하게 90세 혹은 100세까지 보장되는 보험입니다.</t>
+  </si>
+  <si>
+    <t>실손 미보유 시 추천</t>
+  </si>
+  <si>
+    <t>네 맞습니다. 한 가지 더 말씀을 드리자면 국민의 70% 이상이 보유 중인 실손 의료비 보험을 고객님께선 미보유 중이시기 때문에 실손의료비 또한 추천드립니다.</t>
+  </si>
+  <si>
+    <t>회사 단체 실손 있을 때</t>
+  </si>
+  <si>
+    <t>회사실비보험은 회사에서 제공하는 좋은 혜택이지만, 회사를 다니는 동안만 보장받을 수 있는 보험이기 때문에, 이직이나 퇴사 시에는 더 이상 실비보험 혜택을 받을 수 없게 됩니다 🥲
+회사를 그만두게 되어 실비보험을 새로 가입하려 해도, 대부분 이미 발병한 질병 때문에 신규 가입이 어려울 수 있는 점 꼭 유의하시길 바랍니다.
+그렇기 때문에 회사실손보험이 있더라도 반드시 개인실손보험을 따로 준비하셔야 합니다!
+➡️ 이런 고객들을 위해 보험사는 [실손의료비 중지제도]를 운영하고 있습니다. 회사 실비보험이 가입된 상태에서 개인 실비를 가입하고 1년 이상 납부하면, 개인실비에 대한 보험료 납입 중지가 가능합니다. 퇴직 후 1개월 이내 신청 시 심사 없이 재개 가능합니다.</t>
+  </si>
+  <si>
+    <t>보장 준비 순서 안내</t>
+  </si>
+  <si>
+    <t>1️⃣ 필수 보장 – 실손의료비보험
+병원에서 쓰는 치료비 대부분을 보장해주기 때문에 가장 먼저 준비해야 하는 기본 보험입니다.
+2️⃣ 기본 보장 – 진단비
+실손이 있더라도 암·뇌·심장 같은 큰 병은 치료비 외에도 생활비가 필요합니다. 진단비는 병원비 영수증 없이, 진단을 받은 그 시점에 바로 지급되는 돈입니다.
+3️⃣ 튼튼한 보장 – 질병후유장해·수술비
+진단 이후의 삶까지 대비해야 해요.</t>
+  </si>
+  <si>
+    <t>판단기준 안내</t>
+  </si>
+  <si>
+    <t>보험 분석 시 판단기준
+&lt;판단기준&gt;
+① 나이 들수록 보험료가 오르는 갱신형 구조인지 
+② 이름은 비슷하지만 실제 보장 범위가 좁은 보험인지 
+③ 큰 병 걸렸을 때 받을 돈이 충분한지 
+④ 정작 아플 나이에 보장이 끝나는 만기인지 
+그럼 00세에 암 진단받으시면 얼마 받으실 수 있는지 아세요?</t>
+  </si>
+  <si>
+    <t>가입 순서 안내</t>
+  </si>
+  <si>
+    <t>지금부터 진행될 순서 알려드릴게요!
+① 가입을 위한 고객 등록을 먼저 진행합니다.
+② 병력 확인 후 심사 넣기
+③ 전자서명
+④ 계약 동의를 위한 정보 수집으로 새롭게 보장을 채우실 수 있구요.
+기존 보험 정리는 3개월 이후에 하시는 걸 추천드립니다. 병력 확인이 될 시 보험 가입이 어려우실 수도 있구요. 그때 저에게 알려주시면 정리 함께 도와드릴게요 ㅎㅎ</t>
+  </si>
+  <si>
+    <t>고객 등록 안내 (개인정보)</t>
+  </si>
+  <si>
+    <t>먼저 고객 등록을 위해 저를 조금 도와주셔야 하는데요. 주민번호와 주소, 직업을 저에게 알려주셔도 되고, 보험사 링크를 보내드리면 직접 입력하셔도 됩니다. 어떤 방법으로 진행해 드릴까요?</t>
+  </si>
+  <si>
+    <t>DB생명 링크 안내</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">DB생명(보험사) URL 보내드릴게요.
+링크에 작성하시는 개인정보는 고객님 이외에는 제가 확인할 수 없으니 안심하고 작성하셔도 되십니다😊
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial,sans-serif"/>
+        <color rgb="FF1155CC"/>
+        <sz val="11.0"/>
+        <u/>
+      </rPr>
+      <t>https://metopia.idblife.com/SWSWA00007M.mobile?plannerNo=1126611&amp;hphoneNo=538666&amp;sendNo=4</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial,sans-serif"/>
+        <sz val="9.0"/>
+      </rPr>
+      <t xml:space="preserve"> 
+발송되는 링크는 보험사 공식 도메인으로 연결되는 페이지라 개인정보가 저희 쪽으로는 전달되지 않고, 보험사 시스템에 직접 입력되는 구조입니다.</t>
+    </r>
+  </si>
+  <si>
+    <t>DB손보 링크 안내</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">DB손해(보험사) URL 보내드릴게요.
+링크에 작성하시는 개인정보는 고객님 이외에는 제가 확인할 수 없으니 안심하고 작성하셔도 되십니다😊
+</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial,sans-serif"/>
+        <color rgb="FF1155CC"/>
+        <sz val="9.0"/>
+        <u/>
+      </rPr>
+      <t>https://m.idbins.com/FMMYCV5245.do?no=zT3248ce4622720c5000</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial,sans-serif"/>
+        <sz val="9.0"/>
+      </rPr>
+      <t xml:space="preserve"> 
+발송되는 링크는 보험사 공식 도메인으로 연결되는 페이지라 개인정보가 저희 쪽으로는 전달되지 않고, 보험사 시스템에 직접 입력되는 구조입니다.</t>
+    </r>
+  </si>
+  <si>
+    <t>링크 도메인 불신 시 대응</t>
+  </si>
+  <si>
+    <t>고객님, DB생명 공식 도메인이 'idblife.com'입니다. 지금 발송된 링크 주소가 'metopia.idblife.com'으로 동일한 도메인 안에 있습니다. DB생명이 설계사 영업지원용으로 공식 운영하는 시스템 이름이 MEtopia입니다.</t>
+  </si>
+  <si>
+    <t>알릴의무 중요성</t>
+  </si>
+  <si>
+    <t>만약 이 직업이나 알릴의무가 제대로 고지 안 되면 나중에 불이익을 받으실 수 있어서요 ㅠㅠ</t>
+  </si>
+  <si>
+    <t>병력확인</t>
+  </si>
+  <si>
+    <t>Q. 최근 3개월 이내 의사로부터 진찰 또는 검사를 통하여 아래 의료행위를 받은 사실이 있습니까?
+Q. 최근 3개월이내에 마약을 사용하거나 혈압강하제, 신경안정제, 수면제, 각성제(흥분제), 진통제 등 약물을 상시복용한 사실이 있습니까?
+Q. 최근 1년 이내에 의사로부터 진찰 또는 검사를 받고, 이를 통하여 추가검사(재검사)를 받은 사실이 있습니까? 
+Q. 최근 5년 이내에 의사로부터 진찰 또는 검사를 통하여 다음과 같은 의료행위를 받은 사실이 있습니까?
+Q. 최근 5년 이내에 아래 11대질병으로 의사로부터 진찰 또는 검사를 통하여 다음과 같은 의료행위를 받은 사실이 있습니까?(단, 직장 및 항문관련 질환은 실손의료보험 가입시에만 기재하여 주십시오)</t>
+  </si>
+  <si>
+    <t>전자서명 정보 안내</t>
+  </si>
+  <si>
+    <t>이제 저를 한 번만 더 도와주시면 됩니다.
+전자서명을 위해서는 은행명 / 계좌번호 / 이메일을 저에게 알려주시고, 2회차 보험료 납입일은 5, 10, 15, 20, 25, 말일 중에 선택해주세요.</t>
+  </si>
+  <si>
+    <t>계좌번호 불신 시 대응</t>
+  </si>
+  <si>
+    <t>계좌번호를 저에게 알려주셔야 제가 전자서명을 입력한 후 고객님께 서명안을 보내드리는 시스템입니다 ㅠㅠ 전자서명을 위해서만 사용되고 다른 곳에는 사용되지 않으시니 너무 염려 마시길 바랍니다 ㅎㅎ</t>
+  </si>
+  <si>
+    <t>전자서명 vs 청약 차이 설명</t>
+  </si>
+  <si>
+    <t>전자서명 : 종이로 서명한다
+청약 : 종이에 서명도 했고 보험료도 납부해서 보장 시작
+이라고 생각해주시면 되겠습니다 ㅎㅎ
+아래에 청약 시 주의사항에 관련된 메시지를 보내드릴 텐데요, 조금 길어서 당황스러우실 것으로 예상됩니다 ㅠㅠ 그래도 양해 부탁드립니다. 🙏🏻</t>
+  </si>
+  <si>
+    <t>청약 시 주의사항 1</t>
+  </si>
+  <si>
+    <t>✔ 대면으로 계약 진행했는지? → 대면으로 하셨다고 진행해 주셔야 넘어가요!
+✔ 자필로 직접 서명하셨는지? → 모바일로 직접 서명하셨기에 자필 서명이 맞습니다.
+✔ 고지사항은 정확하게 알렸는지? → 알릴 의무 사항은 청약서를 통한 고객님의 최종 확인이 원칙이기에 서명을 진행하실 때 빠진 내용이 있는지 꼭 확인해 주세요.
+✔ 주계약과 특약의 기간은 각각 다를 수 있으며(실손보험, 배상책임 특약 등), 약관의 모든 내용을 설명에 담기 어려워 보다 자세한 내용은 제안서 및 청약서를 참조해 주세요.</t>
+  </si>
+  <si>
+    <t>청약 시 주의사항 2</t>
+  </si>
+  <si>
+    <t>✔ 청약 철회 (증권 받은 날부터 15일과 청약한 날로부터 30일 중 먼저 도래한 날까지) 가능합니다.
+✔ 보험금 청구권 소멸시효는 진료/치료일로부터 3년 이내입니다.
+✔ 보험은 중도 해지 시, 해약환급금이 납입된 보험료보다 적거나 없을 수 있습니다.
+✔ 상품설명을 못 들었거나 서류 미전달 시 약 3개월(90일) 이내 품질보증 해지가 가능합니다.
+✔ 이륜자동차 또는 원동기 장치 자전거(전동킥보드, 전동 이륜 평행 차 등 포함) 사용 중 사고는 보장되지 않습니다.</t>
+  </si>
+  <si>
+    <t>면책기간 설명</t>
+  </si>
+  <si>
+    <t>암 진단금에는 면책기간이라는 것이 있기에 3개월 정도만 20만 원 정도를 내시게 됩니다.
+면책기간은 암보험 가입하고 나서 바로 암 진단받아도 보험금 안 나오는 기간이에요. 보통 90일(3개월)인데, 이미 암이 있는 사람이 보험에 가입해서 바로 청구하는 걸 막으려고 두는 거예요. 이 기간 안에 암 진단이 나오면 보험금 대신 납입한 보험료만 돌려받고 계약이 끝나요. 90일 지나고 나서야 진짜 보장이 시작되는 거죠!</t>
+  </si>
+  <si>
+    <t>해지 후 가입 공백 주의</t>
+  </si>
+  <si>
+    <t>해지를 하고 가입을 하게 되신다면 그 기간 동안에 보장에 공백이 생기게 됩니다. 그래서 가입을 먼저 해두시고 해지를 하시는 걸 추천드립니다.</t>
+  </si>
+  <si>
+    <t>해지환급금 확인 방법</t>
+  </si>
+  <si>
+    <t>앱 또는 홈페이지 접속
+→ 로그인 / 본인인증 
+→ 보험계약조회 또는 나의 계약
+→ 해당 보험 선택 
+→ 해지환급금 / 해약환급금 / 예상해지환급금 확인
+( 확인되시면 상품명별로 현재 기준 해지환급금 금액만 캡처해서 보내주시면 됩니다. ) ⇒ 로그에 거의 안넣음.</t>
+  </si>
+  <si>
+    <t>정확한 해약환급금 문의 안내</t>
+  </si>
+  <si>
+    <t>정확한 해약환급금은 민감정보로 분류되어 있습니다. 때문에 계약자분께서 고객센터에 문의해주시는 것이 가장 정확합니다.</t>
+  </si>
+  <si>
+    <t>간편심사 → 일반심사 전환 절감 안내</t>
+  </si>
+  <si>
+    <t>일반적으로 간편심사형이 일반심사 대비 30~50% 정도 보험료가 높게 잡힙니다. 83,630원 기준으로 단순 계산하면 매달 2만 원에서 2만 7천 원 정도 절감이 가능해요.
+지금 건강하시다고 하셨으니까, 일반 심사로 새로 가입하시면 보험료는 낮추면서 보장은 그대로 유지하실 수 있습니다.</t>
+  </si>
+  <si>
+    <t>사전심사→가입제안서 순서 안내</t>
+  </si>
+  <si>
+    <t>사전심사는 가입하는 단계는 아니에요  우선 제가 드린 제안서대로 가입이 가능한지 알아보는 단계입니다!
+심사를 진행하지 않으신 상태에서 고민이나 조정은 큰 의미가 없습니다 
+고민이나 조정 후 가입을 결정하셨는데 심사가 아예 거절되거나 인수제한(부담보,할증)된다면,
+처음부터 다시 비교설계 - 조정 - 심사 하셔야합니다 ..ㅠ
+괜찮으시면 사전심사로 가입가능 여부 확인하시고 &gt; 조정이 필요한 부분에 대해 고민하시는 것을 추천드려요  어떠실까요?
+심사에서 문제 없이 통과가 된다면, 가입 전까지는 저랑 다시 상의해서 보험료 및 담보 조정이 가능합니다</t>
+  </si>
+  <si>
+    <t>상담 마무리 &amp; 소개 요청</t>
+  </si>
+  <si>
+    <t>지금까지 상담받으시느라 고생 많으셨습니다! 상담은 만족스러우셨을까요? 앞으로도 보험 관련 고민이 생기면, 저를 찾아주세요!
+만족스러운 상담이셨다면 '뱅금서 김나경'을 가족들, 지인들에게 소개해주세요! 🥰 (명함 같이 보내기)</t>
+  </si>
+  <si>
+    <t>뉴스 기사에 뱅크샐러드 GA 자회사 설립한다는 내용은 있는데, 정직원이라는 걸 어떻게 확인해요? 
+사기꾼도 똑같이 "정직원이라 문제없다"고 하거든요.</t>
+  </si>
+  <si>
+    <t>제 금융감독원 등록번호는 [260202] 입니다.
+파인(FINE) 사이트에서 직접 조회하실 수 있어요.
+👉 fine.fss.or.kr → 금융회사 조회 → 보험설계사 조회
+이름이랑 등록번호 치시면 제 정보 바로 나와요.
+확인하시고 편하게 연락 주세요 😊</t>
+  </si>
+  <si>
+    <t>보험가입 권유?</t>
+  </si>
+  <si>
+    <t>새 상품 권유임?</t>
+  </si>
+  <si>
+    <t>저는 요청하지 않는 이상 가입을 강요드리지 않아요. 제가 지금까지 말씀드린건 필요할 때 받기 힘들 수 있는 보장들이었어요. 저는 보장 대비 납부하시는 보험료 관점에서 줄일 수 있는 방향만 안내드리고 있어요. 안심하셔도 되어요.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="24">
+  <fonts count="29">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -4650,13 +5010,39 @@
     </font>
     <font>
       <b/>
-      <sz val="10.0"/>
-      <color theme="1"/>
+      <sz val="9.0"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10.0"/>
-      <color theme="1"/>
+      <sz val="9.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF1D1C1D"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="9.0"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="9.0"/>
+      <color rgb="FF1D1C1D"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FF1A1A1A"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -4741,6 +5127,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF0000FF"/>
+        <bgColor rgb="FF0000FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
@@ -4773,12 +5165,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF222222"/>
         <bgColor rgb="FF222222"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7F7F7"/>
-        <bgColor rgb="FFF7F7F7"/>
       </patternFill>
     </fill>
   </fills>
@@ -4890,7 +5276,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="83">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -5014,13 +5400,16 @@
     <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="14" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="14" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="15" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="15" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="16" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -5032,7 +5421,7 @@
     <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="14" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="15" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -5065,7 +5454,7 @@
     <xf borderId="0" fillId="0" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="14" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="15" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -5074,13 +5463,13 @@
     <xf borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="16" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="17" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="17" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="6" fillId="18" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -5088,29 +5477,44 @@
     <xf borderId="5" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="18" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="19" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="19" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="9" fillId="20" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="9" fillId="0" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf borderId="0" fillId="0" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="0" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="20" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf quotePrefix="1" borderId="0" fillId="0" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="20" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="24" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="20" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf borderId="0" fillId="0" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="26" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="27" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="15" fontId="28" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5140,7 +5544,7 @@
     <xdr:ext cx="1190625" cy="1257300"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image6.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -5168,7 +5572,7 @@
     <xdr:ext cx="676275" cy="1200150"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image2.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -5196,7 +5600,7 @@
     <xdr:ext cx="1190625" cy="914400"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image4.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -5224,7 +5628,7 @@
     <xdr:ext cx="1457325" cy="1143000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image5.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image1.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -5252,7 +5656,7 @@
     <xdr:ext cx="1790700" cy="914400"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image3.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -5280,7 +5684,7 @@
     <xdr:ext cx="190500" cy="190500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.png"/>
+        <xdr:cNvPr id="0" name="image7.png"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -5308,7 +5712,7 @@
     <xdr:ext cx="295275" cy="190500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image7.png"/>
+        <xdr:cNvPr id="0" name="image5.png"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -20684,9 +21088,7 @@
         <v>299</v>
       </c>
       <c r="E5" s="35"/>
-      <c r="F5" s="36" t="s">
-        <v>300</v>
-      </c>
+      <c r="F5" s="36"/>
       <c r="G5" s="37"/>
       <c r="H5" s="37"/>
       <c r="I5" s="36"/>
@@ -20737,18 +21139,16 @@
         <v>284</v>
       </c>
       <c r="B6" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="C6" s="34" t="s">
         <v>301</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="D6" s="34" t="s">
         <v>302</v>
       </c>
-      <c r="D6" s="34" t="s">
-        <v>303</v>
-      </c>
       <c r="E6" s="35"/>
-      <c r="F6" s="36" t="s">
-        <v>304</v>
-      </c>
+      <c r="F6" s="36"/>
       <c r="G6" s="37"/>
       <c r="H6" s="37"/>
       <c r="I6" s="36"/>
@@ -20791,7 +21191,7 @@
       <c r="AT6" s="39"/>
       <c r="AU6" s="37"/>
       <c r="AV6" s="39" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="AW6" s="37"/>
       <c r="AX6" s="37"/>
@@ -20801,19 +21201,19 @@
         <v>284</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C7" s="34" t="s">
+        <v>304</v>
+      </c>
+      <c r="D7" s="34" t="s">
+        <v>305</v>
+      </c>
+      <c r="E7" s="40" t="s">
         <v>306</v>
       </c>
-      <c r="D7" s="34" t="s">
+      <c r="F7" s="36" t="s">
         <v>307</v>
-      </c>
-      <c r="E7" s="40" t="s">
-        <v>308</v>
-      </c>
-      <c r="F7" s="36" t="s">
-        <v>309</v>
       </c>
       <c r="G7" s="37"/>
       <c r="H7" s="41"/>
@@ -20824,31 +21224,31 @@
       <c r="M7" s="37"/>
       <c r="N7" s="37"/>
       <c r="O7" s="37" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="P7" s="37"/>
       <c r="Q7" s="37"/>
       <c r="R7" s="37"/>
       <c r="S7" s="41" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="T7" s="41" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="U7" s="37"/>
       <c r="V7" s="37"/>
       <c r="W7" s="38"/>
       <c r="X7" s="37" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="Y7" s="37"/>
       <c r="Z7" s="37"/>
       <c r="AA7" s="37" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AB7" s="37"/>
       <c r="AC7" s="41" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AD7" s="37"/>
       <c r="AE7" s="37"/>
@@ -20860,7 +21260,7 @@
       <c r="AK7" s="37"/>
       <c r="AL7" s="37"/>
       <c r="AM7" s="37" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AN7" s="37"/>
       <c r="AO7" s="37"/>
@@ -20869,12 +21269,12 @@
       <c r="AR7" s="37"/>
       <c r="AS7" s="37"/>
       <c r="AT7" s="39" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="AU7" s="37"/>
       <c r="AV7" s="39"/>
       <c r="AW7" s="37" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="AX7" s="37"/>
     </row>
@@ -20883,7 +21283,7 @@
         <v>284</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C8" s="34" t="s">
         <v>17</v>
@@ -20893,7 +21293,7 @@
       </c>
       <c r="E8" s="35"/>
       <c r="F8" s="36" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="G8" s="37"/>
       <c r="H8" s="37"/>
@@ -20912,7 +21312,7 @@
       <c r="U8" s="37"/>
       <c r="V8" s="37"/>
       <c r="W8" s="38" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="X8" s="37"/>
       <c r="Y8" s="37"/>
@@ -20922,12 +21322,12 @@
       <c r="AC8" s="37"/>
       <c r="AD8" s="37"/>
       <c r="AE8" s="37" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="AF8" s="37"/>
       <c r="AG8" s="37"/>
       <c r="AH8" s="42" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="AI8" s="37"/>
       <c r="AJ8" s="37"/>
@@ -20951,17 +21351,17 @@
         <v>284</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C9" s="34" t="s">
         <v>21</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E9" s="35"/>
       <c r="F9" s="36" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G9" s="37"/>
       <c r="H9" s="37"/>
@@ -20991,12 +21391,12 @@
       <c r="AF9" s="37"/>
       <c r="AG9" s="37"/>
       <c r="AH9" s="36" t="s">
-        <v>326</v>
-      </c>
-      <c r="AI9" s="37"/>
-      <c r="AJ9" s="37"/>
-      <c r="AK9" s="37"/>
-      <c r="AL9" s="37"/>
+        <v>324</v>
+      </c>
+      <c r="AI9" s="43"/>
+      <c r="AJ9" s="43"/>
+      <c r="AK9" s="43"/>
+      <c r="AL9" s="43"/>
       <c r="AM9" s="37"/>
       <c r="AN9" s="37"/>
       <c r="AO9" s="37"/>
@@ -21015,19 +21415,19 @@
         <v>284</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C10" s="34" t="s">
+        <v>325</v>
+      </c>
+      <c r="D10" s="34" t="s">
+        <v>326</v>
+      </c>
+      <c r="E10" s="40" t="s">
         <v>327</v>
       </c>
-      <c r="D10" s="34" t="s">
+      <c r="F10" s="36" t="s">
         <v>328</v>
-      </c>
-      <c r="E10" s="40" t="s">
-        <v>329</v>
-      </c>
-      <c r="F10" s="36" t="s">
-        <v>330</v>
       </c>
       <c r="G10" s="37"/>
       <c r="H10" s="37"/>
@@ -21038,48 +21438,48 @@
       <c r="M10" s="37"/>
       <c r="N10" s="37"/>
       <c r="O10" s="37" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="P10" s="37"/>
       <c r="Q10" s="37"/>
       <c r="R10" s="37"/>
       <c r="S10" s="37"/>
       <c r="T10" s="37" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="U10" s="37"/>
       <c r="V10" s="37"/>
       <c r="W10" s="37"/>
       <c r="X10" s="37" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="Y10" s="37"/>
       <c r="Z10" s="37" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AA10" s="37"/>
       <c r="AB10" s="37"/>
       <c r="AC10" s="41" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="AD10" s="37"/>
       <c r="AE10" s="37"/>
       <c r="AF10" s="37" t="s">
+        <v>334</v>
+      </c>
+      <c r="AG10" s="37" t="s">
+        <v>335</v>
+      </c>
+      <c r="AH10" s="44"/>
+      <c r="AI10" s="37" t="s">
         <v>336</v>
-      </c>
-      <c r="AG10" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="AH10" s="43"/>
-      <c r="AI10" s="37" t="s">
-        <v>338</v>
       </c>
       <c r="AJ10" s="37"/>
       <c r="AK10" s="37"/>
       <c r="AL10" s="37"/>
       <c r="AM10" s="37"/>
       <c r="AN10" s="37" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="AO10" s="37"/>
       <c r="AP10" s="37"/>
@@ -21097,16 +21497,16 @@
         <v>284</v>
       </c>
       <c r="B11" s="34" t="s">
+        <v>338</v>
+      </c>
+      <c r="C11" s="34" t="s">
+        <v>338</v>
+      </c>
+      <c r="D11" s="34" t="s">
+        <v>339</v>
+      </c>
+      <c r="E11" s="40" t="s">
         <v>340</v>
-      </c>
-      <c r="C11" s="34" t="s">
-        <v>340</v>
-      </c>
-      <c r="D11" s="34" t="s">
-        <v>341</v>
-      </c>
-      <c r="E11" s="40" t="s">
-        <v>342</v>
       </c>
       <c r="F11" s="36"/>
       <c r="G11" s="37"/>
@@ -21123,34 +21523,34 @@
       <c r="R11" s="37"/>
       <c r="S11" s="37"/>
       <c r="T11" s="37" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="U11" s="37"/>
       <c r="V11" s="37"/>
       <c r="W11" s="37"/>
       <c r="X11" s="37" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="Y11" s="37"/>
       <c r="Z11" s="37" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AA11" s="37"/>
       <c r="AB11" s="37"/>
       <c r="AC11" s="37"/>
-      <c r="AD11" s="44" t="s">
-        <v>346</v>
+      <c r="AD11" s="45" t="s">
+        <v>344</v>
       </c>
       <c r="AE11" s="37" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AF11" s="37"/>
       <c r="AG11" s="37"/>
       <c r="AH11" s="36" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AI11" s="37" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AJ11" s="37"/>
       <c r="AK11" s="37"/>
@@ -21169,543 +21569,543 @@
       <c r="AX11" s="37"/>
     </row>
     <row r="12">
-      <c r="A12" s="45" t="s">
+      <c r="A12" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="B12" s="45" t="s">
+      <c r="B12" s="46" t="s">
+        <v>348</v>
+      </c>
+      <c r="C12" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" s="46" t="s">
+        <v>349</v>
+      </c>
+      <c r="E12" s="35" t="s">
         <v>350</v>
       </c>
-      <c r="C12" s="45" t="s">
-        <v>72</v>
-      </c>
-      <c r="D12" s="45" t="s">
+      <c r="F12" s="36" t="s">
         <v>351</v>
       </c>
-      <c r="E12" s="35" t="s">
+      <c r="G12" s="37" t="s">
         <v>352</v>
       </c>
-      <c r="F12" s="36" t="s">
+      <c r="H12" s="37" t="s">
         <v>353</v>
-      </c>
-      <c r="G12" s="37" t="s">
-        <v>354</v>
-      </c>
-      <c r="H12" s="37" t="s">
-        <v>355</v>
       </c>
       <c r="I12" s="37"/>
       <c r="J12" s="37"/>
       <c r="K12" s="37"/>
       <c r="L12" s="37" t="s">
+        <v>354</v>
+      </c>
+      <c r="M12" s="37"/>
+      <c r="N12" s="47" t="s">
+        <v>355</v>
+      </c>
+      <c r="O12" s="38" t="s">
         <v>356</v>
       </c>
-      <c r="M12" s="37"/>
-      <c r="N12" s="46" t="s">
+      <c r="P12" s="41" t="s">
         <v>357</v>
       </c>
-      <c r="O12" s="38" t="s">
+      <c r="Q12" s="37" t="s">
         <v>358</v>
       </c>
-      <c r="P12" s="41" t="s">
+      <c r="R12" s="48" t="s">
         <v>359</v>
-      </c>
-      <c r="Q12" s="37" t="s">
-        <v>360</v>
-      </c>
-      <c r="R12" s="47" t="s">
-        <v>361</v>
       </c>
       <c r="S12" s="37"/>
       <c r="T12" s="37" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="U12" s="37"/>
       <c r="V12" s="37" t="s">
+        <v>361</v>
+      </c>
+      <c r="W12" s="49" t="s">
+        <v>362</v>
+      </c>
+      <c r="X12" s="37" t="s">
         <v>363</v>
       </c>
-      <c r="W12" s="48" t="s">
+      <c r="Y12" s="37" t="s">
         <v>364</v>
       </c>
-      <c r="X12" s="37" t="s">
+      <c r="Z12" s="37" t="s">
         <v>365</v>
-      </c>
-      <c r="Y12" s="37" t="s">
-        <v>366</v>
-      </c>
-      <c r="Z12" s="37" t="s">
-        <v>367</v>
       </c>
       <c r="AA12" s="37"/>
       <c r="AB12" s="37"/>
       <c r="AC12" s="37" t="s">
+        <v>366</v>
+      </c>
+      <c r="AD12" s="45" t="s">
+        <v>367</v>
+      </c>
+      <c r="AE12" s="37" t="s">
         <v>368</v>
-      </c>
-      <c r="AD12" s="44" t="s">
-        <v>369</v>
-      </c>
-      <c r="AE12" s="37" t="s">
-        <v>370</v>
       </c>
       <c r="AF12" s="37"/>
       <c r="AG12" s="37"/>
       <c r="AH12" s="36" t="s">
+        <v>369</v>
+      </c>
+      <c r="AI12" s="37" t="s">
+        <v>370</v>
+      </c>
+      <c r="AJ12" s="37" t="s">
         <v>371</v>
-      </c>
-      <c r="AI12" s="37" t="s">
-        <v>372</v>
-      </c>
-      <c r="AJ12" s="37" t="s">
-        <v>373</v>
       </c>
       <c r="AK12" s="37"/>
       <c r="AL12" s="37" t="s">
+        <v>372</v>
+      </c>
+      <c r="AM12" s="37" t="s">
+        <v>373</v>
+      </c>
+      <c r="AN12" s="37" t="s">
         <v>374</v>
-      </c>
-      <c r="AM12" s="37" t="s">
-        <v>375</v>
-      </c>
-      <c r="AN12" s="37" t="s">
-        <v>376</v>
       </c>
       <c r="AO12" s="37"/>
       <c r="AP12" s="37" t="s">
+        <v>375</v>
+      </c>
+      <c r="AQ12" s="37" t="s">
+        <v>376</v>
+      </c>
+      <c r="AR12" s="37" t="s">
         <v>377</v>
-      </c>
-      <c r="AQ12" s="37" t="s">
-        <v>378</v>
-      </c>
-      <c r="AR12" s="37" t="s">
-        <v>379</v>
       </c>
       <c r="AS12" s="37"/>
       <c r="AT12" s="39" t="s">
+        <v>378</v>
+      </c>
+      <c r="AU12" s="50" t="s">
+        <v>379</v>
+      </c>
+      <c r="AV12" s="39" t="s">
         <v>380</v>
-      </c>
-      <c r="AU12" s="49" t="s">
-        <v>381</v>
-      </c>
-      <c r="AV12" s="39" t="s">
-        <v>382</v>
       </c>
       <c r="AW12" s="37"/>
       <c r="AX12" s="37"/>
     </row>
     <row r="13">
-      <c r="A13" s="45" t="s">
+      <c r="A13" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="B13" s="45" t="s">
-        <v>350</v>
-      </c>
-      <c r="C13" s="45" t="s">
+      <c r="B13" s="46" t="s">
+        <v>348</v>
+      </c>
+      <c r="C13" s="46" t="s">
         <v>132</v>
       </c>
-      <c r="D13" s="45" t="s">
+      <c r="D13" s="46" t="s">
+        <v>381</v>
+      </c>
+      <c r="E13" s="40" t="s">
+        <v>382</v>
+      </c>
+      <c r="F13" s="36" t="s">
         <v>383</v>
-      </c>
-      <c r="E13" s="40" t="s">
-        <v>384</v>
-      </c>
-      <c r="F13" s="36" t="s">
-        <v>385</v>
       </c>
       <c r="G13" s="37"/>
       <c r="H13" s="37" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="I13" s="36"/>
       <c r="J13" s="37"/>
       <c r="K13" s="37"/>
       <c r="L13" s="37" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="M13" s="37"/>
-      <c r="N13" s="46"/>
+      <c r="N13" s="47"/>
       <c r="O13" s="37"/>
       <c r="P13" s="38" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="Q13" s="37" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="R13" s="37"/>
       <c r="S13" s="37" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="T13" s="37"/>
       <c r="U13" s="37" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="V13" s="37"/>
       <c r="W13" s="38"/>
-      <c r="X13" s="50" t="s">
-        <v>392</v>
+      <c r="X13" s="51" t="s">
+        <v>390</v>
       </c>
       <c r="Y13" s="37"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="37"/>
       <c r="AB13" s="37"/>
       <c r="AC13" s="41" t="s">
+        <v>391</v>
+      </c>
+      <c r="AD13" s="45" t="s">
+        <v>392</v>
+      </c>
+      <c r="AE13" s="37" t="s">
         <v>393</v>
       </c>
-      <c r="AD13" s="44" t="s">
+      <c r="AF13" s="37" t="s">
         <v>394</v>
       </c>
-      <c r="AE13" s="37" t="s">
+      <c r="AG13" s="37" t="s">
         <v>395</v>
       </c>
-      <c r="AF13" s="37" t="s">
+      <c r="AH13" s="36" t="s">
         <v>396</v>
       </c>
-      <c r="AG13" s="37" t="s">
+      <c r="AI13" s="37" t="s">
         <v>397</v>
       </c>
-      <c r="AH13" s="36" t="s">
+      <c r="AJ13" s="37" t="s">
         <v>398</v>
       </c>
-      <c r="AI13" s="37" t="s">
+      <c r="AK13" s="37" t="s">
         <v>399</v>
       </c>
-      <c r="AJ13" s="37" t="s">
+      <c r="AL13" s="37" t="s">
         <v>400</v>
       </c>
-      <c r="AK13" s="37" t="s">
+      <c r="AM13" s="37" t="s">
         <v>401</v>
-      </c>
-      <c r="AL13" s="37" t="s">
-        <v>402</v>
-      </c>
-      <c r="AM13" s="37" t="s">
-        <v>403</v>
       </c>
       <c r="AN13" s="37"/>
       <c r="AO13" s="37"/>
       <c r="AP13" s="37" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AQ13" s="37" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="AR13" s="37"/>
       <c r="AS13" s="37"/>
       <c r="AT13" s="39" t="s">
+        <v>404</v>
+      </c>
+      <c r="AU13" s="52" t="s">
+        <v>405</v>
+      </c>
+      <c r="AV13" s="39" t="s">
         <v>406</v>
       </c>
-      <c r="AU13" s="51" t="s">
+      <c r="AW13" s="37" t="s">
         <v>407</v>
       </c>
-      <c r="AV13" s="39" t="s">
+      <c r="AX13" s="37"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="46" t="s">
+        <v>348</v>
+      </c>
+      <c r="C14" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="35" t="s">
         <v>408</v>
       </c>
-      <c r="AW13" s="37" t="s">
+      <c r="F14" s="36" t="s">
         <v>409</v>
       </c>
-      <c r="AX13" s="37"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="45" t="s">
-        <v>54</v>
-      </c>
-      <c r="B14" s="45" t="s">
-        <v>350</v>
-      </c>
-      <c r="C14" s="45" t="s">
-        <v>57</v>
-      </c>
-      <c r="D14" s="45" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14" s="35" t="s">
+      <c r="G14" s="37" t="s">
         <v>410</v>
       </c>
-      <c r="F14" s="36" t="s">
+      <c r="H14" s="37" t="s">
         <v>411</v>
       </c>
-      <c r="G14" s="37" t="s">
+      <c r="I14" s="37" t="s">
         <v>412</v>
       </c>
-      <c r="H14" s="37" t="s">
+      <c r="J14" s="37" t="s">
         <v>413</v>
-      </c>
-      <c r="I14" s="37" t="s">
-        <v>414</v>
-      </c>
-      <c r="J14" s="37" t="s">
-        <v>415</v>
       </c>
       <c r="K14" s="37"/>
       <c r="L14" s="41" t="s">
+        <v>414</v>
+      </c>
+      <c r="M14" s="37" t="s">
+        <v>415</v>
+      </c>
+      <c r="N14" s="47" t="s">
         <v>416</v>
-      </c>
-      <c r="M14" s="37" t="s">
-        <v>417</v>
-      </c>
-      <c r="N14" s="46" t="s">
-        <v>418</v>
       </c>
       <c r="O14" s="37"/>
       <c r="P14" s="37" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="Q14" s="37"/>
-      <c r="R14" s="47"/>
+      <c r="R14" s="48"/>
       <c r="S14" s="37" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="T14" s="37"/>
       <c r="U14" s="37"/>
       <c r="V14" s="37" t="s">
+        <v>419</v>
+      </c>
+      <c r="W14" s="49"/>
+      <c r="X14" s="37" t="s">
+        <v>420</v>
+      </c>
+      <c r="Y14" s="37" t="s">
         <v>421</v>
-      </c>
-      <c r="W14" s="48"/>
-      <c r="X14" s="37" t="s">
-        <v>422</v>
-      </c>
-      <c r="Y14" s="37" t="s">
-        <v>423</v>
       </c>
       <c r="Z14" s="37"/>
       <c r="AA14" s="37" t="s">
+        <v>422</v>
+      </c>
+      <c r="AB14" s="37" t="s">
+        <v>423</v>
+      </c>
+      <c r="AC14" s="37" t="s">
         <v>424</v>
       </c>
-      <c r="AB14" s="37" t="s">
+      <c r="AD14" s="45" t="s">
         <v>425</v>
       </c>
-      <c r="AC14" s="37" t="s">
+      <c r="AE14" s="37" t="s">
         <v>426</v>
-      </c>
-      <c r="AD14" s="44" t="s">
-        <v>427</v>
-      </c>
-      <c r="AE14" s="37" t="s">
-        <v>428</v>
       </c>
       <c r="AF14" s="37"/>
       <c r="AG14" s="41" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="AH14" s="36" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="AI14" s="37"/>
       <c r="AJ14" s="37" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="AK14" s="37"/>
       <c r="AL14" s="37" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="AM14" s="37" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AN14" s="37"/>
       <c r="AO14" s="37"/>
       <c r="AP14" s="37" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AQ14" s="37" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="AR14" s="37"/>
       <c r="AS14" s="37"/>
       <c r="AT14" s="39"/>
-      <c r="AU14" s="52" t="s">
+      <c r="AU14" s="53" t="s">
+        <v>434</v>
+      </c>
+      <c r="AV14" s="39" t="s">
+        <v>435</v>
+      </c>
+      <c r="AW14" s="37" t="s">
         <v>436</v>
       </c>
-      <c r="AV14" s="39" t="s">
+      <c r="AX14" s="37"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="46" t="s">
+        <v>348</v>
+      </c>
+      <c r="C15" s="46" t="s">
+        <v>87</v>
+      </c>
+      <c r="D15" s="46" t="s">
         <v>437</v>
       </c>
-      <c r="AW14" s="37" t="s">
+      <c r="E15" s="35" t="s">
         <v>438</v>
       </c>
-      <c r="AX14" s="37"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="45" t="s">
-        <v>54</v>
-      </c>
-      <c r="B15" s="45" t="s">
-        <v>350</v>
-      </c>
-      <c r="C15" s="45" t="s">
-        <v>87</v>
-      </c>
-      <c r="D15" s="45" t="s">
+      <c r="F15" s="36" t="s">
         <v>439</v>
-      </c>
-      <c r="E15" s="35" t="s">
-        <v>440</v>
-      </c>
-      <c r="F15" s="36" t="s">
-        <v>441</v>
       </c>
       <c r="G15" s="37"/>
       <c r="H15" s="37" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="I15" s="37"/>
       <c r="J15" s="37" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="K15" s="37"/>
       <c r="L15" s="37" t="s">
+        <v>442</v>
+      </c>
+      <c r="M15" s="41" t="s">
+        <v>443</v>
+      </c>
+      <c r="N15" s="47" t="s">
         <v>444</v>
       </c>
-      <c r="M15" s="41" t="s">
+      <c r="O15" s="45" t="s">
         <v>445</v>
       </c>
-      <c r="N15" s="46" t="s">
+      <c r="P15" s="37" t="s">
         <v>446</v>
       </c>
-      <c r="O15" s="44" t="s">
+      <c r="Q15" s="37"/>
+      <c r="R15" s="54" t="s">
         <v>447</v>
       </c>
-      <c r="P15" s="37" t="s">
+      <c r="S15" s="37" t="s">
         <v>448</v>
-      </c>
-      <c r="Q15" s="37"/>
-      <c r="R15" s="53" t="s">
-        <v>449</v>
-      </c>
-      <c r="S15" s="37" t="s">
-        <v>450</v>
       </c>
       <c r="T15" s="37"/>
       <c r="U15" s="37" t="s">
+        <v>449</v>
+      </c>
+      <c r="V15" s="37" t="s">
+        <v>450</v>
+      </c>
+      <c r="W15" s="41" t="s">
         <v>451</v>
       </c>
-      <c r="V15" s="37" t="s">
+      <c r="X15" s="51" t="s">
         <v>452</v>
-      </c>
-      <c r="W15" s="41" t="s">
-        <v>453</v>
-      </c>
-      <c r="X15" s="50" t="s">
-        <v>454</v>
       </c>
       <c r="Y15" s="37"/>
       <c r="Z15" s="37"/>
       <c r="AA15" s="37" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AB15" s="37"/>
       <c r="AC15" s="37" t="s">
-        <v>456</v>
-      </c>
-      <c r="AD15" s="44" t="s">
-        <v>457</v>
+        <v>454</v>
+      </c>
+      <c r="AD15" s="45" t="s">
+        <v>455</v>
       </c>
       <c r="AE15" s="37"/>
       <c r="AF15" s="37" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AG15" s="37"/>
       <c r="AH15" s="36" t="s">
+        <v>457</v>
+      </c>
+      <c r="AI15" s="37" t="s">
+        <v>458</v>
+      </c>
+      <c r="AJ15" s="37" t="s">
         <v>459</v>
       </c>
-      <c r="AI15" s="37" t="s">
+      <c r="AK15" s="37" t="s">
         <v>460</v>
       </c>
-      <c r="AJ15" s="37" t="s">
+      <c r="AL15" s="37" t="s">
         <v>461</v>
       </c>
-      <c r="AK15" s="37" t="s">
+      <c r="AM15" s="37" t="s">
         <v>462</v>
-      </c>
-      <c r="AL15" s="37" t="s">
-        <v>463</v>
-      </c>
-      <c r="AM15" s="37" t="s">
-        <v>464</v>
       </c>
       <c r="AN15" s="37"/>
       <c r="AO15" s="37"/>
       <c r="AP15" s="37" t="s">
+        <v>463</v>
+      </c>
+      <c r="AQ15" s="37" t="s">
+        <v>464</v>
+      </c>
+      <c r="AR15" s="37" t="s">
         <v>465</v>
-      </c>
-      <c r="AQ15" s="37" t="s">
-        <v>466</v>
-      </c>
-      <c r="AR15" s="37" t="s">
-        <v>467</v>
       </c>
       <c r="AS15" s="37"/>
       <c r="AT15" s="39"/>
-      <c r="AU15" s="49" t="s">
-        <v>468</v>
+      <c r="AU15" s="50" t="s">
+        <v>466</v>
       </c>
       <c r="AV15" s="39" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="AW15" s="37"/>
       <c r="AX15" s="37"/>
     </row>
     <row r="16">
-      <c r="A16" s="45" t="s">
+      <c r="A16" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="B16" s="45" t="s">
-        <v>350</v>
-      </c>
-      <c r="C16" s="45" t="s">
+      <c r="B16" s="46" t="s">
+        <v>348</v>
+      </c>
+      <c r="C16" s="46" t="s">
+        <v>468</v>
+      </c>
+      <c r="D16" s="46" t="s">
+        <v>469</v>
+      </c>
+      <c r="E16" s="35" t="s">
         <v>470</v>
       </c>
-      <c r="D16" s="45" t="s">
+      <c r="F16" s="36" t="s">
         <v>471</v>
-      </c>
-      <c r="E16" s="35" t="s">
-        <v>472</v>
-      </c>
-      <c r="F16" s="36" t="s">
-        <v>473</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="I16" s="37"/>
       <c r="J16" s="37" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="K16" s="37"/>
       <c r="L16" s="37"/>
       <c r="M16" s="37"/>
-      <c r="N16" s="44"/>
+      <c r="N16" s="45"/>
       <c r="O16" s="37"/>
       <c r="P16" s="41" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="Q16" s="37"/>
       <c r="R16" s="37"/>
       <c r="S16" s="37" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="T16" s="37"/>
       <c r="U16" s="37" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="V16" s="37"/>
       <c r="W16" s="38"/>
       <c r="X16" s="37" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="Y16" s="37"/>
       <c r="Z16" s="37"/>
       <c r="AA16" s="41" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="AB16" s="37"/>
       <c r="AC16" s="37"/>
-      <c r="AD16" s="44"/>
+      <c r="AD16" s="45"/>
       <c r="AE16" s="37" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="AF16" s="37" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="AG16" s="37"/>
       <c r="AH16" s="36" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="AI16" s="37"/>
       <c r="AJ16" s="37"/>
@@ -21715,101 +22115,101 @@
       <c r="AN16" s="37"/>
       <c r="AO16" s="37"/>
       <c r="AP16" s="37" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="AQ16" s="37" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="AR16" s="37"/>
       <c r="AS16" s="37"/>
       <c r="AT16" s="39" t="s">
+        <v>484</v>
+      </c>
+      <c r="AU16" s="53" t="s">
+        <v>485</v>
+      </c>
+      <c r="AV16" s="39" t="s">
         <v>486</v>
       </c>
-      <c r="AU16" s="52" t="s">
+      <c r="AW16" s="37" t="s">
         <v>487</v>
       </c>
-      <c r="AV16" s="39" t="s">
+      <c r="AX16" s="37"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" s="46" t="s">
+        <v>348</v>
+      </c>
+      <c r="C17" s="46" t="s">
         <v>488</v>
       </c>
-      <c r="AW16" s="37" t="s">
+      <c r="D17" s="46" t="s">
         <v>489</v>
-      </c>
-      <c r="AX16" s="37"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="45" t="s">
-        <v>54</v>
-      </c>
-      <c r="B17" s="45" t="s">
-        <v>350</v>
-      </c>
-      <c r="C17" s="45" t="s">
-        <v>490</v>
-      </c>
-      <c r="D17" s="45" t="s">
-        <v>491</v>
       </c>
       <c r="E17" s="35"/>
       <c r="F17" s="36" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="I17" s="37"/>
       <c r="J17" s="37" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="K17" s="37"/>
       <c r="L17" s="37"/>
       <c r="M17" s="37"/>
-      <c r="N17" s="46" t="s">
+      <c r="N17" s="47" t="s">
+        <v>493</v>
+      </c>
+      <c r="O17" s="38" t="s">
+        <v>494</v>
+      </c>
+      <c r="P17" s="41" t="s">
         <v>495</v>
-      </c>
-      <c r="O17" s="38" t="s">
-        <v>496</v>
-      </c>
-      <c r="P17" s="41" t="s">
-        <v>497</v>
       </c>
       <c r="Q17" s="37"/>
       <c r="R17" s="37"/>
       <c r="S17" s="37" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="T17" s="37"/>
       <c r="U17" s="37"/>
       <c r="V17" s="37"/>
-      <c r="W17" s="48" t="s">
+      <c r="W17" s="49" t="s">
+        <v>497</v>
+      </c>
+      <c r="X17" s="37" t="s">
+        <v>498</v>
+      </c>
+      <c r="Y17" s="37" t="s">
         <v>499</v>
-      </c>
-      <c r="X17" s="37" t="s">
-        <v>500</v>
-      </c>
-      <c r="Y17" s="37" t="s">
-        <v>501</v>
       </c>
       <c r="Z17" s="37"/>
       <c r="AA17" s="37"/>
       <c r="AB17" s="37" t="s">
+        <v>500</v>
+      </c>
+      <c r="AC17" s="37" t="s">
+        <v>501</v>
+      </c>
+      <c r="AD17" s="45"/>
+      <c r="AE17" s="37" t="s">
         <v>502</v>
       </c>
-      <c r="AC17" s="37" t="s">
+      <c r="AF17" s="37" t="s">
         <v>503</v>
       </c>
-      <c r="AD17" s="44"/>
-      <c r="AE17" s="37" t="s">
+      <c r="AG17" s="41" t="s">
         <v>504</v>
       </c>
-      <c r="AF17" s="37" t="s">
+      <c r="AH17" s="36" t="s">
         <v>505</v>
-      </c>
-      <c r="AG17" s="41" t="s">
-        <v>506</v>
-      </c>
-      <c r="AH17" s="36" t="s">
-        <v>507</v>
       </c>
       <c r="AI17" s="37"/>
       <c r="AJ17" s="37"/>
@@ -21819,169 +22219,169 @@
       <c r="AN17" s="37"/>
       <c r="AO17" s="37"/>
       <c r="AP17" s="37" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="AQ17" s="37" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="AR17" s="37"/>
       <c r="AS17" s="37"/>
       <c r="AT17" s="39" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="AU17" s="37"/>
       <c r="AV17" s="39" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="AW17" s="37"/>
       <c r="AX17" s="37"/>
     </row>
     <row r="18">
-      <c r="A18" s="45" t="s">
+      <c r="A18" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="B18" s="45" t="s">
-        <v>350</v>
-      </c>
-      <c r="C18" s="45" t="s">
+      <c r="B18" s="46" t="s">
+        <v>348</v>
+      </c>
+      <c r="C18" s="46" t="s">
+        <v>510</v>
+      </c>
+      <c r="D18" s="46" t="s">
+        <v>511</v>
+      </c>
+      <c r="E18" s="40" t="s">
         <v>512</v>
       </c>
-      <c r="D18" s="45" t="s">
+      <c r="F18" s="36" t="s">
         <v>513</v>
       </c>
-      <c r="E18" s="40" t="s">
+      <c r="G18" s="37"/>
+      <c r="H18" s="45" t="s">
         <v>514</v>
       </c>
-      <c r="F18" s="36" t="s">
+      <c r="I18" s="37" t="s">
         <v>515</v>
       </c>
-      <c r="G18" s="37"/>
-      <c r="H18" s="44" t="s">
+      <c r="J18" s="37" t="s">
         <v>516</v>
-      </c>
-      <c r="I18" s="37" t="s">
-        <v>517</v>
-      </c>
-      <c r="J18" s="37" t="s">
-        <v>518</v>
       </c>
       <c r="K18" s="37"/>
       <c r="L18" s="37" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="M18" s="37"/>
-      <c r="N18" s="44"/>
+      <c r="N18" s="45"/>
       <c r="O18" s="37"/>
       <c r="P18" s="37"/>
       <c r="Q18" s="37"/>
-      <c r="R18" s="47" t="s">
-        <v>520</v>
+      <c r="R18" s="48" t="s">
+        <v>518</v>
       </c>
       <c r="S18" s="37" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="T18" s="37"/>
       <c r="U18" s="37"/>
       <c r="V18" s="37"/>
-      <c r="W18" s="48" t="s">
-        <v>522</v>
+      <c r="W18" s="49" t="s">
+        <v>520</v>
       </c>
       <c r="X18" s="37"/>
       <c r="Y18" s="37" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="Z18" s="37"/>
       <c r="AA18" s="37"/>
       <c r="AB18" s="37" t="s">
+        <v>522</v>
+      </c>
+      <c r="AC18" s="37"/>
+      <c r="AD18" s="45" t="s">
+        <v>523</v>
+      </c>
+      <c r="AE18" s="37" t="s">
         <v>524</v>
       </c>
-      <c r="AC18" s="37"/>
-      <c r="AD18" s="44" t="s">
+      <c r="AF18" s="37" t="s">
         <v>525</v>
       </c>
-      <c r="AE18" s="37" t="s">
+      <c r="AG18" s="41" t="s">
         <v>526</v>
       </c>
-      <c r="AF18" s="37" t="s">
+      <c r="AH18" s="36" t="s">
         <v>527</v>
-      </c>
-      <c r="AG18" s="41" t="s">
-        <v>528</v>
-      </c>
-      <c r="AH18" s="36" t="s">
-        <v>529</v>
       </c>
       <c r="AI18" s="37"/>
       <c r="AJ18" s="37"/>
       <c r="AK18" s="37" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="AL18" s="37"/>
       <c r="AM18" s="37"/>
       <c r="AN18" s="37"/>
       <c r="AO18" s="37"/>
       <c r="AP18" s="37" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="AQ18" s="37" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="AR18" s="37"/>
       <c r="AS18" s="37"/>
       <c r="AT18" s="39" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="AU18" s="37"/>
       <c r="AV18" s="39"/>
       <c r="AW18" s="37" t="s">
+        <v>532</v>
+      </c>
+      <c r="AX18" s="37"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="46" t="s">
+        <v>348</v>
+      </c>
+      <c r="C19" s="46" t="s">
+        <v>533</v>
+      </c>
+      <c r="D19" s="46" t="s">
         <v>534</v>
       </c>
-      <c r="AX18" s="37"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="45" t="s">
-        <v>54</v>
-      </c>
-      <c r="B19" s="45" t="s">
-        <v>350</v>
-      </c>
-      <c r="C19" s="45" t="s">
+      <c r="E19" s="40" t="s">
         <v>535</v>
       </c>
-      <c r="D19" s="45" t="s">
+      <c r="F19" s="36" t="s">
         <v>536</v>
       </c>
-      <c r="E19" s="40" t="s">
+      <c r="G19" s="37"/>
+      <c r="H19" s="45" t="s">
         <v>537</v>
-      </c>
-      <c r="F19" s="36" t="s">
-        <v>538</v>
-      </c>
-      <c r="G19" s="37"/>
-      <c r="H19" s="44" t="s">
-        <v>539</v>
       </c>
       <c r="I19" s="37"/>
       <c r="J19" s="37"/>
       <c r="K19" s="37" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="L19" s="37"/>
       <c r="M19" s="37"/>
-      <c r="N19" s="46" t="s">
-        <v>541</v>
+      <c r="N19" s="47" t="s">
+        <v>539</v>
       </c>
       <c r="O19" s="37"/>
       <c r="P19" s="41" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="Q19" s="37"/>
-      <c r="R19" s="54" t="s">
-        <v>543</v>
+      <c r="R19" s="55" t="s">
+        <v>541</v>
       </c>
       <c r="S19" s="37"/>
       <c r="T19" s="37" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="U19" s="37"/>
       <c r="V19" s="37"/>
@@ -21991,155 +22391,155 @@
       <c r="Z19" s="37"/>
       <c r="AA19" s="37"/>
       <c r="AB19" s="41" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="AC19" s="37" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="AD19" s="37"/>
       <c r="AE19" s="37" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="AF19" s="37"/>
       <c r="AG19" s="37"/>
       <c r="AH19" s="36" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="AI19" s="37" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="AJ19" s="37"/>
       <c r="AK19" s="37" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="AL19" s="37" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="AM19" s="37"/>
       <c r="AN19" s="37" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="AO19" s="37"/>
       <c r="AP19" s="37" t="s">
+        <v>551</v>
+      </c>
+      <c r="AQ19" s="37" t="s">
+        <v>552</v>
+      </c>
+      <c r="AR19" s="37" t="s">
         <v>553</v>
-      </c>
-      <c r="AQ19" s="37" t="s">
-        <v>554</v>
-      </c>
-      <c r="AR19" s="37" t="s">
-        <v>555</v>
       </c>
       <c r="AS19" s="37"/>
       <c r="AT19" s="39" t="s">
+        <v>554</v>
+      </c>
+      <c r="AU19" s="53" t="s">
+        <v>555</v>
+      </c>
+      <c r="AV19" s="39" t="s">
         <v>556</v>
       </c>
-      <c r="AU19" s="52" t="s">
+      <c r="AW19" s="37" t="s">
         <v>557</v>
       </c>
-      <c r="AV19" s="39" t="s">
+      <c r="AX19" s="37"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" s="46" t="s">
         <v>558</v>
       </c>
-      <c r="AW19" s="37" t="s">
+      <c r="C20" s="46" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" s="46" t="s">
         <v>559</v>
       </c>
-      <c r="AX19" s="37"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="45" t="s">
-        <v>54</v>
-      </c>
-      <c r="B20" s="45" t="s">
+      <c r="E20" s="35" t="s">
         <v>560</v>
       </c>
-      <c r="C20" s="45" t="s">
-        <v>61</v>
-      </c>
-      <c r="D20" s="45" t="s">
+      <c r="F20" s="36" t="s">
         <v>561</v>
-      </c>
-      <c r="E20" s="35" t="s">
-        <v>562</v>
-      </c>
-      <c r="F20" s="36" t="s">
-        <v>563</v>
       </c>
       <c r="G20" s="37"/>
       <c r="H20" s="37"/>
       <c r="I20" s="37"/>
       <c r="J20" s="37" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="K20" s="37"/>
       <c r="L20" s="37"/>
       <c r="M20" s="37" t="s">
-        <v>565</v>
-      </c>
-      <c r="N20" s="46" t="s">
-        <v>566</v>
+        <v>563</v>
+      </c>
+      <c r="N20" s="47" t="s">
+        <v>564</v>
       </c>
       <c r="O20" s="37"/>
       <c r="P20" s="41" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="Q20" s="37"/>
-      <c r="R20" s="54" t="s">
-        <v>568</v>
+      <c r="R20" s="55" t="s">
+        <v>566</v>
       </c>
       <c r="S20" s="37"/>
       <c r="T20" s="37"/>
       <c r="U20" s="37"/>
       <c r="V20" s="37"/>
       <c r="W20" s="41" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="X20" s="37" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="Y20" s="37"/>
       <c r="Z20" s="41" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="AA20" s="37"/>
       <c r="AB20" s="37"/>
       <c r="AC20" s="37" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="AD20" s="37"/>
       <c r="AE20" s="37" t="s">
+        <v>571</v>
+      </c>
+      <c r="AF20" s="37" t="s">
+        <v>572</v>
+      </c>
+      <c r="AG20" s="41" t="s">
         <v>573</v>
       </c>
-      <c r="AF20" s="37" t="s">
+      <c r="AH20" s="36" t="s">
         <v>574</v>
       </c>
-      <c r="AG20" s="41" t="s">
+      <c r="AI20" s="37" t="s">
         <v>575</v>
       </c>
-      <c r="AH20" s="36" t="s">
-        <v>576</v>
-      </c>
-      <c r="AI20" s="37" t="s">
-        <v>577</v>
-      </c>
-      <c r="AJ20" s="44"/>
+      <c r="AJ20" s="45"/>
       <c r="AK20" s="37"/>
       <c r="AL20" s="37" t="s">
+        <v>576</v>
+      </c>
+      <c r="AM20" s="37" t="s">
+        <v>577</v>
+      </c>
+      <c r="AN20" s="37" t="s">
         <v>578</v>
-      </c>
-      <c r="AM20" s="37" t="s">
-        <v>579</v>
-      </c>
-      <c r="AN20" s="37" t="s">
-        <v>580</v>
       </c>
       <c r="AO20" s="37"/>
       <c r="AP20" s="37" t="s">
+        <v>579</v>
+      </c>
+      <c r="AQ20" s="37" t="s">
+        <v>580</v>
+      </c>
+      <c r="AR20" s="37" t="s">
         <v>581</v>
-      </c>
-      <c r="AQ20" s="37" t="s">
-        <v>582</v>
-      </c>
-      <c r="AR20" s="37" t="s">
-        <v>583</v>
       </c>
       <c r="AS20" s="37"/>
       <c r="AT20" s="39"/>
@@ -22149,254 +22549,254 @@
       <c r="AX20" s="37"/>
     </row>
     <row r="21">
-      <c r="A21" s="45" t="s">
+      <c r="A21" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="45" t="s">
-        <v>560</v>
-      </c>
-      <c r="C21" s="45" t="s">
+      <c r="B21" s="46" t="s">
+        <v>558</v>
+      </c>
+      <c r="C21" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="D21" s="45" t="s">
-        <v>584</v>
+      <c r="D21" s="46" t="s">
+        <v>582</v>
       </c>
       <c r="E21" s="35"/>
       <c r="F21" s="36" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="G21" s="37"/>
       <c r="H21" s="37"/>
       <c r="I21" s="37"/>
       <c r="J21" s="37" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="K21" s="37"/>
       <c r="L21" s="37"/>
       <c r="M21" s="37"/>
-      <c r="N21" s="46"/>
+      <c r="N21" s="47"/>
       <c r="O21" s="37"/>
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
-      <c r="R21" s="54"/>
+      <c r="R21" s="55"/>
       <c r="S21" s="37"/>
       <c r="T21" s="37" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="U21" s="37"/>
       <c r="V21" s="37"/>
       <c r="W21" s="38" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="X21" s="37" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="Y21" s="37"/>
       <c r="Z21" s="37"/>
       <c r="AA21" s="37"/>
       <c r="AB21" s="37" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="AC21" s="37" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="AD21" s="37"/>
       <c r="AE21" s="37" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="AF21" s="37" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="AG21" s="37"/>
       <c r="AH21" s="36" t="s">
+        <v>592</v>
+      </c>
+      <c r="AI21" s="37" t="s">
+        <v>593</v>
+      </c>
+      <c r="AJ21" s="45" t="s">
         <v>594</v>
-      </c>
-      <c r="AI21" s="37" t="s">
-        <v>595</v>
-      </c>
-      <c r="AJ21" s="44" t="s">
-        <v>596</v>
       </c>
       <c r="AK21" s="37"/>
       <c r="AL21" s="37"/>
       <c r="AM21" s="37" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="AN21" s="37" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="AO21" s="37"/>
       <c r="AP21" s="37" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="AQ21" s="37" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="AR21" s="37"/>
       <c r="AS21" s="37"/>
       <c r="AT21" s="39"/>
-      <c r="AU21" s="52" t="s">
-        <v>601</v>
+      <c r="AU21" s="53" t="s">
+        <v>599</v>
       </c>
       <c r="AV21" s="39" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="AW21" s="37"/>
       <c r="AX21" s="37"/>
     </row>
     <row r="22">
-      <c r="A22" s="45" t="s">
+      <c r="A22" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="B22" s="45" t="s">
-        <v>560</v>
-      </c>
-      <c r="C22" s="45" t="s">
-        <v>603</v>
-      </c>
-      <c r="D22" s="45" t="s">
-        <v>604</v>
+      <c r="B22" s="46" t="s">
+        <v>558</v>
+      </c>
+      <c r="C22" s="46" t="s">
+        <v>601</v>
+      </c>
+      <c r="D22" s="46" t="s">
+        <v>602</v>
       </c>
       <c r="E22" s="35"/>
       <c r="F22" s="36" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="G22" s="37"/>
       <c r="H22" s="37"/>
       <c r="I22" s="37"/>
       <c r="J22" s="37" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="K22" s="37"/>
       <c r="L22" s="37" t="s">
+        <v>605</v>
+      </c>
+      <c r="M22" s="37"/>
+      <c r="N22" s="47" t="s">
+        <v>606</v>
+      </c>
+      <c r="O22" s="37" t="s">
         <v>607</v>
       </c>
-      <c r="M22" s="37"/>
-      <c r="N22" s="46" t="s">
+      <c r="P22" s="41" t="s">
         <v>608</v>
       </c>
-      <c r="O22" s="37" t="s">
+      <c r="Q22" s="41" t="s">
         <v>609</v>
       </c>
-      <c r="P22" s="41" t="s">
+      <c r="R22" s="55" t="s">
         <v>610</v>
-      </c>
-      <c r="Q22" s="41" t="s">
-        <v>611</v>
-      </c>
-      <c r="R22" s="54" t="s">
-        <v>612</v>
       </c>
       <c r="S22" s="37"/>
       <c r="T22" s="37"/>
       <c r="U22" s="37" t="s">
+        <v>611</v>
+      </c>
+      <c r="V22" s="37" t="s">
+        <v>612</v>
+      </c>
+      <c r="W22" s="49" t="s">
         <v>613</v>
-      </c>
-      <c r="V22" s="37" t="s">
-        <v>614</v>
-      </c>
-      <c r="W22" s="48" t="s">
-        <v>615</v>
       </c>
       <c r="X22" s="37"/>
       <c r="Y22" s="41" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="Z22" s="41" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="AA22" s="37"/>
       <c r="AB22" s="41" t="s">
+        <v>616</v>
+      </c>
+      <c r="AC22" s="41" t="s">
+        <v>617</v>
+      </c>
+      <c r="AD22" s="56" t="s">
         <v>618</v>
       </c>
-      <c r="AC22" s="41" t="s">
+      <c r="AE22" s="37" t="s">
         <v>619</v>
       </c>
-      <c r="AD22" s="55" t="s">
+      <c r="AF22" s="37" t="s">
         <v>620</v>
       </c>
-      <c r="AE22" s="37" t="s">
+      <c r="AG22" s="41" t="s">
         <v>621</v>
       </c>
-      <c r="AF22" s="37" t="s">
+      <c r="AH22" s="36" t="s">
         <v>622</v>
       </c>
-      <c r="AG22" s="41" t="s">
+      <c r="AI22" s="37" t="s">
         <v>623</v>
-      </c>
-      <c r="AH22" s="36" t="s">
-        <v>624</v>
-      </c>
-      <c r="AI22" s="37" t="s">
-        <v>625</v>
       </c>
       <c r="AJ22" s="37"/>
       <c r="AK22" s="37" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="AL22" s="37" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="AM22" s="37"/>
       <c r="AN22" s="37"/>
       <c r="AO22" s="37"/>
       <c r="AP22" s="37"/>
       <c r="AQ22" s="37" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="AR22" s="37"/>
       <c r="AS22" s="37"/>
       <c r="AT22" s="39"/>
       <c r="AU22" s="37"/>
       <c r="AV22" s="39" t="s">
+        <v>627</v>
+      </c>
+      <c r="AW22" s="37" t="s">
+        <v>628</v>
+      </c>
+      <c r="AX22" s="37"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" s="46" t="s">
+        <v>558</v>
+      </c>
+      <c r="C23" s="46" t="s">
         <v>629</v>
       </c>
-      <c r="AW22" s="37" t="s">
+      <c r="D23" s="46" t="s">
         <v>630</v>
-      </c>
-      <c r="AX22" s="37"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="45" t="s">
-        <v>54</v>
-      </c>
-      <c r="B23" s="45" t="s">
-        <v>560</v>
-      </c>
-      <c r="C23" s="45" t="s">
-        <v>631</v>
-      </c>
-      <c r="D23" s="45" t="s">
-        <v>632</v>
       </c>
       <c r="E23" s="35"/>
       <c r="F23" s="36" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="G23" s="37"/>
       <c r="H23" s="37"/>
       <c r="I23" s="37"/>
       <c r="J23" s="37" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="K23" s="37"/>
       <c r="L23" s="37" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="M23" s="37"/>
-      <c r="N23" s="44"/>
+      <c r="N23" s="45"/>
       <c r="O23" s="37"/>
       <c r="P23" s="37"/>
       <c r="Q23" s="37"/>
-      <c r="R23" s="54" t="s">
-        <v>636</v>
+      <c r="R23" s="55" t="s">
+        <v>634</v>
       </c>
       <c r="S23" s="37"/>
       <c r="T23" s="37"/>
       <c r="U23" s="37"/>
       <c r="V23" s="37"/>
-      <c r="W23" s="48" t="s">
-        <v>637</v>
+      <c r="W23" s="49" t="s">
+        <v>635</v>
       </c>
       <c r="X23" s="37"/>
       <c r="Y23" s="37"/>
@@ -22404,19 +22804,19 @@
       <c r="AA23" s="37"/>
       <c r="AB23" s="37"/>
       <c r="AC23" s="37"/>
-      <c r="AD23" s="44" t="s">
-        <v>638</v>
+      <c r="AD23" s="45" t="s">
+        <v>636</v>
       </c>
       <c r="AE23" s="37" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="AF23" s="37"/>
       <c r="AG23" s="37"/>
       <c r="AH23" s="36" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="AI23" s="37" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="AJ23" s="37"/>
       <c r="AK23" s="37"/>
@@ -22425,65 +22825,65 @@
       <c r="AN23" s="37"/>
       <c r="AO23" s="37"/>
       <c r="AP23" s="37" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="AQ23" s="37"/>
       <c r="AR23" s="37"/>
       <c r="AS23" s="37"/>
       <c r="AT23" s="39" t="s">
+        <v>641</v>
+      </c>
+      <c r="AU23" s="53" t="s">
+        <v>642</v>
+      </c>
+      <c r="AV23" s="39" t="s">
         <v>643</v>
       </c>
-      <c r="AU23" s="52" t="s">
+      <c r="AW23" s="37" t="s">
         <v>644</v>
       </c>
-      <c r="AV23" s="39" t="s">
+      <c r="AX23" s="37"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="46" t="s">
+        <v>558</v>
+      </c>
+      <c r="C24" s="46" t="s">
         <v>645</v>
       </c>
-      <c r="AW23" s="37" t="s">
+      <c r="D24" s="46" t="s">
         <v>646</v>
-      </c>
-      <c r="AX23" s="37"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="45" t="s">
-        <v>54</v>
-      </c>
-      <c r="B24" s="45" t="s">
-        <v>560</v>
-      </c>
-      <c r="C24" s="45" t="s">
-        <v>647</v>
-      </c>
-      <c r="D24" s="45" t="s">
-        <v>648</v>
       </c>
       <c r="E24" s="35"/>
       <c r="F24" s="36" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="G24" s="37"/>
       <c r="H24" s="37"/>
       <c r="I24" s="37"/>
       <c r="J24" s="37" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="K24" s="37"/>
       <c r="L24" s="37"/>
       <c r="M24" s="37"/>
-      <c r="N24" s="46"/>
+      <c r="N24" s="47"/>
       <c r="O24" s="37" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="P24" s="37"/>
       <c r="Q24" s="37"/>
-      <c r="R24" s="56" t="s">
-        <v>652</v>
+      <c r="R24" s="57" t="s">
+        <v>650</v>
       </c>
       <c r="S24" s="37"/>
       <c r="T24" s="37"/>
       <c r="U24" s="37"/>
       <c r="V24" s="37" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="W24" s="38"/>
       <c r="X24" s="37"/>
@@ -22494,339 +22894,339 @@
       <c r="AC24" s="37"/>
       <c r="AD24" s="37"/>
       <c r="AE24" s="37" t="s">
+        <v>652</v>
+      </c>
+      <c r="AF24" s="37" t="s">
+        <v>653</v>
+      </c>
+      <c r="AG24" s="41" t="s">
         <v>654</v>
-      </c>
-      <c r="AF24" s="37" t="s">
-        <v>655</v>
-      </c>
-      <c r="AG24" s="41" t="s">
-        <v>656</v>
       </c>
       <c r="AH24" s="36"/>
       <c r="AI24" s="37" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="AJ24" s="37"/>
       <c r="AK24" s="37"/>
       <c r="AL24" s="37" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="AM24" s="37"/>
       <c r="AN24" s="37"/>
       <c r="AO24" s="37"/>
       <c r="AP24" s="37"/>
       <c r="AQ24" s="37" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="AR24" s="37"/>
       <c r="AS24" s="37"/>
       <c r="AT24" s="39"/>
       <c r="AU24" s="37"/>
       <c r="AV24" s="39" t="s">
+        <v>658</v>
+      </c>
+      <c r="AW24" s="37" t="s">
+        <v>659</v>
+      </c>
+      <c r="AX24" s="37"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" s="46" t="s">
+        <v>338</v>
+      </c>
+      <c r="C25" s="46" t="s">
         <v>660</v>
       </c>
-      <c r="AW24" s="37" t="s">
+      <c r="D25" s="46" t="s">
         <v>661</v>
       </c>
-      <c r="AX24" s="37"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="45" t="s">
-        <v>54</v>
-      </c>
-      <c r="B25" s="45" t="s">
-        <v>340</v>
-      </c>
-      <c r="C25" s="45" t="s">
+      <c r="E25" s="35" t="s">
         <v>662</v>
       </c>
-      <c r="D25" s="45" t="s">
+      <c r="F25" s="36" t="s">
         <v>663</v>
       </c>
-      <c r="E25" s="35" t="s">
+      <c r="G25" s="37"/>
+      <c r="H25" s="45" t="s">
         <v>664</v>
-      </c>
-      <c r="F25" s="36" t="s">
-        <v>665</v>
-      </c>
-      <c r="G25" s="37"/>
-      <c r="H25" s="44" t="s">
-        <v>666</v>
       </c>
       <c r="I25" s="37"/>
       <c r="J25" s="37" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="K25" s="37"/>
       <c r="L25" s="37"/>
       <c r="M25" s="37"/>
-      <c r="N25" s="44"/>
+      <c r="N25" s="45"/>
       <c r="O25" s="37"/>
       <c r="P25" s="8"/>
       <c r="Q25" s="37"/>
-      <c r="R25" s="54" t="s">
-        <v>668</v>
+      <c r="R25" s="55" t="s">
+        <v>666</v>
       </c>
       <c r="S25" s="37"/>
       <c r="T25" s="37"/>
       <c r="U25" s="37"/>
       <c r="V25" s="37" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="W25" s="38"/>
       <c r="X25" s="37"/>
       <c r="Y25" s="41" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="Z25" s="37"/>
       <c r="AA25" s="41" t="s">
+        <v>669</v>
+      </c>
+      <c r="AB25" s="37" t="s">
+        <v>670</v>
+      </c>
+      <c r="AC25" s="37"/>
+      <c r="AD25" s="45" t="s">
         <v>671</v>
       </c>
-      <c r="AB25" s="37" t="s">
+      <c r="AE25" s="37" t="s">
         <v>672</v>
       </c>
-      <c r="AC25" s="37"/>
-      <c r="AD25" s="44" t="s">
+      <c r="AF25" s="37" t="s">
         <v>673</v>
-      </c>
-      <c r="AE25" s="37" t="s">
-        <v>674</v>
-      </c>
-      <c r="AF25" s="37" t="s">
-        <v>675</v>
       </c>
       <c r="AG25" s="37"/>
       <c r="AH25" s="36"/>
       <c r="AI25" s="37" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="AJ25" s="37"/>
       <c r="AK25" s="37" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="AL25" s="37" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="AM25" s="37"/>
       <c r="AN25" s="37"/>
       <c r="AO25" s="37"/>
       <c r="AP25" s="37" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AQ25" s="37" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="AR25" s="37"/>
       <c r="AS25" s="37"/>
       <c r="AT25" s="39" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="AU25" s="37"/>
       <c r="AV25" s="39" t="s">
+        <v>680</v>
+      </c>
+      <c r="AW25" s="37" t="s">
+        <v>681</v>
+      </c>
+      <c r="AX25" s="37"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="B26" s="46" t="s">
+        <v>338</v>
+      </c>
+      <c r="C26" s="46" t="s">
+        <v>90</v>
+      </c>
+      <c r="D26" s="46" t="s">
+        <v>89</v>
+      </c>
+      <c r="E26" s="35" t="s">
         <v>682</v>
       </c>
-      <c r="AW25" s="37" t="s">
+      <c r="F26" s="42" t="s">
         <v>683</v>
-      </c>
-      <c r="AX25" s="37"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="45" t="s">
-        <v>54</v>
-      </c>
-      <c r="B26" s="45" t="s">
-        <v>340</v>
-      </c>
-      <c r="C26" s="45" t="s">
-        <v>90</v>
-      </c>
-      <c r="D26" s="45" t="s">
-        <v>89</v>
-      </c>
-      <c r="E26" s="35" t="s">
-        <v>684</v>
-      </c>
-      <c r="F26" s="42" t="s">
-        <v>685</v>
       </c>
       <c r="G26" s="37"/>
       <c r="H26" s="37" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="I26" s="37"/>
       <c r="J26" s="37" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="K26" s="37" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="L26" s="37"/>
       <c r="M26" s="37"/>
-      <c r="N26" s="46" t="s">
-        <v>689</v>
+      <c r="N26" s="47" t="s">
+        <v>687</v>
       </c>
       <c r="O26" s="37"/>
       <c r="P26" s="8"/>
       <c r="Q26" s="37"/>
-      <c r="R26" s="56" t="s">
-        <v>690</v>
+      <c r="R26" s="57" t="s">
+        <v>688</v>
       </c>
       <c r="S26" s="37"/>
       <c r="T26" s="37"/>
       <c r="U26" s="37" t="s">
+        <v>689</v>
+      </c>
+      <c r="V26" s="37" t="s">
+        <v>690</v>
+      </c>
+      <c r="W26" s="49" t="s">
         <v>691</v>
       </c>
-      <c r="V26" s="37" t="s">
+      <c r="X26" s="37"/>
+      <c r="Y26" s="58" t="s">
         <v>692</v>
-      </c>
-      <c r="W26" s="48" t="s">
-        <v>693</v>
-      </c>
-      <c r="X26" s="37"/>
-      <c r="Y26" s="57" t="s">
-        <v>694</v>
       </c>
       <c r="Z26" s="37"/>
       <c r="AA26" s="41" t="s">
+        <v>693</v>
+      </c>
+      <c r="AB26" s="37" t="s">
+        <v>694</v>
+      </c>
+      <c r="AC26" s="37" t="s">
         <v>695</v>
-      </c>
-      <c r="AB26" s="37" t="s">
-        <v>696</v>
-      </c>
-      <c r="AC26" s="37" t="s">
-        <v>697</v>
       </c>
       <c r="AD26" s="37"/>
       <c r="AE26" s="37" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AF26" s="37"/>
       <c r="AG26" s="41" t="s">
+        <v>697</v>
+      </c>
+      <c r="AH26" s="42" t="s">
+        <v>698</v>
+      </c>
+      <c r="AI26" s="37" t="s">
         <v>699</v>
       </c>
-      <c r="AH26" s="42" t="s">
+      <c r="AJ26" s="37" t="s">
         <v>700</v>
-      </c>
-      <c r="AI26" s="37" t="s">
-        <v>701</v>
-      </c>
-      <c r="AJ26" s="37" t="s">
-        <v>702</v>
       </c>
       <c r="AK26" s="37"/>
       <c r="AL26" s="37"/>
       <c r="AM26" s="37"/>
       <c r="AN26" s="37" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="AO26" s="37"/>
       <c r="AP26" s="37"/>
       <c r="AQ26" s="37" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="AR26" s="37" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="AS26" s="37"/>
       <c r="AT26" s="39" t="s">
+        <v>704</v>
+      </c>
+      <c r="AU26" s="53" t="s">
+        <v>705</v>
+      </c>
+      <c r="AV26" s="39" t="s">
         <v>706</v>
-      </c>
-      <c r="AU26" s="52" t="s">
-        <v>707</v>
-      </c>
-      <c r="AV26" s="39" t="s">
-        <v>708</v>
       </c>
       <c r="AW26" s="37"/>
       <c r="AX26" s="37"/>
     </row>
     <row r="27">
-      <c r="A27" s="58" t="s">
+      <c r="A27" s="59" t="s">
         <v>104</v>
       </c>
-      <c r="B27" s="58" t="s">
-        <v>709</v>
-      </c>
-      <c r="C27" s="58" t="s">
+      <c r="B27" s="59" t="s">
+        <v>707</v>
+      </c>
+      <c r="C27" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="D27" s="58" t="s">
-        <v>710</v>
+      <c r="D27" s="59" t="s">
+        <v>708</v>
       </c>
       <c r="E27" s="35"/>
       <c r="F27" s="36" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="G27" s="37" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="H27" s="37"/>
       <c r="I27" s="37" t="s">
+        <v>711</v>
+      </c>
+      <c r="J27" s="37" t="s">
+        <v>712</v>
+      </c>
+      <c r="K27" s="37" t="s">
         <v>713</v>
-      </c>
-      <c r="J27" s="37" t="s">
-        <v>714</v>
-      </c>
-      <c r="K27" s="37" t="s">
-        <v>715</v>
       </c>
       <c r="L27" s="37"/>
       <c r="M27" s="37"/>
-      <c r="N27" s="44"/>
+      <c r="N27" s="45"/>
       <c r="O27" s="37" t="s">
+        <v>714</v>
+      </c>
+      <c r="P27" s="41" t="s">
+        <v>715</v>
+      </c>
+      <c r="Q27" s="37" t="s">
         <v>716</v>
       </c>
-      <c r="P27" s="41" t="s">
+      <c r="R27" s="55"/>
+      <c r="S27" s="37" t="s">
         <v>717</v>
       </c>
-      <c r="Q27" s="37" t="s">
+      <c r="T27" s="37" t="s">
         <v>718</v>
       </c>
-      <c r="R27" s="54"/>
-      <c r="S27" s="37" t="s">
+      <c r="U27" s="37" t="s">
         <v>719</v>
-      </c>
-      <c r="T27" s="37" t="s">
-        <v>720</v>
-      </c>
-      <c r="U27" s="37" t="s">
-        <v>721</v>
       </c>
       <c r="V27" s="37"/>
       <c r="W27" s="37"/>
       <c r="X27" s="37"/>
-      <c r="Y27" s="59"/>
+      <c r="Y27" s="60"/>
       <c r="Z27" s="37"/>
       <c r="AA27" s="41" t="s">
+        <v>720</v>
+      </c>
+      <c r="AB27" s="37" t="s">
+        <v>721</v>
+      </c>
+      <c r="AC27" s="41" t="s">
         <v>722</v>
       </c>
-      <c r="AB27" s="37" t="s">
+      <c r="AD27" s="45" t="s">
         <v>723</v>
       </c>
-      <c r="AC27" s="41" t="s">
+      <c r="AE27" s="37" t="s">
         <v>724</v>
-      </c>
-      <c r="AD27" s="44" t="s">
-        <v>725</v>
-      </c>
-      <c r="AE27" s="37" t="s">
-        <v>726</v>
       </c>
       <c r="AF27" s="37"/>
       <c r="AG27" s="37"/>
       <c r="AH27" s="36" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="AI27" s="37" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="AJ27" s="37"/>
       <c r="AK27" s="37" t="s">
-        <v>729</v>
-      </c>
-      <c r="AL27" s="44"/>
-      <c r="AM27" s="44" t="s">
-        <v>730</v>
+        <v>727</v>
+      </c>
+      <c r="AL27" s="45"/>
+      <c r="AM27" s="45" t="s">
+        <v>728</v>
       </c>
       <c r="AN27" s="37"/>
       <c r="AO27" s="37"/>
@@ -22835,36 +23235,36 @@
       <c r="AR27" s="37"/>
       <c r="AS27" s="37"/>
       <c r="AT27" s="39" t="s">
-        <v>731</v>
-      </c>
-      <c r="AU27" s="52" t="s">
-        <v>732</v>
+        <v>729</v>
+      </c>
+      <c r="AU27" s="53" t="s">
+        <v>730</v>
       </c>
       <c r="AV27" s="39"/>
       <c r="AW27" s="37" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="AX27" s="37"/>
     </row>
     <row r="28">
-      <c r="A28" s="58" t="s">
+      <c r="A28" s="59" t="s">
         <v>104</v>
       </c>
-      <c r="B28" s="58" t="s">
-        <v>709</v>
-      </c>
-      <c r="C28" s="58" t="s">
+      <c r="B28" s="59" t="s">
+        <v>707</v>
+      </c>
+      <c r="C28" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="D28" s="58" t="s">
-        <v>734</v>
+      <c r="D28" s="59" t="s">
+        <v>732</v>
       </c>
       <c r="E28" s="35"/>
       <c r="F28" s="36" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="G28" s="37" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="H28" s="37"/>
       <c r="I28" s="37"/>
@@ -22872,12 +23272,12 @@
       <c r="K28" s="37"/>
       <c r="L28" s="37"/>
       <c r="M28" s="37"/>
-      <c r="N28" s="46"/>
+      <c r="N28" s="47"/>
       <c r="O28" s="37"/>
       <c r="P28" s="37"/>
       <c r="Q28" s="37"/>
-      <c r="R28" s="54" t="s">
-        <v>737</v>
+      <c r="R28" s="55" t="s">
+        <v>735</v>
       </c>
       <c r="S28" s="37"/>
       <c r="T28" s="37"/>
@@ -22895,7 +23295,7 @@
       <c r="AF28" s="37"/>
       <c r="AG28" s="37"/>
       <c r="AH28" s="36" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="AI28" s="37"/>
       <c r="AJ28" s="37"/>
@@ -22915,21 +23315,21 @@
       <c r="AX28" s="37"/>
     </row>
     <row r="29">
-      <c r="A29" s="58" t="s">
+      <c r="A29" s="59" t="s">
         <v>104</v>
       </c>
-      <c r="B29" s="58" t="s">
+      <c r="B29" s="59" t="s">
+        <v>737</v>
+      </c>
+      <c r="C29" s="59" t="s">
+        <v>738</v>
+      </c>
+      <c r="D29" s="59" t="s">
         <v>739</v>
-      </c>
-      <c r="C29" s="58" t="s">
-        <v>740</v>
-      </c>
-      <c r="D29" s="58" t="s">
-        <v>741</v>
       </c>
       <c r="E29" s="35"/>
       <c r="F29" s="36" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="G29" s="37"/>
       <c r="H29" s="37"/>
@@ -22938,10 +23338,10 @@
       <c r="K29" s="37"/>
       <c r="L29" s="37"/>
       <c r="M29" s="37"/>
-      <c r="N29" s="44"/>
+      <c r="N29" s="45"/>
       <c r="O29" s="37"/>
       <c r="P29" s="41" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="Q29" s="37"/>
       <c r="R29" s="37"/>
@@ -22953,27 +23353,27 @@
       <c r="X29" s="37"/>
       <c r="Y29" s="37"/>
       <c r="Z29" s="37" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="AA29" s="37"/>
       <c r="AB29" s="37"/>
       <c r="AC29" s="37"/>
-      <c r="AD29" s="44" t="s">
-        <v>745</v>
+      <c r="AD29" s="45" t="s">
+        <v>743</v>
       </c>
       <c r="AE29" s="37" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="AF29" s="37"/>
       <c r="AG29" s="37"/>
       <c r="AH29" s="36" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="AI29" s="37"/>
       <c r="AJ29" s="37"/>
       <c r="AK29" s="37"/>
       <c r="AL29" s="37" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="AM29" s="37"/>
       <c r="AN29" s="37"/>
@@ -22989,49 +23389,49 @@
       <c r="AX29" s="37"/>
     </row>
     <row r="30">
-      <c r="A30" s="58" t="s">
+      <c r="A30" s="59" t="s">
         <v>104</v>
       </c>
-      <c r="B30" s="58" t="s">
-        <v>739</v>
-      </c>
-      <c r="C30" s="58" t="s">
-        <v>748</v>
-      </c>
-      <c r="D30" s="58" t="s">
-        <v>749</v>
+      <c r="B30" s="59" t="s">
+        <v>737</v>
+      </c>
+      <c r="C30" s="59" t="s">
+        <v>746</v>
+      </c>
+      <c r="D30" s="59" t="s">
+        <v>747</v>
       </c>
       <c r="E30" s="35"/>
       <c r="F30" s="36" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="G30" s="37"/>
       <c r="H30" s="37" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="I30" s="37" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="J30" s="37"/>
       <c r="K30" s="37"/>
       <c r="L30" s="37"/>
       <c r="M30" s="37"/>
-      <c r="N30" s="44" t="s">
-        <v>753</v>
+      <c r="N30" s="45" t="s">
+        <v>751</v>
       </c>
       <c r="O30" s="37"/>
       <c r="P30" s="37"/>
       <c r="Q30" s="37" t="s">
-        <v>754</v>
-      </c>
-      <c r="R30" s="54" t="s">
-        <v>755</v>
+        <v>752</v>
+      </c>
+      <c r="R30" s="55" t="s">
+        <v>753</v>
       </c>
       <c r="S30" s="37"/>
       <c r="T30" s="37"/>
       <c r="U30" s="37"/>
       <c r="V30" s="41" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="W30" s="37"/>
       <c r="X30" s="37"/>
@@ -23042,56 +23442,56 @@
       <c r="AC30" s="37"/>
       <c r="AD30" s="37"/>
       <c r="AE30" s="37" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="AF30" s="37"/>
       <c r="AG30" s="37"/>
       <c r="AH30" s="36" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="AI30" s="37"/>
       <c r="AJ30" s="37"/>
       <c r="AK30" s="37" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="AL30" s="37"/>
       <c r="AM30" s="37"/>
       <c r="AN30" s="37" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="AO30" s="37"/>
       <c r="AP30" s="37"/>
       <c r="AQ30" s="37" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="AR30" s="37" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="AS30" s="37"/>
       <c r="AT30" s="39"/>
       <c r="AU30" s="37"/>
       <c r="AV30" s="39"/>
       <c r="AW30" s="37" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="AX30" s="37"/>
     </row>
     <row r="31">
-      <c r="A31" s="58" t="s">
+      <c r="A31" s="59" t="s">
         <v>104</v>
       </c>
-      <c r="B31" s="58" t="s">
-        <v>709</v>
-      </c>
-      <c r="C31" s="58" t="s">
-        <v>327</v>
-      </c>
-      <c r="D31" s="58" t="s">
+      <c r="B31" s="59" t="s">
+        <v>707</v>
+      </c>
+      <c r="C31" s="59" t="s">
+        <v>325</v>
+      </c>
+      <c r="D31" s="59" t="s">
         <v>101</v>
       </c>
       <c r="E31" s="35"/>
       <c r="F31" s="36" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="G31" s="37"/>
       <c r="H31" s="37"/>
@@ -23100,50 +23500,50 @@
       <c r="K31" s="37"/>
       <c r="L31" s="37"/>
       <c r="M31" s="37" t="s">
-        <v>765</v>
-      </c>
-      <c r="N31" s="46" t="s">
-        <v>766</v>
+        <v>763</v>
+      </c>
+      <c r="N31" s="47" t="s">
+        <v>764</v>
       </c>
       <c r="O31" s="37"/>
       <c r="P31" s="37"/>
       <c r="Q31" s="37"/>
       <c r="R31" s="37"/>
       <c r="S31" s="37" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="T31" s="37" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="U31" s="37"/>
       <c r="V31" s="37"/>
       <c r="W31" s="41" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="X31" s="37"/>
       <c r="Y31" s="37"/>
       <c r="Z31" s="37"/>
       <c r="AA31" s="41" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="AB31" s="37" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="AC31" s="37"/>
       <c r="AD31" s="37"/>
       <c r="AE31" s="37" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="AF31" s="37"/>
       <c r="AG31" s="37"/>
       <c r="AH31" s="36" t="s">
+        <v>771</v>
+      </c>
+      <c r="AI31" s="37" t="s">
+        <v>772</v>
+      </c>
+      <c r="AJ31" s="37" t="s">
         <v>773</v>
-      </c>
-      <c r="AI31" s="37" t="s">
-        <v>774</v>
-      </c>
-      <c r="AJ31" s="37" t="s">
-        <v>775</v>
       </c>
       <c r="AK31" s="37"/>
       <c r="AL31" s="37"/>
@@ -23155,49 +23555,49 @@
       <c r="AR31" s="37"/>
       <c r="AS31" s="37"/>
       <c r="AT31" s="39" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="AU31" s="37"/>
       <c r="AV31" s="39" t="s">
+        <v>775</v>
+      </c>
+      <c r="AW31" s="37" t="s">
+        <v>776</v>
+      </c>
+      <c r="AX31" s="37"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="59" t="s">
+        <v>104</v>
+      </c>
+      <c r="B32" s="59" t="s">
+        <v>338</v>
+      </c>
+      <c r="C32" s="59" t="s">
         <v>777</v>
       </c>
-      <c r="AW31" s="37" t="s">
+      <c r="D32" s="59" t="s">
         <v>778</v>
-      </c>
-      <c r="AX31" s="37"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="58" t="s">
-        <v>104</v>
-      </c>
-      <c r="B32" s="58" t="s">
-        <v>340</v>
-      </c>
-      <c r="C32" s="58" t="s">
-        <v>779</v>
-      </c>
-      <c r="D32" s="58" t="s">
-        <v>780</v>
       </c>
       <c r="E32" s="35"/>
       <c r="F32" s="36" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="G32" s="37"/>
       <c r="H32" s="37"/>
       <c r="I32" s="37"/>
       <c r="J32" s="37" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="K32" s="37"/>
       <c r="L32" s="37"/>
       <c r="M32" s="37"/>
-      <c r="N32" s="44"/>
+      <c r="N32" s="45"/>
       <c r="O32" s="37" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="P32" s="37" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="Q32" s="37"/>
       <c r="R32" s="37"/>
@@ -23207,26 +23607,26 @@
       <c r="V32" s="37"/>
       <c r="W32" s="37"/>
       <c r="X32" s="37"/>
-      <c r="Y32" s="60"/>
-      <c r="Z32" s="60"/>
-      <c r="AA32" s="60"/>
+      <c r="Y32" s="61"/>
+      <c r="Z32" s="61"/>
+      <c r="AA32" s="61"/>
       <c r="AB32" s="37" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="AC32" s="37"/>
       <c r="AD32" s="37"/>
       <c r="AE32" s="37" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="AF32" s="37"/>
       <c r="AG32" s="37" t="s">
+        <v>785</v>
+      </c>
+      <c r="AH32" s="36" t="s">
+        <v>786</v>
+      </c>
+      <c r="AI32" s="37" t="s">
         <v>787</v>
-      </c>
-      <c r="AH32" s="36" t="s">
-        <v>788</v>
-      </c>
-      <c r="AI32" s="37" t="s">
-        <v>789</v>
       </c>
       <c r="AJ32" s="37"/>
       <c r="AK32" s="37"/>
@@ -23245,84 +23645,84 @@
       <c r="AX32" s="37"/>
     </row>
     <row r="33">
-      <c r="A33" s="58" t="s">
+      <c r="A33" s="59" t="s">
         <v>104</v>
       </c>
-      <c r="B33" s="58" t="s">
-        <v>340</v>
-      </c>
-      <c r="C33" s="58" t="s">
-        <v>662</v>
-      </c>
-      <c r="D33" s="58" t="s">
+      <c r="B33" s="59" t="s">
+        <v>338</v>
+      </c>
+      <c r="C33" s="59" t="s">
+        <v>660</v>
+      </c>
+      <c r="D33" s="59" t="s">
         <v>123</v>
       </c>
       <c r="E33" s="40" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="F33" s="36" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="G33" s="37"/>
       <c r="H33" s="37"/>
       <c r="I33" s="37" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="J33" s="37"/>
       <c r="K33" s="37"/>
       <c r="L33" s="37"/>
       <c r="M33" s="37" t="s">
-        <v>793</v>
-      </c>
-      <c r="N33" s="46" t="s">
-        <v>794</v>
+        <v>791</v>
+      </c>
+      <c r="N33" s="47" t="s">
+        <v>792</v>
       </c>
       <c r="O33" s="37"/>
       <c r="P33" s="37" t="s">
+        <v>793</v>
+      </c>
+      <c r="Q33" s="37"/>
+      <c r="R33" s="55" t="s">
+        <v>794</v>
+      </c>
+      <c r="S33" s="37" t="s">
         <v>795</v>
-      </c>
-      <c r="Q33" s="37"/>
-      <c r="R33" s="54" t="s">
-        <v>796</v>
-      </c>
-      <c r="S33" s="37" t="s">
-        <v>797</v>
       </c>
       <c r="T33" s="37"/>
       <c r="U33" s="37" t="s">
+        <v>796</v>
+      </c>
+      <c r="V33" s="37" t="s">
+        <v>797</v>
+      </c>
+      <c r="W33" s="41" t="s">
         <v>798</v>
-      </c>
-      <c r="V33" s="37" t="s">
-        <v>799</v>
-      </c>
-      <c r="W33" s="41" t="s">
-        <v>800</v>
       </c>
       <c r="X33" s="37"/>
       <c r="Y33" s="37"/>
       <c r="Z33" s="37" t="s">
+        <v>799</v>
+      </c>
+      <c r="AA33" s="37" t="s">
+        <v>800</v>
+      </c>
+      <c r="AB33" s="37" t="s">
         <v>801</v>
       </c>
-      <c r="AA33" s="37" t="s">
+      <c r="AC33" s="37"/>
+      <c r="AD33" s="45" t="s">
         <v>802</v>
       </c>
-      <c r="AB33" s="37" t="s">
+      <c r="AE33" s="37" t="s">
         <v>803</v>
-      </c>
-      <c r="AC33" s="37"/>
-      <c r="AD33" s="44" t="s">
-        <v>804</v>
-      </c>
-      <c r="AE33" s="37" t="s">
-        <v>805</v>
       </c>
       <c r="AF33" s="37"/>
       <c r="AG33" s="37"/>
       <c r="AH33" s="36" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="AI33" s="37" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="AJ33" s="37"/>
       <c r="AK33" s="37"/>
@@ -23331,39 +23731,39 @@
       <c r="AN33" s="37"/>
       <c r="AO33" s="37"/>
       <c r="AP33" s="37" t="s">
+        <v>806</v>
+      </c>
+      <c r="AQ33" s="37" t="s">
+        <v>807</v>
+      </c>
+      <c r="AR33" s="37" t="s">
         <v>808</v>
-      </c>
-      <c r="AQ33" s="37" t="s">
-        <v>809</v>
-      </c>
-      <c r="AR33" s="37" t="s">
-        <v>810</v>
       </c>
       <c r="AS33" s="37"/>
       <c r="AT33" s="39"/>
       <c r="AU33" s="37"/>
       <c r="AV33" s="39"/>
       <c r="AW33" s="37" t="s">
+        <v>809</v>
+      </c>
+      <c r="AX33" s="37"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="59" t="s">
+        <v>104</v>
+      </c>
+      <c r="B34" s="59" t="s">
+        <v>810</v>
+      </c>
+      <c r="C34" s="59" t="s">
         <v>811</v>
       </c>
-      <c r="AX33" s="37"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="58" t="s">
-        <v>104</v>
-      </c>
-      <c r="B34" s="58" t="s">
+      <c r="D34" s="59" t="s">
         <v>812</v>
-      </c>
-      <c r="C34" s="58" t="s">
-        <v>813</v>
-      </c>
-      <c r="D34" s="58" t="s">
-        <v>814</v>
       </c>
       <c r="E34" s="35"/>
       <c r="F34" s="36" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="G34" s="37"/>
       <c r="H34" s="37"/>
@@ -23372,7 +23772,7 @@
       <c r="K34" s="37"/>
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
-      <c r="N34" s="44"/>
+      <c r="N34" s="45"/>
       <c r="O34" s="37"/>
       <c r="P34" s="37"/>
       <c r="Q34" s="37"/>
@@ -23393,7 +23793,7 @@
       <c r="AF34" s="37"/>
       <c r="AG34" s="37"/>
       <c r="AH34" s="36" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="AI34" s="37"/>
       <c r="AJ34" s="37"/>
@@ -23413,21 +23813,21 @@
       <c r="AX34" s="37"/>
     </row>
     <row r="35">
-      <c r="A35" s="58" t="s">
+      <c r="A35" s="59" t="s">
         <v>104</v>
       </c>
-      <c r="B35" s="58" t="s">
-        <v>812</v>
-      </c>
-      <c r="C35" s="58" t="s">
-        <v>816</v>
-      </c>
-      <c r="D35" s="58" t="s">
-        <v>817</v>
+      <c r="B35" s="59" t="s">
+        <v>810</v>
+      </c>
+      <c r="C35" s="59" t="s">
+        <v>814</v>
+      </c>
+      <c r="D35" s="59" t="s">
+        <v>815</v>
       </c>
       <c r="E35" s="35"/>
       <c r="F35" s="36" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="G35" s="37"/>
       <c r="H35" s="37"/>
@@ -23436,7 +23836,7 @@
       <c r="K35" s="37"/>
       <c r="L35" s="37"/>
       <c r="M35" s="37"/>
-      <c r="N35" s="44"/>
+      <c r="N35" s="45"/>
       <c r="O35" s="37"/>
       <c r="P35" s="37"/>
       <c r="Q35" s="37"/>
@@ -23444,7 +23844,7 @@
       <c r="S35" s="37"/>
       <c r="T35" s="37"/>
       <c r="U35" s="37" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="V35" s="37"/>
       <c r="W35" s="8"/>
@@ -23459,22 +23859,22 @@
       <c r="AF35" s="37"/>
       <c r="AG35" s="37"/>
       <c r="AH35" s="42" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="AI35" s="37"/>
       <c r="AJ35" s="37"/>
       <c r="AK35" s="37" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="AL35" s="37"/>
       <c r="AM35" s="37"/>
       <c r="AN35" s="37" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="AO35" s="37"/>
       <c r="AP35" s="37"/>
       <c r="AQ35" s="37" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="AR35" s="37"/>
       <c r="AS35" s="37"/>
@@ -23485,83 +23885,83 @@
       <c r="AX35" s="37"/>
     </row>
     <row r="36">
-      <c r="A36" s="58" t="s">
+      <c r="A36" s="59" t="s">
         <v>104</v>
       </c>
-      <c r="B36" s="58" t="s">
-        <v>824</v>
-      </c>
-      <c r="C36" s="58" t="s">
-        <v>816</v>
-      </c>
-      <c r="D36" s="58" t="s">
-        <v>825</v>
+      <c r="B36" s="59" t="s">
+        <v>822</v>
+      </c>
+      <c r="C36" s="59" t="s">
+        <v>814</v>
+      </c>
+      <c r="D36" s="59" t="s">
+        <v>823</v>
       </c>
       <c r="E36" s="35"/>
       <c r="F36" s="36" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="G36" s="37"/>
       <c r="H36" s="37"/>
       <c r="I36" s="37"/>
       <c r="J36" s="37" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="K36" s="37"/>
       <c r="L36" s="37" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="M36" s="37"/>
-      <c r="N36" s="44"/>
+      <c r="N36" s="45"/>
       <c r="O36" s="37"/>
       <c r="P36" s="37"/>
       <c r="Q36" s="37"/>
       <c r="R36" s="37"/>
       <c r="S36" s="37"/>
       <c r="T36" s="37" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="U36" s="37"/>
       <c r="V36" s="37" t="s">
+        <v>827</v>
+      </c>
+      <c r="W36" s="49" t="s">
+        <v>828</v>
+      </c>
+      <c r="X36" s="37" t="s">
         <v>829</v>
-      </c>
-      <c r="W36" s="48" t="s">
-        <v>830</v>
-      </c>
-      <c r="X36" s="37" t="s">
-        <v>831</v>
       </c>
       <c r="Y36" s="37"/>
       <c r="Z36" s="37" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="AA36" s="37"/>
       <c r="AB36" s="41" t="s">
+        <v>831</v>
+      </c>
+      <c r="AC36" s="37"/>
+      <c r="AD36" s="45" t="s">
+        <v>832</v>
+      </c>
+      <c r="AE36" s="37" t="s">
         <v>833</v>
-      </c>
-      <c r="AC36" s="37"/>
-      <c r="AD36" s="44" t="s">
-        <v>834</v>
-      </c>
-      <c r="AE36" s="37" t="s">
-        <v>835</v>
       </c>
       <c r="AF36" s="37"/>
       <c r="AG36" s="37" t="s">
+        <v>834</v>
+      </c>
+      <c r="AH36" s="36" t="s">
+        <v>835</v>
+      </c>
+      <c r="AI36" s="37" t="s">
         <v>836</v>
       </c>
-      <c r="AH36" s="36" t="s">
+      <c r="AJ36" s="45" t="s">
         <v>837</v>
-      </c>
-      <c r="AI36" s="37" t="s">
-        <v>838</v>
-      </c>
-      <c r="AJ36" s="44" t="s">
-        <v>839</v>
       </c>
       <c r="AK36" s="37"/>
       <c r="AL36" s="37" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="AM36" s="37"/>
       <c r="AN36" s="37"/>
@@ -23573,31 +23973,31 @@
       <c r="AT36" s="39"/>
       <c r="AU36" s="37"/>
       <c r="AV36" s="39" t="s">
+        <v>839</v>
+      </c>
+      <c r="AW36" s="37" t="s">
+        <v>840</v>
+      </c>
+      <c r="AX36" s="37"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="59" t="s">
+        <v>104</v>
+      </c>
+      <c r="B37" s="59" t="s">
+        <v>822</v>
+      </c>
+      <c r="C37" s="59" t="s">
         <v>841</v>
       </c>
-      <c r="AW36" s="37" t="s">
+      <c r="D37" s="59" t="s">
         <v>842</v>
       </c>
-      <c r="AX36" s="37"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="58" t="s">
-        <v>104</v>
-      </c>
-      <c r="B37" s="58" t="s">
-        <v>824</v>
-      </c>
-      <c r="C37" s="58" t="s">
+      <c r="E37" s="35" t="s">
         <v>843</v>
       </c>
-      <c r="D37" s="58" t="s">
+      <c r="F37" s="36" t="s">
         <v>844</v>
-      </c>
-      <c r="E37" s="35" t="s">
-        <v>845</v>
-      </c>
-      <c r="F37" s="36" t="s">
-        <v>846</v>
       </c>
       <c r="G37" s="37"/>
       <c r="H37" s="37"/>
@@ -23606,7 +24006,7 @@
       <c r="K37" s="37"/>
       <c r="L37" s="37"/>
       <c r="M37" s="37"/>
-      <c r="N37" s="44"/>
+      <c r="N37" s="45"/>
       <c r="O37" s="37"/>
       <c r="P37" s="37"/>
       <c r="Q37" s="37"/>
@@ -23615,46 +24015,46 @@
       <c r="T37" s="37"/>
       <c r="U37" s="37"/>
       <c r="V37" s="37"/>
-      <c r="W37" s="48" t="s">
-        <v>847</v>
+      <c r="W37" s="49" t="s">
+        <v>845</v>
       </c>
       <c r="X37" s="37" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="Y37" s="37"/>
       <c r="Z37" s="37"/>
       <c r="AA37" s="37"/>
       <c r="AB37" s="41" t="s">
+        <v>847</v>
+      </c>
+      <c r="AC37" s="37"/>
+      <c r="AD37" s="45" t="s">
+        <v>848</v>
+      </c>
+      <c r="AE37" s="37" t="s">
         <v>849</v>
-      </c>
-      <c r="AC37" s="37"/>
-      <c r="AD37" s="44" t="s">
-        <v>850</v>
-      </c>
-      <c r="AE37" s="37" t="s">
-        <v>851</v>
       </c>
       <c r="AF37" s="37"/>
       <c r="AH37" s="36" t="s">
+        <v>850</v>
+      </c>
+      <c r="AI37" s="37" t="s">
+        <v>851</v>
+      </c>
+      <c r="AJ37" s="45" t="s">
         <v>852</v>
       </c>
-      <c r="AI37" s="37" t="s">
+      <c r="AK37" s="37" t="s">
         <v>853</v>
-      </c>
-      <c r="AJ37" s="44" t="s">
-        <v>854</v>
-      </c>
-      <c r="AK37" s="37" t="s">
-        <v>855</v>
       </c>
       <c r="AL37" s="37"/>
       <c r="AM37" s="37"/>
       <c r="AN37" s="37" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="AO37" s="37"/>
       <c r="AP37" s="37" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="AQ37" s="37"/>
       <c r="AR37" s="37"/>
@@ -23662,127 +24062,127 @@
       <c r="AT37" s="39"/>
       <c r="AU37" s="37"/>
       <c r="AV37" s="39" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="AW37" s="37"/>
       <c r="AX37" s="37"/>
     </row>
     <row r="38">
-      <c r="A38" s="58" t="s">
+      <c r="A38" s="59" t="s">
         <v>104</v>
       </c>
-      <c r="B38" s="58" t="s">
+      <c r="B38" s="59" t="s">
+        <v>857</v>
+      </c>
+      <c r="C38" s="59" t="s">
+        <v>858</v>
+      </c>
+      <c r="D38" s="59" t="s">
         <v>859</v>
       </c>
-      <c r="C38" s="58" t="s">
+      <c r="E38" s="35" t="s">
         <v>860</v>
       </c>
-      <c r="D38" s="58" t="s">
+      <c r="F38" s="36" t="s">
         <v>861</v>
-      </c>
-      <c r="E38" s="35" t="s">
-        <v>862</v>
-      </c>
-      <c r="F38" s="36" t="s">
-        <v>863</v>
       </c>
       <c r="G38" s="37"/>
       <c r="H38" s="37"/>
       <c r="I38" s="37"/>
       <c r="J38" s="37" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="K38" s="37"/>
       <c r="L38" s="37"/>
       <c r="M38" s="37"/>
-      <c r="N38" s="44"/>
+      <c r="N38" s="45"/>
       <c r="O38" s="37" t="s">
+        <v>863</v>
+      </c>
+      <c r="P38" s="41" t="s">
+        <v>864</v>
+      </c>
+      <c r="Q38" s="37" t="s">
         <v>865</v>
-      </c>
-      <c r="P38" s="41" t="s">
-        <v>866</v>
-      </c>
-      <c r="Q38" s="37" t="s">
-        <v>867</v>
       </c>
       <c r="R38" s="37"/>
       <c r="S38" s="37"/>
       <c r="T38" s="37"/>
       <c r="U38" s="37"/>
       <c r="V38" s="37" t="s">
-        <v>868</v>
-      </c>
-      <c r="W38" s="48"/>
+        <v>866</v>
+      </c>
+      <c r="W38" s="49"/>
       <c r="X38" s="37"/>
       <c r="Y38" s="37"/>
       <c r="Z38" s="37"/>
       <c r="AA38" s="37" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="AB38" s="37"/>
       <c r="AC38" s="37" t="s">
-        <v>870</v>
-      </c>
-      <c r="AD38" s="44" t="s">
-        <v>871</v>
+        <v>868</v>
+      </c>
+      <c r="AD38" s="45" t="s">
+        <v>869</v>
       </c>
       <c r="AE38" s="8"/>
       <c r="AF38" s="37"/>
       <c r="AG38" s="37" t="s">
+        <v>870</v>
+      </c>
+      <c r="AH38" s="36" t="s">
+        <v>871</v>
+      </c>
+      <c r="AI38" s="37" t="s">
         <v>872</v>
-      </c>
-      <c r="AH38" s="36" t="s">
-        <v>873</v>
-      </c>
-      <c r="AI38" s="37" t="s">
-        <v>874</v>
       </c>
       <c r="AJ38" s="37"/>
       <c r="AK38" s="37"/>
       <c r="AL38" s="37"/>
       <c r="AM38" s="37" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="AN38" s="37"/>
       <c r="AO38" s="37"/>
       <c r="AP38" s="37" t="s">
+        <v>874</v>
+      </c>
+      <c r="AQ38" s="37" t="s">
+        <v>875</v>
+      </c>
+      <c r="AR38" s="37" t="s">
         <v>876</v>
-      </c>
-      <c r="AQ38" s="37" t="s">
-        <v>877</v>
-      </c>
-      <c r="AR38" s="37" t="s">
-        <v>878</v>
       </c>
       <c r="AS38" s="37"/>
       <c r="AT38" s="39" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="AU38" s="37"/>
       <c r="AV38" s="39" t="s">
+        <v>878</v>
+      </c>
+      <c r="AW38" s="37" t="s">
+        <v>879</v>
+      </c>
+      <c r="AX38" s="37"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="59" t="s">
+        <v>104</v>
+      </c>
+      <c r="B39" s="59" t="s">
+        <v>857</v>
+      </c>
+      <c r="C39" s="59" t="s">
         <v>880</v>
       </c>
-      <c r="AW38" s="37" t="s">
+      <c r="D39" s="59" t="s">
         <v>881</v>
-      </c>
-      <c r="AX38" s="37"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="58" t="s">
-        <v>104</v>
-      </c>
-      <c r="B39" s="58" t="s">
-        <v>859</v>
-      </c>
-      <c r="C39" s="58" t="s">
-        <v>882</v>
-      </c>
-      <c r="D39" s="58" t="s">
-        <v>883</v>
       </c>
       <c r="E39" s="35"/>
       <c r="F39" s="36" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="G39" s="37"/>
       <c r="H39" s="37"/>
@@ -23791,7 +24191,7 @@
       <c r="K39" s="37"/>
       <c r="L39" s="37"/>
       <c r="M39" s="37"/>
-      <c r="N39" s="44"/>
+      <c r="N39" s="45"/>
       <c r="O39" s="37"/>
       <c r="P39" s="37"/>
       <c r="Q39" s="37"/>
@@ -23812,7 +24212,7 @@
       <c r="AF39" s="37"/>
       <c r="AG39" s="37"/>
       <c r="AH39" s="36" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="AI39" s="37"/>
       <c r="AJ39" s="37"/>
@@ -23822,7 +24222,7 @@
       <c r="AN39" s="37"/>
       <c r="AO39" s="37"/>
       <c r="AP39" s="37" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="AQ39" s="37"/>
       <c r="AR39" s="37"/>
@@ -23834,79 +24234,79 @@
       <c r="AX39" s="37"/>
     </row>
     <row r="40">
-      <c r="A40" s="58" t="s">
+      <c r="A40" s="59" t="s">
         <v>104</v>
       </c>
-      <c r="B40" s="58" t="s">
+      <c r="B40" s="59" t="s">
+        <v>884</v>
+      </c>
+      <c r="C40" s="59" t="s">
+        <v>885</v>
+      </c>
+      <c r="D40" s="59" t="s">
         <v>886</v>
-      </c>
-      <c r="C40" s="58" t="s">
-        <v>887</v>
-      </c>
-      <c r="D40" s="58" t="s">
-        <v>888</v>
       </c>
       <c r="E40" s="35"/>
       <c r="F40" s="36" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="G40" s="37"/>
-      <c r="H40" s="44" t="s">
-        <v>890</v>
+      <c r="H40" s="45" t="s">
+        <v>888</v>
       </c>
       <c r="I40" s="37"/>
       <c r="J40" s="37" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="K40" s="37" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="L40" s="37"/>
       <c r="M40" s="37"/>
-      <c r="N40" s="44"/>
+      <c r="N40" s="45"/>
       <c r="O40" s="37"/>
       <c r="P40" s="37"/>
       <c r="Q40" s="37"/>
-      <c r="R40" s="54" t="s">
-        <v>893</v>
+      <c r="R40" s="55" t="s">
+        <v>891</v>
       </c>
       <c r="S40" s="37"/>
       <c r="T40" s="37"/>
       <c r="U40" s="37"/>
       <c r="V40" s="37" t="s">
+        <v>892</v>
+      </c>
+      <c r="W40" s="62" t="s">
+        <v>893</v>
+      </c>
+      <c r="X40" s="37" t="s">
         <v>894</v>
-      </c>
-      <c r="W40" s="61" t="s">
-        <v>895</v>
-      </c>
-      <c r="X40" s="37" t="s">
-        <v>896</v>
       </c>
       <c r="Y40" s="37"/>
       <c r="Z40" s="37" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="AA40" s="37"/>
       <c r="AB40" s="37"/>
       <c r="AC40" s="37"/>
-      <c r="AD40" s="44" t="s">
-        <v>898</v>
+      <c r="AD40" s="45" t="s">
+        <v>896</v>
       </c>
       <c r="AE40" s="37" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="AF40" s="37"/>
       <c r="AG40" s="37" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="AH40" s="36"/>
       <c r="AI40" s="37" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="AJ40" s="37"/>
       <c r="AK40" s="37"/>
       <c r="AL40" s="37" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="AM40" s="37"/>
       <c r="AN40" s="37"/>
@@ -23919,26 +24319,26 @@
       <c r="AU40" s="37"/>
       <c r="AV40" s="39"/>
       <c r="AW40" s="37" t="s">
+        <v>901</v>
+      </c>
+      <c r="AX40" s="37"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="59" t="s">
+        <v>104</v>
+      </c>
+      <c r="B41" s="59" t="s">
+        <v>902</v>
+      </c>
+      <c r="C41" s="59" t="s">
         <v>903</v>
       </c>
-      <c r="AX40" s="37"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="58" t="s">
-        <v>104</v>
-      </c>
-      <c r="B41" s="58" t="s">
+      <c r="D41" s="59" t="s">
         <v>904</v>
-      </c>
-      <c r="C41" s="58" t="s">
-        <v>905</v>
-      </c>
-      <c r="D41" s="58" t="s">
-        <v>906</v>
       </c>
       <c r="E41" s="35"/>
       <c r="F41" s="36" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="G41" s="37"/>
       <c r="H41" s="37"/>
@@ -23946,59 +24346,59 @@
       <c r="J41" s="37"/>
       <c r="K41" s="37"/>
       <c r="L41" s="37" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="M41" s="37"/>
-      <c r="N41" s="44"/>
+      <c r="N41" s="45"/>
       <c r="O41" s="37"/>
       <c r="P41" s="37"/>
       <c r="Q41" s="37"/>
-      <c r="R41" s="54" t="s">
-        <v>909</v>
+      <c r="R41" s="55" t="s">
+        <v>907</v>
       </c>
       <c r="S41" s="37"/>
       <c r="T41" s="37"/>
       <c r="U41" s="37"/>
       <c r="V41" s="37"/>
-      <c r="W41" s="62" t="s">
-        <v>910</v>
-      </c>
-      <c r="X41" s="50" t="s">
-        <v>911</v>
+      <c r="W41" s="63" t="s">
+        <v>908</v>
+      </c>
+      <c r="X41" s="51" t="s">
+        <v>909</v>
       </c>
       <c r="Y41" s="37"/>
       <c r="Z41" s="37"/>
       <c r="AA41" s="37"/>
       <c r="AB41" s="37" t="s">
+        <v>910</v>
+      </c>
+      <c r="AC41" s="41" t="s">
+        <v>911</v>
+      </c>
+      <c r="AD41" s="45" t="s">
         <v>912</v>
       </c>
-      <c r="AC41" s="41" t="s">
+      <c r="AE41" s="37" t="s">
         <v>913</v>
-      </c>
-      <c r="AD41" s="44" t="s">
-        <v>914</v>
-      </c>
-      <c r="AE41" s="37" t="s">
-        <v>915</v>
       </c>
       <c r="AF41" s="37"/>
       <c r="AG41" s="41" t="s">
-        <v>916</v>
-      </c>
-      <c r="AH41" s="63"/>
+        <v>914</v>
+      </c>
+      <c r="AH41" s="64"/>
       <c r="AI41" s="37" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="AJ41" s="37"/>
       <c r="AK41" s="37"/>
       <c r="AL41" s="37"/>
       <c r="AM41" s="37"/>
       <c r="AN41" s="37" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="AO41" s="37"/>
       <c r="AP41" s="37" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="AQ41" s="37"/>
       <c r="AR41" s="37"/>
@@ -24007,37 +24407,37 @@
       <c r="AU41" s="37"/>
       <c r="AV41" s="39"/>
       <c r="AW41" s="37" t="s">
+        <v>918</v>
+      </c>
+      <c r="AX41" s="37"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="59" t="s">
+        <v>104</v>
+      </c>
+      <c r="B42" s="59" t="s">
+        <v>902</v>
+      </c>
+      <c r="C42" s="59" t="s">
+        <v>919</v>
+      </c>
+      <c r="D42" s="59" t="s">
         <v>920</v>
-      </c>
-      <c r="AX41" s="37"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="58" t="s">
-        <v>104</v>
-      </c>
-      <c r="B42" s="58" t="s">
-        <v>904</v>
-      </c>
-      <c r="C42" s="58" t="s">
-        <v>921</v>
-      </c>
-      <c r="D42" s="58" t="s">
-        <v>922</v>
       </c>
       <c r="E42" s="35"/>
       <c r="F42" s="36" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="G42" s="37"/>
       <c r="H42" s="37"/>
       <c r="I42" s="37"/>
       <c r="J42" s="37" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="K42" s="37"/>
       <c r="L42" s="37"/>
       <c r="M42" s="37"/>
-      <c r="N42" s="44"/>
+      <c r="N42" s="45"/>
       <c r="O42" s="37"/>
       <c r="P42" s="37"/>
       <c r="Q42" s="37"/>
@@ -24050,131 +24450,131 @@
       <c r="X42" s="37"/>
       <c r="Y42" s="37"/>
       <c r="Z42" s="37" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="AA42" s="37"/>
       <c r="AB42" s="37" t="s">
+        <v>924</v>
+      </c>
+      <c r="AC42" s="37"/>
+      <c r="AD42" s="45" t="s">
+        <v>925</v>
+      </c>
+      <c r="AE42" s="37" t="s">
         <v>926</v>
-      </c>
-      <c r="AC42" s="37"/>
-      <c r="AD42" s="44" t="s">
-        <v>927</v>
-      </c>
-      <c r="AE42" s="37" t="s">
-        <v>928</v>
       </c>
       <c r="AF42" s="37"/>
       <c r="AG42" s="37" t="s">
+        <v>927</v>
+      </c>
+      <c r="AH42" s="36" t="s">
+        <v>928</v>
+      </c>
+      <c r="AI42" s="37" t="s">
         <v>929</v>
-      </c>
-      <c r="AH42" s="36" t="s">
-        <v>930</v>
-      </c>
-      <c r="AI42" s="37" t="s">
-        <v>931</v>
       </c>
       <c r="AJ42" s="37"/>
       <c r="AK42" s="37"/>
       <c r="AL42" s="37" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="AM42" s="37"/>
       <c r="AN42" s="37" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="AO42" s="37"/>
       <c r="AP42" s="37" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="AQ42" s="37" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="AR42" s="37"/>
       <c r="AS42" s="37"/>
       <c r="AT42" s="39"/>
       <c r="AU42" s="37"/>
       <c r="AV42" s="39" t="s">
+        <v>934</v>
+      </c>
+      <c r="AW42" s="37" t="s">
+        <v>935</v>
+      </c>
+      <c r="AX42" s="37"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="59" t="s">
+        <v>104</v>
+      </c>
+      <c r="B43" s="59" t="s">
+        <v>902</v>
+      </c>
+      <c r="C43" s="59" t="s">
         <v>936</v>
       </c>
-      <c r="AW42" s="37" t="s">
+      <c r="D43" s="59" t="s">
         <v>937</v>
-      </c>
-      <c r="AX42" s="37"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="58" t="s">
-        <v>104</v>
-      </c>
-      <c r="B43" s="58" t="s">
-        <v>904</v>
-      </c>
-      <c r="C43" s="58" t="s">
-        <v>938</v>
-      </c>
-      <c r="D43" s="58" t="s">
-        <v>939</v>
       </c>
       <c r="E43" s="35"/>
       <c r="F43" s="36" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="G43" s="37"/>
       <c r="H43" s="37"/>
       <c r="I43" s="37" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="J43" s="37" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="K43" s="37"/>
       <c r="L43" s="37"/>
       <c r="M43" s="37"/>
-      <c r="N43" s="44"/>
+      <c r="N43" s="45"/>
       <c r="O43" s="37"/>
       <c r="P43" s="37"/>
       <c r="Q43" s="37"/>
-      <c r="R43" s="64" t="s">
-        <v>943</v>
+      <c r="R43" s="65" t="s">
+        <v>941</v>
       </c>
       <c r="S43" s="37"/>
       <c r="T43" s="37" t="s">
+        <v>942</v>
+      </c>
+      <c r="U43" s="37" t="s">
+        <v>943</v>
+      </c>
+      <c r="V43" s="37"/>
+      <c r="W43" s="62" t="s">
         <v>944</v>
-      </c>
-      <c r="U43" s="37" t="s">
-        <v>945</v>
-      </c>
-      <c r="V43" s="37"/>
-      <c r="W43" s="61" t="s">
-        <v>946</v>
       </c>
       <c r="X43" s="37"/>
       <c r="Y43" s="37"/>
       <c r="Z43" s="37"/>
       <c r="AA43" s="37" t="s">
+        <v>945</v>
+      </c>
+      <c r="AB43" s="37" t="s">
+        <v>946</v>
+      </c>
+      <c r="AC43" s="37"/>
+      <c r="AD43" s="45" t="s">
         <v>947</v>
       </c>
-      <c r="AB43" s="37" t="s">
+      <c r="AE43" s="37" t="s">
         <v>948</v>
-      </c>
-      <c r="AC43" s="37"/>
-      <c r="AD43" s="44" t="s">
-        <v>949</v>
-      </c>
-      <c r="AE43" s="37" t="s">
-        <v>950</v>
       </c>
       <c r="AF43" s="37"/>
       <c r="AG43" s="37" t="s">
+        <v>949</v>
+      </c>
+      <c r="AH43" s="36" t="s">
+        <v>950</v>
+      </c>
+      <c r="AI43" s="37" t="s">
         <v>951</v>
       </c>
-      <c r="AH43" s="36" t="s">
+      <c r="AJ43" s="37" t="s">
         <v>952</v>
-      </c>
-      <c r="AI43" s="37" t="s">
-        <v>953</v>
-      </c>
-      <c r="AJ43" s="37" t="s">
-        <v>954</v>
       </c>
       <c r="AK43" s="37"/>
       <c r="AL43" s="37"/>
@@ -24188,83 +24588,83 @@
       <c r="AT43" s="39"/>
       <c r="AU43" s="37"/>
       <c r="AV43" s="39" t="s">
+        <v>953</v>
+      </c>
+      <c r="AW43" s="37" t="s">
+        <v>954</v>
+      </c>
+      <c r="AX43" s="37"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="59" t="s">
+        <v>104</v>
+      </c>
+      <c r="B44" s="59" t="s">
         <v>955</v>
       </c>
-      <c r="AW43" s="37" t="s">
+      <c r="C44" s="59" t="s">
         <v>956</v>
       </c>
-      <c r="AX43" s="37"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="58" t="s">
-        <v>104</v>
-      </c>
-      <c r="B44" s="58" t="s">
+      <c r="D44" s="59" t="s">
         <v>957</v>
       </c>
-      <c r="C44" s="58" t="s">
+      <c r="E44" s="35" t="s">
         <v>958</v>
       </c>
-      <c r="D44" s="58" t="s">
+      <c r="F44" s="36" t="s">
         <v>959</v>
-      </c>
-      <c r="E44" s="35" t="s">
-        <v>960</v>
-      </c>
-      <c r="F44" s="36" t="s">
-        <v>961</v>
       </c>
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
       <c r="I44" s="37"/>
       <c r="J44" s="37"/>
       <c r="K44" s="37" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="L44" s="37" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="M44" s="37"/>
-      <c r="N44" s="44"/>
+      <c r="N44" s="45"/>
       <c r="O44" s="37"/>
       <c r="P44" s="37"/>
       <c r="Q44" s="37"/>
       <c r="R44" s="37"/>
       <c r="S44" s="37" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="T44" s="37" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="U44" s="37"/>
       <c r="V44" s="37" t="s">
+        <v>964</v>
+      </c>
+      <c r="W44" s="62" t="s">
+        <v>965</v>
+      </c>
+      <c r="X44" s="51" t="s">
         <v>966</v>
-      </c>
-      <c r="W44" s="61" t="s">
-        <v>967</v>
-      </c>
-      <c r="X44" s="50" t="s">
-        <v>968</v>
       </c>
       <c r="Y44" s="37"/>
       <c r="Z44" s="37"/>
       <c r="AA44" s="37"/>
       <c r="AB44" s="37" t="s">
+        <v>967</v>
+      </c>
+      <c r="AC44" s="37"/>
+      <c r="AD44" s="45" t="s">
+        <v>968</v>
+      </c>
+      <c r="AE44" s="37" t="s">
         <v>969</v>
-      </c>
-      <c r="AC44" s="37"/>
-      <c r="AD44" s="44" t="s">
-        <v>970</v>
-      </c>
-      <c r="AE44" s="37" t="s">
-        <v>971</v>
       </c>
       <c r="AF44" s="37"/>
       <c r="AG44" s="37" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="AH44" s="36" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="AI44" s="37"/>
       <c r="AJ44" s="37"/>
@@ -24278,50 +24678,50 @@
       <c r="AR44" s="37"/>
       <c r="AS44" s="37"/>
       <c r="AT44" s="39"/>
-      <c r="AU44" s="52" t="s">
-        <v>974</v>
+      <c r="AU44" s="53" t="s">
+        <v>972</v>
       </c>
       <c r="AV44" s="39"/>
       <c r="AW44" s="37" t="s">
+        <v>973</v>
+      </c>
+      <c r="AX44" s="37"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="59" t="s">
+        <v>104</v>
+      </c>
+      <c r="B45" s="59" t="s">
+        <v>955</v>
+      </c>
+      <c r="C45" s="59" t="s">
+        <v>974</v>
+      </c>
+      <c r="D45" s="59" t="s">
         <v>975</v>
-      </c>
-      <c r="AX44" s="37"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="58" t="s">
-        <v>104</v>
-      </c>
-      <c r="B45" s="58" t="s">
-        <v>957</v>
-      </c>
-      <c r="C45" s="58" t="s">
-        <v>976</v>
-      </c>
-      <c r="D45" s="58" t="s">
-        <v>977</v>
       </c>
       <c r="E45" s="35"/>
       <c r="F45" s="36" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="G45" s="37"/>
       <c r="H45" s="41" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="I45" s="37"/>
       <c r="J45" s="37"/>
       <c r="K45" s="37" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="L45" s="37"/>
       <c r="M45" s="37"/>
-      <c r="N45" s="44"/>
+      <c r="N45" s="45"/>
       <c r="O45" s="37"/>
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
       <c r="R45" s="37"/>
       <c r="S45" s="37" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="T45" s="37"/>
       <c r="U45" s="37"/>
@@ -24330,27 +24730,27 @@
       <c r="X45" s="37"/>
       <c r="Y45" s="37"/>
       <c r="Z45" s="37" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="AA45" s="37"/>
       <c r="AB45" s="37" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="AC45" s="37"/>
       <c r="AD45" s="37"/>
       <c r="AE45" s="37" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="AF45" s="37"/>
       <c r="AG45" s="37"/>
-      <c r="AH45" s="63"/>
+      <c r="AH45" s="64"/>
       <c r="AI45" s="37"/>
       <c r="AJ45" s="37"/>
       <c r="AK45" s="37"/>
       <c r="AL45" s="37"/>
       <c r="AM45" s="37"/>
       <c r="AN45" s="37" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="AO45" s="37"/>
       <c r="AP45" s="37"/>
@@ -24360,98 +24760,98 @@
       <c r="AT45" s="39"/>
       <c r="AU45" s="37"/>
       <c r="AV45" s="39" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="AW45" s="37"/>
       <c r="AX45" s="37"/>
     </row>
     <row r="46">
-      <c r="A46" s="58" t="s">
+      <c r="A46" s="59" t="s">
         <v>104</v>
       </c>
-      <c r="B46" s="58" t="s">
-        <v>957</v>
-      </c>
-      <c r="C46" s="58" t="s">
-        <v>986</v>
-      </c>
-      <c r="D46" s="58" t="s">
-        <v>987</v>
+      <c r="B46" s="59" t="s">
+        <v>955</v>
+      </c>
+      <c r="C46" s="59" t="s">
+        <v>984</v>
+      </c>
+      <c r="D46" s="59" t="s">
+        <v>985</v>
       </c>
       <c r="E46" s="35"/>
       <c r="F46" s="36" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="G46" s="37" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="H46" s="37"/>
       <c r="I46" s="37" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="J46" s="37" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="K46" s="37"/>
       <c r="L46" s="37" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="M46" s="37"/>
-      <c r="N46" s="44"/>
+      <c r="N46" s="45"/>
       <c r="O46" s="37"/>
       <c r="P46" s="37"/>
       <c r="Q46" s="37"/>
-      <c r="R46" s="53" t="s">
-        <v>993</v>
+      <c r="R46" s="54" t="s">
+        <v>991</v>
       </c>
       <c r="S46" s="37"/>
       <c r="T46" s="37"/>
       <c r="U46" s="37" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="V46" s="37"/>
       <c r="W46" s="37"/>
-      <c r="X46" s="50" t="s">
-        <v>995</v>
+      <c r="X46" s="51" t="s">
+        <v>993</v>
       </c>
       <c r="Y46" s="37"/>
       <c r="Z46" s="37"/>
       <c r="AA46" s="37"/>
       <c r="AB46" s="37" t="s">
+        <v>994</v>
+      </c>
+      <c r="AC46" s="37" t="s">
+        <v>995</v>
+      </c>
+      <c r="AD46" s="45" t="s">
         <v>996</v>
       </c>
-      <c r="AC46" s="37" t="s">
+      <c r="AE46" s="37" t="s">
         <v>997</v>
-      </c>
-      <c r="AD46" s="44" t="s">
-        <v>998</v>
-      </c>
-      <c r="AE46" s="37" t="s">
-        <v>999</v>
       </c>
       <c r="AF46" s="37"/>
       <c r="AG46" s="37" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="AH46" s="36" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="AI46" s="37"/>
       <c r="AJ46" s="38" t="s">
+        <v>1000</v>
+      </c>
+      <c r="AK46" s="37" t="s">
+        <v>1001</v>
+      </c>
+      <c r="AL46" s="37" t="s">
         <v>1002</v>
-      </c>
-      <c r="AK46" s="37" t="s">
-        <v>1003</v>
-      </c>
-      <c r="AL46" s="37" t="s">
-        <v>1004</v>
       </c>
       <c r="AM46" s="37"/>
       <c r="AN46" s="37"/>
       <c r="AO46" s="37"/>
       <c r="AP46" s="37"/>
       <c r="AQ46" s="37" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="AR46" s="37"/>
       <c r="AS46" s="37"/>
@@ -24459,39 +24859,39 @@
       <c r="AU46" s="37"/>
       <c r="AV46" s="39"/>
       <c r="AW46" s="37" t="s">
+        <v>1004</v>
+      </c>
+      <c r="AX46" s="37"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="59" t="s">
+        <v>104</v>
+      </c>
+      <c r="B47" s="59" t="s">
+        <v>955</v>
+      </c>
+      <c r="C47" s="59" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D47" s="59" t="s">
         <v>1006</v>
-      </c>
-      <c r="AX46" s="37"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="58" t="s">
-        <v>104</v>
-      </c>
-      <c r="B47" s="58" t="s">
-        <v>957</v>
-      </c>
-      <c r="C47" s="58" t="s">
-        <v>1007</v>
-      </c>
-      <c r="D47" s="58" t="s">
-        <v>1008</v>
       </c>
       <c r="E47" s="35"/>
       <c r="F47" s="36"/>
       <c r="G47" s="37"/>
       <c r="H47" s="37" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="I47" s="37"/>
       <c r="J47" s="37" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="K47" s="37"/>
       <c r="L47" s="37"/>
       <c r="M47" s="37"/>
-      <c r="N47" s="44"/>
+      <c r="N47" s="45"/>
       <c r="O47" s="37" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="P47" s="37"/>
       <c r="Q47" s="37"/>
@@ -24500,11 +24900,11 @@
       <c r="T47" s="37"/>
       <c r="U47" s="37"/>
       <c r="V47" s="37"/>
-      <c r="W47" s="48" t="s">
-        <v>1012</v>
-      </c>
-      <c r="X47" s="50" t="s">
-        <v>1013</v>
+      <c r="W47" s="49" t="s">
+        <v>1010</v>
+      </c>
+      <c r="X47" s="51" t="s">
+        <v>1011</v>
       </c>
       <c r="Y47" s="37"/>
       <c r="Z47" s="37"/>
@@ -24513,19 +24913,19 @@
       <c r="AC47" s="37"/>
       <c r="AD47" s="37"/>
       <c r="AE47" s="37" t="s">
+        <v>1012</v>
+      </c>
+      <c r="AF47" s="37" t="s">
+        <v>1013</v>
+      </c>
+      <c r="AG47" s="37" t="s">
         <v>1014</v>
       </c>
-      <c r="AF47" s="37" t="s">
-        <v>1015</v>
-      </c>
-      <c r="AG47" s="37" t="s">
-        <v>1016</v>
-      </c>
-      <c r="AH47" s="63"/>
+      <c r="AH47" s="64"/>
       <c r="AI47" s="37"/>
       <c r="AJ47" s="37"/>
       <c r="AK47" s="37" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="AL47" s="37"/>
       <c r="AM47" s="37"/>
@@ -24533,12 +24933,12 @@
       <c r="AO47" s="37"/>
       <c r="AP47" s="37"/>
       <c r="AQ47" s="37" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="AR47" s="37"/>
       <c r="AS47" s="37"/>
       <c r="AT47" s="39" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="AU47" s="37"/>
       <c r="AV47" s="39"/>
@@ -24546,21 +24946,21 @@
       <c r="AX47" s="37"/>
     </row>
     <row r="48">
-      <c r="A48" s="58" t="s">
+      <c r="A48" s="59" t="s">
         <v>104</v>
       </c>
-      <c r="B48" s="58" t="s">
-        <v>1020</v>
-      </c>
-      <c r="C48" s="58" t="s">
-        <v>1021</v>
-      </c>
-      <c r="D48" s="58" t="s">
-        <v>883</v>
+      <c r="B48" s="59" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C48" s="59" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D48" s="59" t="s">
+        <v>881</v>
       </c>
       <c r="E48" s="35"/>
       <c r="F48" s="36" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="G48" s="37"/>
       <c r="H48" s="37"/>
@@ -24569,7 +24969,7 @@
       <c r="K48" s="37"/>
       <c r="L48" s="37"/>
       <c r="M48" s="37"/>
-      <c r="N48" s="44"/>
+      <c r="N48" s="45"/>
       <c r="O48" s="37"/>
       <c r="P48" s="37"/>
       <c r="Q48" s="37"/>
@@ -24589,8 +24989,8 @@
       <c r="AE48" s="37"/>
       <c r="AF48" s="37"/>
       <c r="AG48" s="37"/>
-      <c r="AH48" s="65" t="s">
-        <v>1023</v>
+      <c r="AH48" s="66" t="s">
+        <v>1021</v>
       </c>
       <c r="AI48" s="37"/>
       <c r="AJ48" s="37"/>
@@ -24610,41 +25010,41 @@
       <c r="AX48" s="37"/>
     </row>
     <row r="49">
-      <c r="A49" s="58" t="s">
+      <c r="A49" s="59" t="s">
         <v>104</v>
       </c>
-      <c r="B49" s="58" t="s">
+      <c r="B49" s="59" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C49" s="59" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D49" s="59" t="s">
+        <v>886</v>
+      </c>
+      <c r="E49" s="40" t="s">
         <v>1024</v>
       </c>
-      <c r="C49" s="58" t="s">
-        <v>1025</v>
-      </c>
-      <c r="D49" s="58" t="s">
+      <c r="F49" s="36" t="s">
+        <v>882</v>
+      </c>
+      <c r="G49" s="37"/>
+      <c r="H49" s="45" t="s">
         <v>888</v>
-      </c>
-      <c r="E49" s="40" t="s">
-        <v>1026</v>
-      </c>
-      <c r="F49" s="36" t="s">
-        <v>884</v>
-      </c>
-      <c r="G49" s="37"/>
-      <c r="H49" s="44" t="s">
-        <v>890</v>
       </c>
       <c r="I49" s="37"/>
       <c r="J49" s="37"/>
       <c r="K49" s="37" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="L49" s="37"/>
       <c r="M49" s="41"/>
-      <c r="N49" s="44"/>
+      <c r="N49" s="45"/>
       <c r="O49" s="37"/>
       <c r="P49" s="37"/>
       <c r="Q49" s="37"/>
-      <c r="R49" s="54" t="s">
-        <v>1027</v>
+      <c r="R49" s="55" t="s">
+        <v>1025</v>
       </c>
       <c r="S49" s="37"/>
       <c r="T49" s="37"/>
@@ -24654,26 +25054,26 @@
       <c r="X49" s="37"/>
       <c r="Y49" s="37"/>
       <c r="Z49" s="37" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="AA49" s="37"/>
       <c r="AB49" s="37"/>
       <c r="AC49" s="37"/>
-      <c r="AD49" s="44" t="s">
-        <v>898</v>
+      <c r="AD49" s="45" t="s">
+        <v>896</v>
       </c>
       <c r="AE49" s="37"/>
       <c r="AF49" s="37"/>
       <c r="AG49" s="37" t="s">
-        <v>900</v>
-      </c>
-      <c r="AH49" s="66"/>
+        <v>898</v>
+      </c>
+      <c r="AH49" s="67"/>
       <c r="AI49" s="37"/>
       <c r="AJ49" s="37"/>
       <c r="AK49" s="37"/>
       <c r="AL49" s="37"/>
       <c r="AM49" s="37" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="AN49" s="37"/>
       <c r="AO49" s="37"/>
@@ -24688,41 +25088,41 @@
       <c r="AX49" s="37"/>
     </row>
     <row r="50">
-      <c r="A50" s="58" t="s">
+      <c r="A50" s="59" t="s">
         <v>104</v>
       </c>
-      <c r="B50" s="58" t="s">
-        <v>1024</v>
-      </c>
-      <c r="C50" s="58" t="s">
-        <v>1029</v>
-      </c>
-      <c r="D50" s="58" t="s">
-        <v>906</v>
+      <c r="B50" s="59" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C50" s="59" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D50" s="59" t="s">
+        <v>904</v>
       </c>
       <c r="E50" s="35"/>
       <c r="F50" s="36" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="G50" s="37" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="H50" s="37"/>
       <c r="I50" s="37"/>
       <c r="J50" s="37"/>
       <c r="K50" s="37"/>
       <c r="L50" s="37" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="M50" s="37"/>
-      <c r="N50" s="44" t="s">
-        <v>1032</v>
+      <c r="N50" s="45" t="s">
+        <v>1030</v>
       </c>
       <c r="O50" s="37"/>
       <c r="P50" s="37"/>
       <c r="Q50" s="37"/>
-      <c r="R50" s="54" t="s">
-        <v>1033</v>
+      <c r="R50" s="55" t="s">
+        <v>1031</v>
       </c>
       <c r="S50" s="37"/>
       <c r="T50" s="37"/>
@@ -24734,18 +25134,18 @@
       <c r="Z50" s="37"/>
       <c r="AA50" s="37"/>
       <c r="AB50" s="37" t="s">
+        <v>910</v>
+      </c>
+      <c r="AC50" s="37"/>
+      <c r="AD50" s="45" t="s">
         <v>912</v>
-      </c>
-      <c r="AC50" s="37"/>
-      <c r="AD50" s="44" t="s">
-        <v>914</v>
       </c>
       <c r="AE50" s="37"/>
       <c r="AF50" s="37"/>
       <c r="AG50" s="37" t="s">
-        <v>1034</v>
-      </c>
-      <c r="AH50" s="66"/>
+        <v>1032</v>
+      </c>
+      <c r="AH50" s="67"/>
       <c r="AI50" s="37"/>
       <c r="AJ50" s="37"/>
       <c r="AK50" s="37"/>
@@ -24755,7 +25155,7 @@
       <c r="AO50" s="37"/>
       <c r="AP50" s="37"/>
       <c r="AQ50" s="37" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="AR50" s="37"/>
       <c r="AS50" s="37"/>
@@ -24766,21 +25166,21 @@
       <c r="AX50" s="37"/>
     </row>
     <row r="51">
-      <c r="A51" s="58" t="s">
+      <c r="A51" s="59" t="s">
         <v>104</v>
       </c>
-      <c r="B51" s="58" t="s">
-        <v>1024</v>
-      </c>
-      <c r="C51" s="58" t="s">
-        <v>1036</v>
-      </c>
-      <c r="D51" s="58" t="s">
-        <v>922</v>
+      <c r="B51" s="59" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C51" s="59" t="s">
+        <v>1034</v>
+      </c>
+      <c r="D51" s="59" t="s">
+        <v>920</v>
       </c>
       <c r="E51" s="35"/>
       <c r="F51" s="36" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="G51" s="37"/>
       <c r="H51" s="37"/>
@@ -24789,14 +25189,14 @@
       <c r="K51" s="37"/>
       <c r="L51" s="37"/>
       <c r="M51" s="37"/>
-      <c r="N51" s="44"/>
+      <c r="N51" s="45"/>
       <c r="O51" s="37"/>
       <c r="P51" s="37"/>
       <c r="Q51" s="37"/>
       <c r="R51" s="37"/>
       <c r="S51" s="37"/>
       <c r="T51" s="37" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="U51" s="37"/>
       <c r="V51" s="37"/>
@@ -24804,22 +25204,22 @@
       <c r="X51" s="37"/>
       <c r="Y51" s="37"/>
       <c r="Z51" s="37" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="AA51" s="37"/>
       <c r="AB51" s="37" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="AC51" s="37"/>
-      <c r="AD51" s="44" t="s">
-        <v>927</v>
+      <c r="AD51" s="45" t="s">
+        <v>925</v>
       </c>
       <c r="AE51" s="37"/>
       <c r="AF51" s="37"/>
       <c r="AG51" s="37" t="s">
-        <v>929</v>
-      </c>
-      <c r="AH51" s="66"/>
+        <v>927</v>
+      </c>
+      <c r="AH51" s="67"/>
       <c r="AI51" s="37"/>
       <c r="AJ51" s="37"/>
       <c r="AK51" s="37"/>
@@ -24829,7 +25229,7 @@
       <c r="AO51" s="37"/>
       <c r="AP51" s="37"/>
       <c r="AQ51" s="37" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="AR51" s="37"/>
       <c r="AS51" s="37"/>
@@ -24840,23 +25240,23 @@
       <c r="AX51" s="37"/>
     </row>
     <row r="52">
-      <c r="A52" s="58" t="s">
+      <c r="A52" s="59" t="s">
         <v>104</v>
       </c>
-      <c r="B52" s="58" t="s">
-        <v>1024</v>
-      </c>
-      <c r="C52" s="58" t="s">
-        <v>1039</v>
-      </c>
-      <c r="D52" s="58" t="s">
-        <v>939</v>
+      <c r="B52" s="59" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C52" s="59" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D52" s="59" t="s">
+        <v>937</v>
       </c>
       <c r="E52" s="40" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="F52" s="36" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="G52" s="37"/>
       <c r="H52" s="37"/>
@@ -24865,8 +25265,8 @@
       <c r="K52" s="37"/>
       <c r="L52" s="37"/>
       <c r="M52" s="37"/>
-      <c r="N52" s="46" t="s">
-        <v>1041</v>
+      <c r="N52" s="47" t="s">
+        <v>1039</v>
       </c>
       <c r="O52" s="37"/>
       <c r="P52" s="37"/>
@@ -24882,18 +25282,18 @@
       <c r="Z52" s="37"/>
       <c r="AA52" s="37"/>
       <c r="AB52" s="37" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="AC52" s="37"/>
-      <c r="AD52" s="44" t="s">
-        <v>949</v>
+      <c r="AD52" s="45" t="s">
+        <v>947</v>
       </c>
       <c r="AE52" s="37"/>
       <c r="AF52" s="37"/>
       <c r="AG52" s="37" t="s">
-        <v>951</v>
-      </c>
-      <c r="AH52" s="66"/>
+        <v>949</v>
+      </c>
+      <c r="AH52" s="67"/>
       <c r="AI52" s="37"/>
       <c r="AJ52" s="37"/>
       <c r="AK52" s="37"/>
@@ -24912,36 +25312,36 @@
       <c r="AX52" s="37"/>
     </row>
     <row r="53">
-      <c r="A53" s="58" t="s">
+      <c r="A53" s="59" t="s">
         <v>104</v>
       </c>
-      <c r="B53" s="58" t="s">
-        <v>1042</v>
-      </c>
-      <c r="C53" s="58" t="s">
-        <v>1043</v>
-      </c>
-      <c r="D53" s="58" t="s">
-        <v>959</v>
+      <c r="B53" s="59" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C53" s="59" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D53" s="59" t="s">
+        <v>957</v>
       </c>
       <c r="E53" s="35"/>
       <c r="F53" s="36" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="G53" s="37"/>
       <c r="H53" s="37"/>
       <c r="I53" s="37"/>
       <c r="J53" s="37"/>
       <c r="K53" s="37" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="L53" s="37" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="M53" s="37" t="s">
-        <v>1044</v>
-      </c>
-      <c r="N53" s="46"/>
+        <v>1042</v>
+      </c>
+      <c r="N53" s="47"/>
       <c r="O53" s="37"/>
       <c r="P53" s="37"/>
       <c r="Q53" s="37"/>
@@ -24956,18 +25356,18 @@
       <c r="Z53" s="37"/>
       <c r="AA53" s="37"/>
       <c r="AB53" s="37" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="AC53" s="37"/>
-      <c r="AD53" s="44" t="s">
-        <v>970</v>
+      <c r="AD53" s="45" t="s">
+        <v>968</v>
       </c>
       <c r="AE53" s="37"/>
       <c r="AF53" s="37"/>
       <c r="AG53" s="37" t="s">
-        <v>972</v>
-      </c>
-      <c r="AH53" s="66"/>
+        <v>970</v>
+      </c>
+      <c r="AH53" s="67"/>
       <c r="AI53" s="37"/>
       <c r="AJ53" s="37"/>
       <c r="AK53" s="37"/>
@@ -24986,35 +25386,35 @@
       <c r="AX53" s="37"/>
     </row>
     <row r="54">
-      <c r="A54" s="58" t="s">
+      <c r="A54" s="59" t="s">
         <v>104</v>
       </c>
-      <c r="B54" s="58" t="s">
-        <v>1042</v>
-      </c>
-      <c r="C54" s="58" t="s">
-        <v>1045</v>
-      </c>
-      <c r="D54" s="58" t="s">
-        <v>977</v>
+      <c r="B54" s="59" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C54" s="59" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D54" s="59" t="s">
+        <v>975</v>
       </c>
       <c r="E54" s="35"/>
       <c r="F54" s="36" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="G54" s="37"/>
       <c r="H54" s="41" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="I54" s="37"/>
       <c r="J54" s="37"/>
       <c r="K54" s="37" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="L54" s="37"/>
       <c r="M54" s="37"/>
-      <c r="N54" s="46" t="s">
-        <v>1047</v>
+      <c r="N54" s="47" t="s">
+        <v>1045</v>
       </c>
       <c r="O54" s="37"/>
       <c r="P54" s="37"/>
@@ -25028,18 +25428,18 @@
       <c r="X54" s="37"/>
       <c r="Y54" s="37"/>
       <c r="Z54" s="37" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="AA54" s="37"/>
       <c r="AB54" s="37" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="AC54" s="37"/>
       <c r="AD54" s="37"/>
       <c r="AE54" s="37"/>
       <c r="AF54" s="37"/>
       <c r="AG54" s="37"/>
-      <c r="AH54" s="66"/>
+      <c r="AH54" s="67"/>
       <c r="AI54" s="37"/>
       <c r="AJ54" s="37"/>
       <c r="AK54" s="37"/>
@@ -25058,23 +25458,23 @@
       <c r="AX54" s="37"/>
     </row>
     <row r="55">
-      <c r="A55" s="58" t="s">
+      <c r="A55" s="59" t="s">
         <v>104</v>
       </c>
-      <c r="B55" s="58" t="s">
-        <v>1042</v>
-      </c>
-      <c r="C55" s="58" t="s">
+      <c r="B55" s="59" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C55" s="59" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D55" s="59" t="s">
+        <v>985</v>
+      </c>
+      <c r="E55" s="40" t="s">
+        <v>1047</v>
+      </c>
+      <c r="F55" s="36" t="s">
         <v>1048</v>
-      </c>
-      <c r="D55" s="58" t="s">
-        <v>987</v>
-      </c>
-      <c r="E55" s="40" t="s">
-        <v>1049</v>
-      </c>
-      <c r="F55" s="36" t="s">
-        <v>1050</v>
       </c>
       <c r="G55" s="37"/>
       <c r="H55" s="37"/>
@@ -25082,11 +25482,11 @@
       <c r="J55" s="37"/>
       <c r="K55" s="37"/>
       <c r="L55" s="37" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="M55" s="37"/>
-      <c r="N55" s="46" t="s">
-        <v>1051</v>
+      <c r="N55" s="47" t="s">
+        <v>1049</v>
       </c>
       <c r="O55" s="37"/>
       <c r="P55" s="37"/>
@@ -25102,18 +25502,18 @@
       <c r="Z55" s="37"/>
       <c r="AA55" s="37"/>
       <c r="AB55" s="37" t="s">
+        <v>994</v>
+      </c>
+      <c r="AC55" s="37"/>
+      <c r="AD55" s="45" t="s">
         <v>996</v>
-      </c>
-      <c r="AC55" s="37"/>
-      <c r="AD55" s="44" t="s">
-        <v>998</v>
       </c>
       <c r="AE55" s="37"/>
       <c r="AF55" s="37"/>
       <c r="AG55" s="37" t="s">
-        <v>1000</v>
-      </c>
-      <c r="AH55" s="66"/>
+        <v>998</v>
+      </c>
+      <c r="AH55" s="67"/>
       <c r="AI55" s="37"/>
       <c r="AJ55" s="37"/>
       <c r="AK55" s="37"/>
@@ -25132,32 +25532,32 @@
       <c r="AX55" s="37"/>
     </row>
     <row r="56">
-      <c r="A56" s="58" t="s">
+      <c r="A56" s="59" t="s">
         <v>104</v>
       </c>
-      <c r="B56" s="58" t="s">
-        <v>1042</v>
-      </c>
-      <c r="C56" s="58" t="s">
-        <v>1052</v>
-      </c>
-      <c r="D56" s="58" t="s">
-        <v>1008</v>
+      <c r="B56" s="59" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C56" s="59" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D56" s="59" t="s">
+        <v>1006</v>
       </c>
       <c r="E56" s="35"/>
       <c r="F56" s="36" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="G56" s="37"/>
       <c r="H56" s="37" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="I56" s="37"/>
       <c r="J56" s="37"/>
       <c r="K56" s="37"/>
       <c r="L56" s="37"/>
       <c r="M56" s="37"/>
-      <c r="N56" s="44"/>
+      <c r="N56" s="45"/>
       <c r="O56" s="37"/>
       <c r="P56" s="37"/>
       <c r="Q56" s="37"/>
@@ -25177,9 +25577,9 @@
       <c r="AE56" s="37"/>
       <c r="AF56" s="37"/>
       <c r="AG56" s="37" t="s">
-        <v>1016</v>
-      </c>
-      <c r="AH56" s="67"/>
+        <v>1014</v>
+      </c>
+      <c r="AH56" s="68"/>
       <c r="AI56" s="37"/>
       <c r="AJ56" s="37"/>
       <c r="AK56" s="37"/>
@@ -25198,16 +25598,16 @@
       <c r="AX56" s="37"/>
     </row>
     <row r="57">
-      <c r="A57" s="58" t="s">
+      <c r="A57" s="59" t="s">
         <v>104</v>
       </c>
-      <c r="B57" s="58" t="s">
-        <v>1053</v>
-      </c>
-      <c r="C57" s="58" t="s">
-        <v>1054</v>
-      </c>
-      <c r="D57" s="58" t="s">
+      <c r="B57" s="59" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C57" s="59" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D57" s="59" t="s">
         <v>138</v>
       </c>
       <c r="E57" s="35"/>
@@ -25216,126 +25616,126 @@
       <c r="H57" s="37"/>
       <c r="I57" s="37"/>
       <c r="J57" s="37" t="s">
+        <v>1053</v>
+      </c>
+      <c r="K57" s="37" t="s">
+        <v>1054</v>
+      </c>
+      <c r="L57" s="37" t="s">
         <v>1055</v>
       </c>
-      <c r="K57" s="37" t="s">
+      <c r="M57" s="37" t="s">
         <v>1056</v>
       </c>
-      <c r="L57" s="37" t="s">
+      <c r="N57" s="47" t="s">
         <v>1057</v>
-      </c>
-      <c r="M57" s="37" t="s">
-        <v>1058</v>
-      </c>
-      <c r="N57" s="46" t="s">
-        <v>1059</v>
       </c>
       <c r="O57" s="37"/>
       <c r="P57" s="41" t="s">
+        <v>1058</v>
+      </c>
+      <c r="Q57" s="37"/>
+      <c r="R57" s="54" t="s">
+        <v>1059</v>
+      </c>
+      <c r="S57" s="37" t="s">
         <v>1060</v>
-      </c>
-      <c r="Q57" s="37"/>
-      <c r="R57" s="53" t="s">
-        <v>1061</v>
-      </c>
-      <c r="S57" s="37" t="s">
-        <v>1062</v>
       </c>
       <c r="T57" s="37"/>
       <c r="U57" s="37"/>
       <c r="V57" s="37"/>
-      <c r="W57" s="61" t="s">
+      <c r="W57" s="62" t="s">
+        <v>1061</v>
+      </c>
+      <c r="X57" s="51" t="s">
+        <v>1062</v>
+      </c>
+      <c r="Y57" s="37" t="s">
         <v>1063</v>
-      </c>
-      <c r="X57" s="50" t="s">
-        <v>1064</v>
-      </c>
-      <c r="Y57" s="37" t="s">
-        <v>1065</v>
       </c>
       <c r="Z57" s="37"/>
       <c r="AA57" s="37" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="AB57" s="37"/>
       <c r="AC57" s="37"/>
-      <c r="AD57" s="44" t="s">
+      <c r="AD57" s="45" t="s">
+        <v>1065</v>
+      </c>
+      <c r="AE57" s="37" t="s">
+        <v>1066</v>
+      </c>
+      <c r="AF57" s="37" t="s">
         <v>1067</v>
       </c>
-      <c r="AE57" s="37" t="s">
+      <c r="AG57" s="37" t="s">
         <v>1068</v>
       </c>
-      <c r="AF57" s="37" t="s">
+      <c r="AH57" s="36" t="s">
         <v>1069</v>
-      </c>
-      <c r="AG57" s="37" t="s">
-        <v>1070</v>
-      </c>
-      <c r="AH57" s="36" t="s">
-        <v>1071</v>
       </c>
       <c r="AI57" s="37"/>
       <c r="AJ57" s="37" t="s">
+        <v>1070</v>
+      </c>
+      <c r="AK57" s="37" t="s">
+        <v>1071</v>
+      </c>
+      <c r="AL57" s="37" t="s">
         <v>1072</v>
       </c>
-      <c r="AK57" s="37" t="s">
+      <c r="AM57" s="37" t="s">
         <v>1073</v>
       </c>
-      <c r="AL57" s="37" t="s">
+      <c r="AN57" s="37" t="s">
         <v>1074</v>
-      </c>
-      <c r="AM57" s="37" t="s">
-        <v>1075</v>
-      </c>
-      <c r="AN57" s="37" t="s">
-        <v>1076</v>
       </c>
       <c r="AO57" s="37"/>
       <c r="AP57" s="37"/>
       <c r="AQ57" s="37" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="AR57" s="37"/>
       <c r="AS57" s="37"/>
       <c r="AT57" s="39"/>
-      <c r="AU57" s="49" t="s">
+      <c r="AU57" s="50" t="s">
+        <v>1076</v>
+      </c>
+      <c r="AV57" s="39" t="s">
+        <v>1077</v>
+      </c>
+      <c r="AW57" s="37" t="s">
         <v>1078</v>
       </c>
-      <c r="AV57" s="39" t="s">
+      <c r="AX57" s="37"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="59" t="s">
+        <v>104</v>
+      </c>
+      <c r="B58" s="59" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C58" s="59" t="s">
         <v>1079</v>
       </c>
-      <c r="AW57" s="37" t="s">
+      <c r="D58" s="59" t="s">
         <v>1080</v>
       </c>
-      <c r="AX57" s="37"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="58" t="s">
-        <v>104</v>
-      </c>
-      <c r="B58" s="58" t="s">
-        <v>1053</v>
-      </c>
-      <c r="C58" s="58" t="s">
+      <c r="E58" s="40" t="s">
         <v>1081</v>
-      </c>
-      <c r="D58" s="58" t="s">
-        <v>1082</v>
-      </c>
-      <c r="E58" s="40" t="s">
-        <v>1083</v>
       </c>
       <c r="F58" s="36"/>
       <c r="G58" s="37"/>
       <c r="H58" s="37"/>
       <c r="I58" s="37"/>
       <c r="J58" s="37" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="K58" s="37"/>
       <c r="L58" s="37"/>
       <c r="M58" s="37"/>
-      <c r="N58" s="44"/>
+      <c r="N58" s="45"/>
       <c r="O58" s="37"/>
       <c r="P58" s="8"/>
       <c r="Q58" s="37"/>
@@ -25344,8 +25744,8 @@
       <c r="T58" s="37"/>
       <c r="U58" s="37"/>
       <c r="V58" s="37"/>
-      <c r="W58" s="61" t="s">
-        <v>1085</v>
+      <c r="W58" s="62" t="s">
+        <v>1083</v>
       </c>
       <c r="X58" s="37"/>
       <c r="Y58" s="37"/>
@@ -25353,58 +25753,58 @@
       <c r="AA58" s="37"/>
       <c r="AB58" s="37"/>
       <c r="AC58" s="37"/>
-      <c r="AD58" s="44" t="s">
-        <v>1086</v>
+      <c r="AD58" s="45" t="s">
+        <v>1084</v>
       </c>
       <c r="AE58" s="37"/>
       <c r="AF58" s="37"/>
       <c r="AG58" s="37"/>
-      <c r="AH58" s="63"/>
+      <c r="AH58" s="64"/>
       <c r="AI58" s="37"/>
       <c r="AJ58" s="37"/>
       <c r="AK58" s="37" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="AL58" s="37"/>
       <c r="AM58" s="37"/>
       <c r="AN58" s="37"/>
       <c r="AO58" s="37"/>
       <c r="AP58" s="37" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="AQ58" s="37" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="AR58" s="37"/>
       <c r="AS58" s="37"/>
       <c r="AT58" s="39" t="s">
-        <v>1089</v>
-      </c>
-      <c r="AU58" s="52" t="s">
-        <v>1090</v>
+        <v>1087</v>
+      </c>
+      <c r="AU58" s="53" t="s">
+        <v>1088</v>
       </c>
       <c r="AV58" s="39"/>
       <c r="AW58" s="37" t="s">
+        <v>1089</v>
+      </c>
+      <c r="AX58" s="37"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="59" t="s">
+        <v>104</v>
+      </c>
+      <c r="B59" s="59" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C59" s="59" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D59" s="59" t="s">
         <v>1091</v>
-      </c>
-      <c r="AX58" s="37"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="58" t="s">
-        <v>104</v>
-      </c>
-      <c r="B59" s="58" t="s">
-        <v>1053</v>
-      </c>
-      <c r="C59" s="58" t="s">
-        <v>1092</v>
-      </c>
-      <c r="D59" s="58" t="s">
-        <v>1093</v>
       </c>
       <c r="E59" s="35"/>
       <c r="F59" s="36" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="G59" s="37"/>
       <c r="H59" s="37"/>
@@ -25413,16 +25813,16 @@
       <c r="K59" s="37"/>
       <c r="L59" s="37"/>
       <c r="M59" s="37"/>
-      <c r="N59" s="44"/>
+      <c r="N59" s="45"/>
       <c r="O59" s="37"/>
       <c r="P59" s="41" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="Q59" s="37"/>
       <c r="R59" s="37"/>
       <c r="S59" s="37"/>
       <c r="T59" s="37" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="U59" s="37"/>
       <c r="V59" s="37"/>
@@ -25437,14 +25837,14 @@
       <c r="AE59" s="37"/>
       <c r="AF59" s="37"/>
       <c r="AG59" s="37"/>
-      <c r="AH59" s="63"/>
+      <c r="AH59" s="64"/>
       <c r="AI59" s="37"/>
       <c r="AJ59" s="37"/>
       <c r="AK59" s="37"/>
       <c r="AL59" s="37"/>
       <c r="AM59" s="37"/>
       <c r="AN59" s="37" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="AO59" s="37"/>
       <c r="AP59" s="37"/>
@@ -25455,92 +25855,92 @@
       <c r="AU59" s="37"/>
       <c r="AV59" s="39"/>
       <c r="AW59" s="37" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AX59" s="37"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="59" t="s">
+        <v>104</v>
+      </c>
+      <c r="B60" s="59" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C60" s="59" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D60" s="59" t="s">
         <v>1098</v>
       </c>
-      <c r="AX59" s="37"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="58" t="s">
-        <v>104</v>
-      </c>
-      <c r="B60" s="58" t="s">
-        <v>1053</v>
-      </c>
-      <c r="C60" s="58" t="s">
+      <c r="E60" s="35" t="s">
         <v>1099</v>
       </c>
-      <c r="D60" s="58" t="s">
+      <c r="F60" s="36" t="s">
         <v>1100</v>
-      </c>
-      <c r="E60" s="35" t="s">
-        <v>1101</v>
-      </c>
-      <c r="F60" s="36" t="s">
-        <v>1102</v>
       </c>
       <c r="G60" s="37"/>
       <c r="H60" s="37"/>
       <c r="I60" s="37" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="J60" s="37" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="K60" s="37"/>
       <c r="L60" s="37"/>
       <c r="M60" s="37"/>
-      <c r="N60" s="44"/>
+      <c r="N60" s="45"/>
       <c r="O60" s="37"/>
       <c r="P60" s="41" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="Q60" s="37"/>
       <c r="R60" s="37"/>
       <c r="S60" s="37"/>
       <c r="T60" s="37"/>
       <c r="U60" s="37" t="s">
+        <v>1104</v>
+      </c>
+      <c r="V60" s="37" t="s">
+        <v>1105</v>
+      </c>
+      <c r="W60" s="49" t="s">
         <v>1106</v>
-      </c>
-      <c r="V60" s="37" t="s">
-        <v>1107</v>
-      </c>
-      <c r="W60" s="48" t="s">
-        <v>1108</v>
       </c>
       <c r="X60" s="37"/>
       <c r="Y60" s="37"/>
       <c r="Z60" s="37"/>
       <c r="AA60" s="37" t="s">
+        <v>1107</v>
+      </c>
+      <c r="AB60" s="37" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC60" s="37"/>
+      <c r="AD60" s="45" t="s">
         <v>1109</v>
-      </c>
-      <c r="AB60" s="37" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC60" s="37"/>
-      <c r="AD60" s="44" t="s">
-        <v>1111</v>
       </c>
       <c r="AE60" s="37"/>
       <c r="AF60" s="37" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="AG60" s="37"/>
       <c r="AH60" s="36" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="AI60" s="37"/>
       <c r="AJ60" s="37"/>
       <c r="AK60" s="37"/>
       <c r="AL60" s="37" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="AM60" s="37"/>
       <c r="AN60" s="37" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="AO60" s="37"/>
       <c r="AP60" s="37" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="AQ60" s="37"/>
       <c r="AR60" s="37"/>
@@ -25552,78 +25952,78 @@
       <c r="AX60" s="37"/>
     </row>
     <row r="61">
-      <c r="A61" s="68" t="s">
+      <c r="A61" s="69" t="s">
         <v>166</v>
       </c>
-      <c r="B61" s="68" t="s">
-        <v>340</v>
-      </c>
-      <c r="C61" s="68" t="s">
-        <v>1117</v>
-      </c>
-      <c r="D61" s="68" t="s">
+      <c r="B61" s="69" t="s">
+        <v>338</v>
+      </c>
+      <c r="C61" s="69" t="s">
+        <v>1115</v>
+      </c>
+      <c r="D61" s="69" t="s">
         <v>168</v>
       </c>
       <c r="E61" s="35"/>
       <c r="F61" s="36" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="G61" s="37" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="H61" s="37"/>
       <c r="I61" s="37" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="J61" s="37"/>
       <c r="K61" s="37"/>
       <c r="L61" s="37"/>
       <c r="M61" s="37"/>
-      <c r="N61" s="44"/>
+      <c r="N61" s="45"/>
       <c r="O61" s="37"/>
       <c r="P61" s="37"/>
       <c r="Q61" s="37"/>
-      <c r="R61" s="53" t="s">
-        <v>1121</v>
+      <c r="R61" s="54" t="s">
+        <v>1119</v>
       </c>
       <c r="S61" s="37"/>
       <c r="T61" s="37"/>
       <c r="U61" s="37"/>
       <c r="V61" s="37" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="W61" s="37"/>
-      <c r="X61" s="50" t="s">
-        <v>1123</v>
+      <c r="X61" s="51" t="s">
+        <v>1121</v>
       </c>
       <c r="Y61" s="37"/>
       <c r="Z61" s="37" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="AA61" s="37"/>
       <c r="AB61" s="37" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AC61" s="37" t="s">
+        <v>1124</v>
+      </c>
+      <c r="AD61" s="45" t="s">
         <v>1125</v>
-      </c>
-      <c r="AC61" s="37" t="s">
-        <v>1126</v>
-      </c>
-      <c r="AD61" s="44" t="s">
-        <v>1127</v>
       </c>
       <c r="AE61" s="37"/>
       <c r="AF61" s="37" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="AG61" s="37"/>
       <c r="AH61" s="36" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="AI61" s="37"/>
       <c r="AJ61" s="37"/>
       <c r="AK61" s="37"/>
       <c r="AL61" s="37"/>
       <c r="AM61" s="37" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="AN61" s="37"/>
       <c r="AO61" s="37"/>
@@ -25638,130 +26038,130 @@
       <c r="AX61" s="37"/>
     </row>
     <row r="62">
-      <c r="A62" s="68" t="s">
+      <c r="A62" s="69" t="s">
         <v>166</v>
       </c>
-      <c r="B62" s="68" t="s">
-        <v>340</v>
-      </c>
-      <c r="C62" s="68" t="s">
-        <v>779</v>
-      </c>
-      <c r="D62" s="68" t="s">
+      <c r="B62" s="69" t="s">
+        <v>338</v>
+      </c>
+      <c r="C62" s="69" t="s">
+        <v>777</v>
+      </c>
+      <c r="D62" s="69" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E62" s="35" t="s">
+        <v>1130</v>
+      </c>
+      <c r="F62" s="36" t="s">
         <v>1131</v>
-      </c>
-      <c r="E62" s="35" t="s">
-        <v>1132</v>
-      </c>
-      <c r="F62" s="36" t="s">
-        <v>1133</v>
       </c>
       <c r="G62" s="37"/>
       <c r="H62" s="37"/>
       <c r="I62" s="37"/>
       <c r="J62" s="37" t="s">
+        <v>1132</v>
+      </c>
+      <c r="K62" s="37" t="s">
+        <v>1133</v>
+      </c>
+      <c r="L62" s="41" t="s">
         <v>1134</v>
       </c>
-      <c r="K62" s="37" t="s">
+      <c r="M62" s="37" t="s">
         <v>1135</v>
       </c>
-      <c r="L62" s="41" t="s">
-        <v>1136</v>
-      </c>
-      <c r="M62" s="37" t="s">
-        <v>1137</v>
-      </c>
-      <c r="N62" s="46"/>
+      <c r="N62" s="47"/>
       <c r="O62" s="37"/>
       <c r="P62" s="37"/>
       <c r="Q62" s="37" t="s">
-        <v>1138</v>
-      </c>
-      <c r="R62" s="54" t="s">
-        <v>1139</v>
+        <v>1136</v>
+      </c>
+      <c r="R62" s="55" t="s">
+        <v>1137</v>
       </c>
       <c r="S62" s="37"/>
       <c r="T62" s="37"/>
       <c r="U62" s="37"/>
       <c r="V62" s="37" t="s">
-        <v>1140</v>
-      </c>
-      <c r="W62" s="61" t="s">
-        <v>1141</v>
+        <v>1138</v>
+      </c>
+      <c r="W62" s="62" t="s">
+        <v>1139</v>
       </c>
       <c r="X62" s="37"/>
       <c r="Y62" s="37"/>
       <c r="Z62" s="37"/>
       <c r="AA62" s="37" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="AB62" s="37"/>
       <c r="AC62" s="37"/>
-      <c r="AD62" s="44" t="s">
-        <v>1143</v>
+      <c r="AD62" s="45" t="s">
+        <v>1141</v>
       </c>
       <c r="AE62" s="37"/>
       <c r="AF62" s="41" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="AG62" s="37"/>
-      <c r="AH62" s="63"/>
+      <c r="AH62" s="64"/>
       <c r="AI62" s="37"/>
       <c r="AJ62" s="37" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="AK62" s="37"/>
       <c r="AL62" s="37"/>
       <c r="AM62" s="37"/>
       <c r="AN62" s="37" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="AO62" s="37"/>
       <c r="AP62" s="37"/>
       <c r="AQ62" s="37" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="AR62" s="37" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="AS62" s="37"/>
       <c r="AT62" s="39"/>
-      <c r="AU62" s="52" t="s">
-        <v>1149</v>
+      <c r="AU62" s="53" t="s">
+        <v>1147</v>
       </c>
       <c r="AV62" s="39" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="AW62" s="37"/>
       <c r="AX62" s="37"/>
     </row>
     <row r="63">
-      <c r="A63" s="68" t="s">
+      <c r="A63" s="69" t="s">
         <v>166</v>
       </c>
-      <c r="B63" s="68" t="s">
-        <v>340</v>
-      </c>
-      <c r="C63" s="68" t="s">
-        <v>662</v>
-      </c>
-      <c r="D63" s="68" t="s">
+      <c r="B63" s="69" t="s">
+        <v>338</v>
+      </c>
+      <c r="C63" s="69" t="s">
+        <v>660</v>
+      </c>
+      <c r="D63" s="69" t="s">
         <v>172</v>
       </c>
       <c r="E63" s="35"/>
       <c r="F63" s="36" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="G63" s="37"/>
       <c r="H63" s="37"/>
       <c r="I63" s="37"/>
       <c r="J63" s="37"/>
       <c r="K63" s="37" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="L63" s="37"/>
       <c r="M63" s="37"/>
-      <c r="N63" s="44"/>
+      <c r="N63" s="45"/>
       <c r="O63" s="37"/>
       <c r="P63" s="37"/>
       <c r="Q63" s="37"/>
@@ -25770,8 +26170,8 @@
       <c r="T63" s="37"/>
       <c r="U63" s="37"/>
       <c r="V63" s="37"/>
-      <c r="W63" s="61" t="s">
-        <v>1153</v>
+      <c r="W63" s="62" t="s">
+        <v>1151</v>
       </c>
       <c r="X63" s="37"/>
       <c r="Y63" s="37"/>
@@ -25783,7 +26183,7 @@
       <c r="AE63" s="37"/>
       <c r="AF63" s="37"/>
       <c r="AG63" s="37"/>
-      <c r="AH63" s="63"/>
+      <c r="AH63" s="64"/>
       <c r="AI63" s="37"/>
       <c r="AJ63" s="37"/>
       <c r="AK63" s="37"/>
@@ -25798,38 +26198,38 @@
       <c r="AT63" s="39"/>
       <c r="AU63" s="37"/>
       <c r="AV63" s="39" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="AW63" s="37"/>
       <c r="AX63" s="37"/>
     </row>
     <row r="64">
-      <c r="A64" s="68" t="s">
+      <c r="A64" s="69" t="s">
         <v>166</v>
       </c>
-      <c r="B64" s="68" t="s">
-        <v>340</v>
-      </c>
-      <c r="C64" s="68" t="s">
+      <c r="B64" s="69" t="s">
+        <v>338</v>
+      </c>
+      <c r="C64" s="69" t="s">
         <v>90</v>
       </c>
-      <c r="D64" s="68" t="s">
+      <c r="D64" s="69" t="s">
         <v>190</v>
       </c>
       <c r="E64" s="35"/>
       <c r="F64" s="36" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
       <c r="I64" s="37"/>
       <c r="J64" s="37" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="K64" s="37"/>
       <c r="L64" s="37"/>
       <c r="M64" s="37"/>
-      <c r="N64" s="46"/>
+      <c r="N64" s="47"/>
       <c r="O64" s="37"/>
       <c r="P64" s="37"/>
       <c r="Q64" s="37"/>
@@ -25838,8 +26238,8 @@
       <c r="T64" s="37"/>
       <c r="U64" s="37"/>
       <c r="V64" s="37"/>
-      <c r="W64" s="62" t="s">
-        <v>1157</v>
+      <c r="W64" s="63" t="s">
+        <v>1155</v>
       </c>
       <c r="X64" s="37"/>
       <c r="Y64" s="37"/>
@@ -25851,7 +26251,7 @@
       <c r="AE64" s="37"/>
       <c r="AF64" s="37"/>
       <c r="AG64" s="37"/>
-      <c r="AH64" s="63"/>
+      <c r="AH64" s="64"/>
       <c r="AI64" s="37"/>
       <c r="AJ64" s="37"/>
       <c r="AK64" s="37"/>
@@ -25866,27 +26266,27 @@
       <c r="AT64" s="39"/>
       <c r="AU64" s="37"/>
       <c r="AV64" s="39" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="AW64" s="37"/>
       <c r="AX64" s="37"/>
     </row>
     <row r="65">
-      <c r="A65" s="69" t="s">
+      <c r="A65" s="70" t="s">
         <v>193</v>
       </c>
-      <c r="B65" s="69" t="s">
-        <v>340</v>
-      </c>
-      <c r="C65" s="69" t="s">
-        <v>1117</v>
-      </c>
-      <c r="D65" s="69" t="s">
-        <v>1159</v>
+      <c r="B65" s="70" t="s">
+        <v>338</v>
+      </c>
+      <c r="C65" s="70" t="s">
+        <v>1115</v>
+      </c>
+      <c r="D65" s="70" t="s">
+        <v>1157</v>
       </c>
       <c r="E65" s="35"/>
       <c r="F65" s="36" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="G65" s="37"/>
       <c r="H65" s="37"/>
@@ -25894,43 +26294,43 @@
       <c r="J65" s="37"/>
       <c r="K65" s="37"/>
       <c r="L65" s="37" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="M65" s="37" t="s">
-        <v>1162</v>
-      </c>
-      <c r="N65" s="44"/>
+        <v>1160</v>
+      </c>
+      <c r="N65" s="45"/>
       <c r="O65" s="37"/>
       <c r="P65" s="41" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="Q65" s="37"/>
       <c r="R65" s="37"/>
       <c r="S65" s="37" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="T65" s="37"/>
       <c r="U65" s="37"/>
       <c r="V65" s="37"/>
-      <c r="W65" s="62"/>
+      <c r="W65" s="63"/>
       <c r="X65" s="37"/>
       <c r="Y65" s="37"/>
       <c r="Z65" s="37"/>
       <c r="AA65" s="37"/>
       <c r="AB65" s="37"/>
       <c r="AC65" s="37"/>
-      <c r="AD65" s="44" t="s">
-        <v>1165</v>
+      <c r="AD65" s="45" t="s">
+        <v>1163</v>
       </c>
       <c r="AE65" s="37"/>
       <c r="AF65" s="41" t="s">
+        <v>1164</v>
+      </c>
+      <c r="AG65" s="37" t="s">
+        <v>1165</v>
+      </c>
+      <c r="AH65" s="36" t="s">
         <v>1166</v>
-      </c>
-      <c r="AG65" s="37" t="s">
-        <v>1167</v>
-      </c>
-      <c r="AH65" s="36" t="s">
-        <v>1168</v>
       </c>
       <c r="AI65" s="37"/>
       <c r="AJ65" s="37"/>
@@ -25941,7 +26341,7 @@
       <c r="AO65" s="37"/>
       <c r="AP65" s="37"/>
       <c r="AQ65" s="37" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="AR65" s="37"/>
       <c r="AS65" s="37"/>
@@ -25952,21 +26352,21 @@
       <c r="AX65" s="37"/>
     </row>
     <row r="66">
-      <c r="A66" s="69" t="s">
+      <c r="A66" s="70" t="s">
         <v>193</v>
       </c>
-      <c r="B66" s="69" t="s">
-        <v>340</v>
-      </c>
-      <c r="C66" s="69" t="s">
-        <v>779</v>
-      </c>
-      <c r="D66" s="69" t="s">
+      <c r="B66" s="70" t="s">
+        <v>338</v>
+      </c>
+      <c r="C66" s="70" t="s">
+        <v>777</v>
+      </c>
+      <c r="D66" s="70" t="s">
         <v>197</v>
       </c>
       <c r="E66" s="35"/>
       <c r="F66" s="36" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G66" s="37"/>
       <c r="H66" s="37"/>
@@ -25974,74 +26374,74 @@
       <c r="J66" s="37"/>
       <c r="K66" s="37"/>
       <c r="L66" s="37" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="M66" s="37"/>
-      <c r="N66" s="44"/>
+      <c r="N66" s="45"/>
       <c r="O66" s="37"/>
       <c r="P66" s="37"/>
       <c r="Q66" s="37"/>
-      <c r="R66" s="53" t="s">
-        <v>1172</v>
+      <c r="R66" s="54" t="s">
+        <v>1170</v>
       </c>
       <c r="S66" s="37"/>
       <c r="T66" s="37" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="U66" s="37"/>
       <c r="V66" s="37" t="s">
-        <v>1174</v>
-      </c>
-      <c r="W66" s="61" t="s">
-        <v>1175</v>
+        <v>1172</v>
+      </c>
+      <c r="W66" s="62" t="s">
+        <v>1173</v>
       </c>
       <c r="X66" s="37"/>
       <c r="Y66" s="37" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="Z66" s="37"/>
       <c r="AA66" s="37"/>
       <c r="AB66" s="37" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="AC66" s="37"/>
       <c r="AD66" s="37" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="AE66" s="37"/>
       <c r="AF66" s="37" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="AG66" s="37"/>
       <c r="AH66" s="36" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="AI66" s="37"/>
       <c r="AJ66" s="37"/>
       <c r="AK66" s="37"/>
       <c r="AL66" s="37" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="AM66" s="37"/>
       <c r="AN66" s="37"/>
       <c r="AO66" s="37"/>
       <c r="AP66" s="37" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="AQ66" s="37"/>
       <c r="AR66" s="37" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="AS66" s="37"/>
       <c r="AT66" s="39" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="AU66" s="37"/>
       <c r="AV66" s="39" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="AW66" s="37" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="AX66" s="37"/>
     </row>
@@ -26059,7 +26459,7 @@
       <c r="K67" s="37"/>
       <c r="L67" s="37"/>
       <c r="M67" s="37"/>
-      <c r="N67" s="44"/>
+      <c r="N67" s="45"/>
       <c r="O67" s="37"/>
       <c r="P67" s="37"/>
       <c r="Q67" s="37"/>
@@ -26111,7 +26511,7 @@
       <c r="K68" s="37"/>
       <c r="L68" s="37"/>
       <c r="M68" s="37"/>
-      <c r="N68" s="44"/>
+      <c r="N68" s="45"/>
       <c r="O68" s="37"/>
       <c r="P68" s="37"/>
       <c r="Q68" s="37"/>
@@ -26163,7 +26563,7 @@
       <c r="K69" s="37"/>
       <c r="L69" s="37"/>
       <c r="M69" s="37"/>
-      <c r="N69" s="44"/>
+      <c r="N69" s="45"/>
       <c r="O69" s="37"/>
       <c r="P69" s="37"/>
       <c r="Q69" s="37"/>
@@ -26215,7 +26615,7 @@
       <c r="K70" s="37"/>
       <c r="L70" s="37"/>
       <c r="M70" s="37"/>
-      <c r="N70" s="44"/>
+      <c r="N70" s="45"/>
       <c r="O70" s="37"/>
       <c r="P70" s="37"/>
       <c r="Q70" s="37"/>
@@ -26267,7 +26667,7 @@
       <c r="K71" s="37"/>
       <c r="L71" s="37"/>
       <c r="M71" s="37"/>
-      <c r="N71" s="44"/>
+      <c r="N71" s="45"/>
       <c r="O71" s="37"/>
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
@@ -74638,290 +75038,600 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="71" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B1" s="71" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="72"/>
+      <c r="O1" s="72"/>
+      <c r="P1" s="72"/>
+      <c r="Q1" s="72"/>
+      <c r="R1" s="72"/>
+      <c r="S1" s="72"/>
+      <c r="T1" s="72"/>
+      <c r="U1" s="72"/>
+      <c r="V1" s="72"/>
+      <c r="W1" s="72"/>
+      <c r="X1" s="72"/>
+      <c r="Y1" s="72"/>
+      <c r="Z1" s="72"/>
+    </row>
+    <row r="2" ht="39.75" customHeight="1">
+      <c r="A2" s="73" t="s">
         <v>1187</v>
       </c>
-      <c r="B1" s="70" t="s">
+      <c r="B2" s="74" t="s">
         <v>1188</v>
       </c>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
-      <c r="I1" s="71"/>
-      <c r="J1" s="71"/>
-      <c r="K1" s="71"/>
-      <c r="L1" s="71"/>
-      <c r="M1" s="71"/>
-      <c r="N1" s="71"/>
-      <c r="O1" s="71"/>
-      <c r="P1" s="71"/>
-      <c r="Q1" s="71"/>
-      <c r="R1" s="71"/>
-      <c r="S1" s="71"/>
-      <c r="T1" s="71"/>
-      <c r="U1" s="71"/>
-      <c r="V1" s="71"/>
-      <c r="W1" s="71"/>
-      <c r="X1" s="71"/>
-      <c r="Y1" s="71"/>
-      <c r="Z1" s="71"/>
-    </row>
-    <row r="2" ht="39.75" customHeight="1">
-      <c r="A2" s="72" t="s">
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
+      <c r="M2" s="72"/>
+      <c r="N2" s="72"/>
+      <c r="O2" s="72"/>
+      <c r="P2" s="72"/>
+      <c r="Q2" s="72"/>
+      <c r="R2" s="72"/>
+      <c r="S2" s="72"/>
+      <c r="T2" s="72"/>
+      <c r="U2" s="72"/>
+      <c r="V2" s="72"/>
+      <c r="W2" s="72"/>
+      <c r="X2" s="72"/>
+      <c r="Y2" s="72"/>
+      <c r="Z2" s="72"/>
+    </row>
+    <row r="3" ht="39.75" customHeight="1">
+      <c r="A3" s="73" t="s">
         <v>1189</v>
       </c>
-      <c r="B2" s="73" t="s">
+      <c r="B3" s="74" t="s">
         <v>1190</v>
       </c>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="71"/>
-      <c r="K2" s="71"/>
-      <c r="L2" s="71"/>
-      <c r="M2" s="71"/>
-      <c r="N2" s="71"/>
-      <c r="O2" s="71"/>
-      <c r="P2" s="71"/>
-      <c r="Q2" s="71"/>
-      <c r="R2" s="71"/>
-      <c r="S2" s="71"/>
-      <c r="T2" s="71"/>
-      <c r="U2" s="71"/>
-      <c r="V2" s="71"/>
-      <c r="W2" s="71"/>
-      <c r="X2" s="71"/>
-      <c r="Y2" s="71"/>
-      <c r="Z2" s="71"/>
-    </row>
-    <row r="3" ht="39.75" customHeight="1">
-      <c r="A3" s="74" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="75" t="s">
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="72"/>
+      <c r="K3" s="72"/>
+      <c r="L3" s="72"/>
+      <c r="M3" s="72"/>
+      <c r="N3" s="72"/>
+      <c r="O3" s="72"/>
+      <c r="P3" s="72"/>
+      <c r="Q3" s="72"/>
+      <c r="R3" s="72"/>
+      <c r="S3" s="72"/>
+      <c r="T3" s="72"/>
+      <c r="U3" s="72"/>
+      <c r="V3" s="72"/>
+      <c r="W3" s="72"/>
+      <c r="X3" s="72"/>
+      <c r="Y3" s="72"/>
+      <c r="Z3" s="72"/>
+    </row>
+    <row r="4" ht="39.75" customHeight="1">
+      <c r="A4" s="73" t="s">
         <v>1191</v>
       </c>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="71"/>
-      <c r="K3" s="71"/>
-      <c r="L3" s="71"/>
-      <c r="M3" s="71"/>
-      <c r="N3" s="71"/>
-      <c r="O3" s="71"/>
-      <c r="P3" s="71"/>
-      <c r="Q3" s="71"/>
-      <c r="R3" s="71"/>
-      <c r="S3" s="71"/>
-      <c r="T3" s="71"/>
-      <c r="U3" s="71"/>
-      <c r="V3" s="71"/>
-      <c r="W3" s="71"/>
-      <c r="X3" s="71"/>
-      <c r="Y3" s="71"/>
-      <c r="Z3" s="71"/>
-    </row>
-    <row r="4" ht="39.75" customHeight="1">
-      <c r="A4" s="72" t="s">
+      <c r="B4" s="74" t="s">
         <v>1192</v>
       </c>
-      <c r="B4" s="73" t="s">
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="72"/>
+      <c r="K4" s="72"/>
+      <c r="L4" s="72"/>
+      <c r="M4" s="72"/>
+      <c r="N4" s="72"/>
+      <c r="O4" s="72"/>
+      <c r="P4" s="72"/>
+      <c r="Q4" s="72"/>
+      <c r="R4" s="72"/>
+      <c r="S4" s="72"/>
+      <c r="T4" s="72"/>
+      <c r="U4" s="72"/>
+      <c r="V4" s="72"/>
+      <c r="W4" s="72"/>
+      <c r="X4" s="72"/>
+      <c r="Y4" s="72"/>
+      <c r="Z4" s="72"/>
+    </row>
+    <row r="5" ht="39.75" customHeight="1">
+      <c r="A5" s="73" t="s">
         <v>1193</v>
       </c>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="71"/>
-      <c r="G4" s="71"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="71"/>
-      <c r="K4" s="71"/>
-      <c r="L4" s="71"/>
-      <c r="M4" s="71"/>
-      <c r="N4" s="71"/>
-      <c r="O4" s="71"/>
-      <c r="P4" s="71"/>
-      <c r="Q4" s="71"/>
-      <c r="R4" s="71"/>
-      <c r="S4" s="71"/>
-      <c r="T4" s="71"/>
-      <c r="U4" s="71"/>
-      <c r="V4" s="71"/>
-      <c r="W4" s="71"/>
-      <c r="X4" s="71"/>
-      <c r="Y4" s="71"/>
-      <c r="Z4" s="71"/>
-    </row>
-    <row r="5" ht="39.75" customHeight="1">
-      <c r="A5" s="74" t="s">
-        <v>56</v>
-      </c>
-      <c r="B5" s="75" t="s">
+      <c r="B5" s="74" t="s">
         <v>1194</v>
       </c>
-      <c r="C5" s="71"/>
-      <c r="D5" s="71"/>
-      <c r="E5" s="71"/>
-      <c r="F5" s="71"/>
-      <c r="G5" s="71"/>
-      <c r="H5" s="71"/>
-      <c r="I5" s="71"/>
-      <c r="J5" s="71"/>
-      <c r="K5" s="71"/>
-      <c r="L5" s="71"/>
-      <c r="M5" s="71"/>
-      <c r="N5" s="71"/>
-      <c r="O5" s="71"/>
-      <c r="P5" s="71"/>
-      <c r="Q5" s="71"/>
-      <c r="R5" s="71"/>
-      <c r="S5" s="71"/>
-      <c r="T5" s="71"/>
-      <c r="U5" s="71"/>
-      <c r="V5" s="71"/>
-      <c r="W5" s="71"/>
-      <c r="X5" s="71"/>
-      <c r="Y5" s="71"/>
-      <c r="Z5" s="71"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="72"/>
+      <c r="K5" s="72"/>
+      <c r="L5" s="72"/>
+      <c r="M5" s="72"/>
+      <c r="N5" s="72"/>
+      <c r="O5" s="72"/>
+      <c r="P5" s="72"/>
+      <c r="Q5" s="72"/>
+      <c r="R5" s="72"/>
+      <c r="S5" s="72"/>
+      <c r="T5" s="72"/>
+      <c r="U5" s="72"/>
+      <c r="V5" s="72"/>
+      <c r="W5" s="72"/>
+      <c r="X5" s="72"/>
+      <c r="Y5" s="72"/>
+      <c r="Z5" s="72"/>
     </row>
     <row r="6" ht="39.75" customHeight="1">
-      <c r="A6" s="72" t="s">
+      <c r="A6" s="73" t="s">
         <v>1195</v>
       </c>
-      <c r="B6" s="73" t="s">
+      <c r="B6" s="74" t="s">
         <v>1196</v>
       </c>
-      <c r="C6" s="71"/>
-      <c r="D6" s="71"/>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
-      <c r="J6" s="71"/>
-      <c r="K6" s="71"/>
-      <c r="L6" s="71"/>
-      <c r="M6" s="71"/>
-      <c r="N6" s="71"/>
-      <c r="O6" s="71"/>
-      <c r="P6" s="71"/>
-      <c r="Q6" s="71"/>
-      <c r="R6" s="71"/>
-      <c r="S6" s="71"/>
-      <c r="T6" s="71"/>
-      <c r="U6" s="71"/>
-      <c r="V6" s="71"/>
-      <c r="W6" s="71"/>
-      <c r="X6" s="71"/>
-      <c r="Y6" s="71"/>
-      <c r="Z6" s="71"/>
+      <c r="C6" s="72"/>
+      <c r="D6" s="72"/>
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="72"/>
+      <c r="K6" s="72"/>
+      <c r="L6" s="72"/>
+      <c r="M6" s="72"/>
+      <c r="N6" s="72"/>
+      <c r="O6" s="72"/>
+      <c r="P6" s="72"/>
+      <c r="Q6" s="72"/>
+      <c r="R6" s="72"/>
+      <c r="S6" s="72"/>
+      <c r="T6" s="72"/>
+      <c r="U6" s="72"/>
+      <c r="V6" s="72"/>
+      <c r="W6" s="72"/>
+      <c r="X6" s="72"/>
+      <c r="Y6" s="72"/>
+      <c r="Z6" s="72"/>
     </row>
     <row r="7" ht="39.75" customHeight="1">
-      <c r="A7" s="74" t="s">
-        <v>663</v>
-      </c>
-      <c r="B7" s="75" t="s">
+      <c r="A7" s="73" t="s">
         <v>1197</v>
       </c>
-      <c r="C7" s="71"/>
-      <c r="D7" s="71"/>
-      <c r="E7" s="71"/>
-      <c r="F7" s="71"/>
-      <c r="G7" s="71"/>
-      <c r="H7" s="71"/>
-      <c r="I7" s="71"/>
-      <c r="J7" s="71"/>
-      <c r="K7" s="71"/>
-      <c r="L7" s="71"/>
-      <c r="M7" s="71"/>
-      <c r="N7" s="71"/>
-      <c r="O7" s="71"/>
-      <c r="P7" s="71"/>
-      <c r="Q7" s="71"/>
-      <c r="R7" s="71"/>
-      <c r="S7" s="71"/>
-      <c r="T7" s="71"/>
-      <c r="U7" s="71"/>
-      <c r="V7" s="71"/>
-      <c r="W7" s="71"/>
-      <c r="X7" s="71"/>
-      <c r="Y7" s="71"/>
-      <c r="Z7" s="71"/>
+      <c r="B7" s="74" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C7" s="72"/>
+      <c r="D7" s="72"/>
+      <c r="E7" s="72"/>
+      <c r="F7" s="72"/>
+      <c r="G7" s="72"/>
+      <c r="H7" s="72"/>
+      <c r="I7" s="72"/>
+      <c r="J7" s="72"/>
+      <c r="K7" s="72"/>
+      <c r="L7" s="72"/>
+      <c r="M7" s="72"/>
+      <c r="N7" s="72"/>
+      <c r="O7" s="72"/>
+      <c r="P7" s="72"/>
+      <c r="Q7" s="72"/>
+      <c r="R7" s="72"/>
+      <c r="S7" s="72"/>
+      <c r="T7" s="72"/>
+      <c r="U7" s="72"/>
+      <c r="V7" s="72"/>
+      <c r="W7" s="72"/>
+      <c r="X7" s="72"/>
+      <c r="Y7" s="72"/>
+      <c r="Z7" s="72"/>
     </row>
     <row r="8" ht="39.75" customHeight="1">
-      <c r="A8" s="72" t="s">
-        <v>1198</v>
-      </c>
-      <c r="B8" s="73" t="s">
+      <c r="A8" s="73" t="s">
         <v>1199</v>
       </c>
-      <c r="C8" s="71"/>
-      <c r="D8" s="71"/>
-      <c r="E8" s="71"/>
-      <c r="F8" s="71"/>
-      <c r="G8" s="71"/>
-      <c r="H8" s="71"/>
-      <c r="I8" s="71"/>
-      <c r="J8" s="71"/>
-      <c r="K8" s="71"/>
-      <c r="L8" s="71"/>
-      <c r="M8" s="71"/>
-      <c r="N8" s="71"/>
-      <c r="O8" s="71"/>
-      <c r="P8" s="71"/>
-      <c r="Q8" s="71"/>
-      <c r="R8" s="71"/>
-      <c r="S8" s="71"/>
-      <c r="T8" s="71"/>
-      <c r="U8" s="71"/>
-      <c r="V8" s="71"/>
-      <c r="W8" s="71"/>
-      <c r="X8" s="71"/>
-      <c r="Y8" s="71"/>
-      <c r="Z8" s="71"/>
+      <c r="B8" s="74" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C8" s="72"/>
+      <c r="D8" s="72"/>
+      <c r="E8" s="72"/>
+      <c r="F8" s="72"/>
+      <c r="G8" s="72"/>
+      <c r="H8" s="72"/>
+      <c r="I8" s="72"/>
+      <c r="J8" s="72"/>
+      <c r="K8" s="72"/>
+      <c r="L8" s="72"/>
+      <c r="M8" s="72"/>
+      <c r="N8" s="72"/>
+      <c r="O8" s="72"/>
+      <c r="P8" s="72"/>
+      <c r="Q8" s="72"/>
+      <c r="R8" s="72"/>
+      <c r="S8" s="72"/>
+      <c r="T8" s="72"/>
+      <c r="U8" s="72"/>
+      <c r="V8" s="72"/>
+      <c r="W8" s="72"/>
+      <c r="X8" s="72"/>
+      <c r="Y8" s="72"/>
+      <c r="Z8" s="72"/>
     </row>
     <row r="9" ht="39.75" customHeight="1">
-      <c r="A9" s="76"/>
-      <c r="B9" s="75"/>
-      <c r="C9" s="71"/>
-      <c r="D9" s="71"/>
-      <c r="E9" s="71"/>
-      <c r="F9" s="71"/>
-      <c r="G9" s="71"/>
-      <c r="H9" s="71"/>
-      <c r="I9" s="71"/>
-      <c r="J9" s="71"/>
-      <c r="K9" s="71"/>
-      <c r="L9" s="71"/>
-      <c r="M9" s="71"/>
-      <c r="N9" s="71"/>
-      <c r="O9" s="71"/>
-      <c r="P9" s="71"/>
-      <c r="Q9" s="71"/>
-      <c r="R9" s="71"/>
-      <c r="S9" s="71"/>
-      <c r="T9" s="71"/>
-      <c r="U9" s="71"/>
-      <c r="V9" s="71"/>
-      <c r="W9" s="71"/>
-      <c r="X9" s="71"/>
-      <c r="Y9" s="71"/>
-      <c r="Z9" s="71"/>
+      <c r="A9" s="73" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B9" s="74" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C9" s="72"/>
+      <c r="D9" s="72"/>
+      <c r="E9" s="72"/>
+      <c r="F9" s="72"/>
+      <c r="G9" s="72"/>
+      <c r="H9" s="72"/>
+      <c r="I9" s="72"/>
+      <c r="J9" s="72"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="72"/>
+      <c r="M9" s="72"/>
+      <c r="N9" s="72"/>
+      <c r="O9" s="72"/>
+      <c r="P9" s="72"/>
+      <c r="Q9" s="72"/>
+      <c r="R9" s="72"/>
+      <c r="S9" s="72"/>
+      <c r="T9" s="72"/>
+      <c r="U9" s="72"/>
+      <c r="V9" s="72"/>
+      <c r="W9" s="72"/>
+      <c r="X9" s="72"/>
+      <c r="Y9" s="72"/>
+      <c r="Z9" s="72"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="73" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B10" s="74" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="73" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B11" s="74" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="73" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B12" s="74" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="73" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B13" s="74" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="73" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B14" s="74" t="s">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="73" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B15" s="74" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="75" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B16" s="74" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="73" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B17" s="76" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="73" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B18" s="74" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="73" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B19" s="74" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="73" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B20" s="74" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="73" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B21" s="74" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="73" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B22" s="74" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="73" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B23" s="74" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="73" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B24" s="74" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="73" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B25" s="77" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="73" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B26" s="74" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="73" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B27" s="74" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="73" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B28" s="78" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="73" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B29" s="78" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="73" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B30" s="74" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="73" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B31" s="74" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="73" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B32" s="79" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="73" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B33" s="74" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="73" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B34" s="74" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="73" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B35" s="74" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="73" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B36" s="74" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="73" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B37" s="74" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="73" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B38" s="74" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="73" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B39" s="74" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="73" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B40" s="74" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="73" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B41" s="74" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="73" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B42" s="74" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="73" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B43" s="80" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="73" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B44" s="74" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="81" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B45" s="76" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="81" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B46" s="82"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="81" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B47" s="76" t="s">
+        <v>1277</v>
+      </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="B28"/>
+    <hyperlink r:id="rId2" ref="B29"/>
+  </hyperlinks>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>